--- a/datos_stock.xlsx
+++ b/datos_stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ingen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63011BCC-7DD7-466E-97F9-FB4692FD19D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07D13A0-777D-473E-AA9E-2BB2F35104FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="813" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5102" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5623" uniqueCount="1317">
   <si>
     <t>GLINA. MONTBLANC ESTUCHE16ESTX7UN INT NG GEMA</t>
   </si>
@@ -2434,6 +2434,1569 @@
   </si>
   <si>
     <t>Plan de demanda</t>
+  </si>
+  <si>
+    <t>Prueba 1</t>
+  </si>
+  <si>
+    <t>Prueba 2</t>
+  </si>
+  <si>
+    <t>Prueba 3</t>
+  </si>
+  <si>
+    <t>Prueba 4</t>
+  </si>
+  <si>
+    <t>Prueba 5</t>
+  </si>
+  <si>
+    <t>Prueba 6</t>
+  </si>
+  <si>
+    <t>Prueba 7</t>
+  </si>
+  <si>
+    <t>Prueba 8</t>
+  </si>
+  <si>
+    <t>Prueba 9</t>
+  </si>
+  <si>
+    <t>Prueba 10</t>
+  </si>
+  <si>
+    <t>Prueba 11</t>
+  </si>
+  <si>
+    <t>Prueba 12</t>
+  </si>
+  <si>
+    <t>Prueba 13</t>
+  </si>
+  <si>
+    <t>Prueba 14</t>
+  </si>
+  <si>
+    <t>Prueba 15</t>
+  </si>
+  <si>
+    <t>Prueba 16</t>
+  </si>
+  <si>
+    <t>Prueba 17</t>
+  </si>
+  <si>
+    <t>Prueba 18</t>
+  </si>
+  <si>
+    <t>Prueba 19</t>
+  </si>
+  <si>
+    <t>Prueba 20</t>
+  </si>
+  <si>
+    <t>Prueba 21</t>
+  </si>
+  <si>
+    <t>Prueba 22</t>
+  </si>
+  <si>
+    <t>Prueba 23</t>
+  </si>
+  <si>
+    <t>Prueba 24</t>
+  </si>
+  <si>
+    <t>Prueba 25</t>
+  </si>
+  <si>
+    <t>Prueba 26</t>
+  </si>
+  <si>
+    <t>Prueba 27</t>
+  </si>
+  <si>
+    <t>Prueba 28</t>
+  </si>
+  <si>
+    <t>Prueba 29</t>
+  </si>
+  <si>
+    <t>Prueba 30</t>
+  </si>
+  <si>
+    <t>Prueba 31</t>
+  </si>
+  <si>
+    <t>Prueba 32</t>
+  </si>
+  <si>
+    <t>Prueba 33</t>
+  </si>
+  <si>
+    <t>Prueba 34</t>
+  </si>
+  <si>
+    <t>Prueba 35</t>
+  </si>
+  <si>
+    <t>Prueba 36</t>
+  </si>
+  <si>
+    <t>Prueba 37</t>
+  </si>
+  <si>
+    <t>Prueba 38</t>
+  </si>
+  <si>
+    <t>Prueba 39</t>
+  </si>
+  <si>
+    <t>Prueba 40</t>
+  </si>
+  <si>
+    <t>Prueba 41</t>
+  </si>
+  <si>
+    <t>Prueba 42</t>
+  </si>
+  <si>
+    <t>Prueba 43</t>
+  </si>
+  <si>
+    <t>Prueba 44</t>
+  </si>
+  <si>
+    <t>Prueba 45</t>
+  </si>
+  <si>
+    <t>Prueba 46</t>
+  </si>
+  <si>
+    <t>Prueba 47</t>
+  </si>
+  <si>
+    <t>Prueba 48</t>
+  </si>
+  <si>
+    <t>Prueba 49</t>
+  </si>
+  <si>
+    <t>Prueba 50</t>
+  </si>
+  <si>
+    <t>Prueba 51</t>
+  </si>
+  <si>
+    <t>Prueba 52</t>
+  </si>
+  <si>
+    <t>Prueba 53</t>
+  </si>
+  <si>
+    <t>Prueba 54</t>
+  </si>
+  <si>
+    <t>Prueba 55</t>
+  </si>
+  <si>
+    <t>Prueba 56</t>
+  </si>
+  <si>
+    <t>Prueba 57</t>
+  </si>
+  <si>
+    <t>Prueba 58</t>
+  </si>
+  <si>
+    <t>Prueba 59</t>
+  </si>
+  <si>
+    <t>Prueba 60</t>
+  </si>
+  <si>
+    <t>Prueba 61</t>
+  </si>
+  <si>
+    <t>Prueba 62</t>
+  </si>
+  <si>
+    <t>Prueba 63</t>
+  </si>
+  <si>
+    <t>Prueba 64</t>
+  </si>
+  <si>
+    <t>Prueba 65</t>
+  </si>
+  <si>
+    <t>Prueba 66</t>
+  </si>
+  <si>
+    <t>Prueba 67</t>
+  </si>
+  <si>
+    <t>Prueba 68</t>
+  </si>
+  <si>
+    <t>Prueba 69</t>
+  </si>
+  <si>
+    <t>Prueba 70</t>
+  </si>
+  <si>
+    <t>Prueba 71</t>
+  </si>
+  <si>
+    <t>Prueba 72</t>
+  </si>
+  <si>
+    <t>Prueba 73</t>
+  </si>
+  <si>
+    <t>Prueba 74</t>
+  </si>
+  <si>
+    <t>Prueba 75</t>
+  </si>
+  <si>
+    <t>Prueba 76</t>
+  </si>
+  <si>
+    <t>Prueba 77</t>
+  </si>
+  <si>
+    <t>Prueba 78</t>
+  </si>
+  <si>
+    <t>Prueba 79</t>
+  </si>
+  <si>
+    <t>Prueba 80</t>
+  </si>
+  <si>
+    <t>Prueba 81</t>
+  </si>
+  <si>
+    <t>Prueba 82</t>
+  </si>
+  <si>
+    <t>Prueba 83</t>
+  </si>
+  <si>
+    <t>Prueba 84</t>
+  </si>
+  <si>
+    <t>Prueba 85</t>
+  </si>
+  <si>
+    <t>Prueba 86</t>
+  </si>
+  <si>
+    <t>Prueba 87</t>
+  </si>
+  <si>
+    <t>Prueba 88</t>
+  </si>
+  <si>
+    <t>Prueba 89</t>
+  </si>
+  <si>
+    <t>Prueba 90</t>
+  </si>
+  <si>
+    <t>Prueba 91</t>
+  </si>
+  <si>
+    <t>Prueba 92</t>
+  </si>
+  <si>
+    <t>Prueba 93</t>
+  </si>
+  <si>
+    <t>Prueba 94</t>
+  </si>
+  <si>
+    <t>Prueba 95</t>
+  </si>
+  <si>
+    <t>Prueba 96</t>
+  </si>
+  <si>
+    <t>Prueba 97</t>
+  </si>
+  <si>
+    <t>Prueba 98</t>
+  </si>
+  <si>
+    <t>Prueba 99</t>
+  </si>
+  <si>
+    <t>Prueba 100</t>
+  </si>
+  <si>
+    <t>Prueba 101</t>
+  </si>
+  <si>
+    <t>Prueba 102</t>
+  </si>
+  <si>
+    <t>Prueba 103</t>
+  </si>
+  <si>
+    <t>Prueba 104</t>
+  </si>
+  <si>
+    <t>Prueba 105</t>
+  </si>
+  <si>
+    <t>Prueba 106</t>
+  </si>
+  <si>
+    <t>Prueba 107</t>
+  </si>
+  <si>
+    <t>Prueba 108</t>
+  </si>
+  <si>
+    <t>Prueba 109</t>
+  </si>
+  <si>
+    <t>Prueba 110</t>
+  </si>
+  <si>
+    <t>Prueba 111</t>
+  </si>
+  <si>
+    <t>Prueba 112</t>
+  </si>
+  <si>
+    <t>Prueba 113</t>
+  </si>
+  <si>
+    <t>Prueba 114</t>
+  </si>
+  <si>
+    <t>Prueba 115</t>
+  </si>
+  <si>
+    <t>Prueba 116</t>
+  </si>
+  <si>
+    <t>Prueba 117</t>
+  </si>
+  <si>
+    <t>Prueba 118</t>
+  </si>
+  <si>
+    <t>Prueba 119</t>
+  </si>
+  <si>
+    <t>Prueba 120</t>
+  </si>
+  <si>
+    <t>Prueba 121</t>
+  </si>
+  <si>
+    <t>Prueba 122</t>
+  </si>
+  <si>
+    <t>Prueba 123</t>
+  </si>
+  <si>
+    <t>Prueba 124</t>
+  </si>
+  <si>
+    <t>Prueba 125</t>
+  </si>
+  <si>
+    <t>Prueba 126</t>
+  </si>
+  <si>
+    <t>Prueba 127</t>
+  </si>
+  <si>
+    <t>Prueba 128</t>
+  </si>
+  <si>
+    <t>Prueba 129</t>
+  </si>
+  <si>
+    <t>Prueba 130</t>
+  </si>
+  <si>
+    <t>Prueba 131</t>
+  </si>
+  <si>
+    <t>Prueba 132</t>
+  </si>
+  <si>
+    <t>Prueba 133</t>
+  </si>
+  <si>
+    <t>Prueba 134</t>
+  </si>
+  <si>
+    <t>Prueba 135</t>
+  </si>
+  <si>
+    <t>Prueba 136</t>
+  </si>
+  <si>
+    <t>Prueba 137</t>
+  </si>
+  <si>
+    <t>Prueba 138</t>
+  </si>
+  <si>
+    <t>Prueba 139</t>
+  </si>
+  <si>
+    <t>Prueba 140</t>
+  </si>
+  <si>
+    <t>Prueba 141</t>
+  </si>
+  <si>
+    <t>Prueba 142</t>
+  </si>
+  <si>
+    <t>Prueba 143</t>
+  </si>
+  <si>
+    <t>Prueba 144</t>
+  </si>
+  <si>
+    <t>Prueba 145</t>
+  </si>
+  <si>
+    <t>Prueba 146</t>
+  </si>
+  <si>
+    <t>Prueba 147</t>
+  </si>
+  <si>
+    <t>Prueba 148</t>
+  </si>
+  <si>
+    <t>Prueba 149</t>
+  </si>
+  <si>
+    <t>Prueba 150</t>
+  </si>
+  <si>
+    <t>Prueba 151</t>
+  </si>
+  <si>
+    <t>Prueba 152</t>
+  </si>
+  <si>
+    <t>Prueba 153</t>
+  </si>
+  <si>
+    <t>Prueba 154</t>
+  </si>
+  <si>
+    <t>Prueba 155</t>
+  </si>
+  <si>
+    <t>Prueba 156</t>
+  </si>
+  <si>
+    <t>Prueba 157</t>
+  </si>
+  <si>
+    <t>Prueba 158</t>
+  </si>
+  <si>
+    <t>Prueba 159</t>
+  </si>
+  <si>
+    <t>Prueba 160</t>
+  </si>
+  <si>
+    <t>Prueba 161</t>
+  </si>
+  <si>
+    <t>Prueba 162</t>
+  </si>
+  <si>
+    <t>Prueba 163</t>
+  </si>
+  <si>
+    <t>Prueba 164</t>
+  </si>
+  <si>
+    <t>Prueba 165</t>
+  </si>
+  <si>
+    <t>Prueba 166</t>
+  </si>
+  <si>
+    <t>Prueba 167</t>
+  </si>
+  <si>
+    <t>Prueba 168</t>
+  </si>
+  <si>
+    <t>Prueba 169</t>
+  </si>
+  <si>
+    <t>Prueba 170</t>
+  </si>
+  <si>
+    <t>Prueba 171</t>
+  </si>
+  <si>
+    <t>Prueba 172</t>
+  </si>
+  <si>
+    <t>Prueba 173</t>
+  </si>
+  <si>
+    <t>Prueba 174</t>
+  </si>
+  <si>
+    <t>Prueba 175</t>
+  </si>
+  <si>
+    <t>Prueba 176</t>
+  </si>
+  <si>
+    <t>Prueba 177</t>
+  </si>
+  <si>
+    <t>Prueba 178</t>
+  </si>
+  <si>
+    <t>Prueba 179</t>
+  </si>
+  <si>
+    <t>Prueba 180</t>
+  </si>
+  <si>
+    <t>Prueba 181</t>
+  </si>
+  <si>
+    <t>Prueba 182</t>
+  </si>
+  <si>
+    <t>Prueba 183</t>
+  </si>
+  <si>
+    <t>Prueba 184</t>
+  </si>
+  <si>
+    <t>Prueba 185</t>
+  </si>
+  <si>
+    <t>Prueba 186</t>
+  </si>
+  <si>
+    <t>Prueba 187</t>
+  </si>
+  <si>
+    <t>Prueba 188</t>
+  </si>
+  <si>
+    <t>Prueba 189</t>
+  </si>
+  <si>
+    <t>Prueba 190</t>
+  </si>
+  <si>
+    <t>Prueba 191</t>
+  </si>
+  <si>
+    <t>Prueba 192</t>
+  </si>
+  <si>
+    <t>Prueba 193</t>
+  </si>
+  <si>
+    <t>Prueba 194</t>
+  </si>
+  <si>
+    <t>Prueba 195</t>
+  </si>
+  <si>
+    <t>Prueba 196</t>
+  </si>
+  <si>
+    <t>Prueba 197</t>
+  </si>
+  <si>
+    <t>Prueba 198</t>
+  </si>
+  <si>
+    <t>Prueba 199</t>
+  </si>
+  <si>
+    <t>Prueba 200</t>
+  </si>
+  <si>
+    <t>Prueba 201</t>
+  </si>
+  <si>
+    <t>Prueba 202</t>
+  </si>
+  <si>
+    <t>Prueba 203</t>
+  </si>
+  <si>
+    <t>Prueba 204</t>
+  </si>
+  <si>
+    <t>Prueba 205</t>
+  </si>
+  <si>
+    <t>Prueba 206</t>
+  </si>
+  <si>
+    <t>Prueba 207</t>
+  </si>
+  <si>
+    <t>Prueba 208</t>
+  </si>
+  <si>
+    <t>Prueba 209</t>
+  </si>
+  <si>
+    <t>Prueba 210</t>
+  </si>
+  <si>
+    <t>Prueba 211</t>
+  </si>
+  <si>
+    <t>Prueba 212</t>
+  </si>
+  <si>
+    <t>Prueba 213</t>
+  </si>
+  <si>
+    <t>Prueba 214</t>
+  </si>
+  <si>
+    <t>Prueba 215</t>
+  </si>
+  <si>
+    <t>Prueba 216</t>
+  </si>
+  <si>
+    <t>Prueba 217</t>
+  </si>
+  <si>
+    <t>Prueba 218</t>
+  </si>
+  <si>
+    <t>Prueba 219</t>
+  </si>
+  <si>
+    <t>Prueba 220</t>
+  </si>
+  <si>
+    <t>Prueba 221</t>
+  </si>
+  <si>
+    <t>Prueba 222</t>
+  </si>
+  <si>
+    <t>Prueba 223</t>
+  </si>
+  <si>
+    <t>Prueba 224</t>
+  </si>
+  <si>
+    <t>Prueba 225</t>
+  </si>
+  <si>
+    <t>Prueba 226</t>
+  </si>
+  <si>
+    <t>Prueba 227</t>
+  </si>
+  <si>
+    <t>Prueba 228</t>
+  </si>
+  <si>
+    <t>Prueba 229</t>
+  </si>
+  <si>
+    <t>Prueba 230</t>
+  </si>
+  <si>
+    <t>Prueba 231</t>
+  </si>
+  <si>
+    <t>Prueba 232</t>
+  </si>
+  <si>
+    <t>Prueba 233</t>
+  </si>
+  <si>
+    <t>Prueba 234</t>
+  </si>
+  <si>
+    <t>Prueba 235</t>
+  </si>
+  <si>
+    <t>Prueba 236</t>
+  </si>
+  <si>
+    <t>Prueba 237</t>
+  </si>
+  <si>
+    <t>Prueba 238</t>
+  </si>
+  <si>
+    <t>Prueba 239</t>
+  </si>
+  <si>
+    <t>Prueba 240</t>
+  </si>
+  <si>
+    <t>Prueba 241</t>
+  </si>
+  <si>
+    <t>Prueba 242</t>
+  </si>
+  <si>
+    <t>Prueba 243</t>
+  </si>
+  <si>
+    <t>Prueba 244</t>
+  </si>
+  <si>
+    <t>Prueba 245</t>
+  </si>
+  <si>
+    <t>Prueba 246</t>
+  </si>
+  <si>
+    <t>Prueba 247</t>
+  </si>
+  <si>
+    <t>Prueba 248</t>
+  </si>
+  <si>
+    <t>Prueba 249</t>
+  </si>
+  <si>
+    <t>Prueba 250</t>
+  </si>
+  <si>
+    <t>Prueba 251</t>
+  </si>
+  <si>
+    <t>Prueba 252</t>
+  </si>
+  <si>
+    <t>Prueba 253</t>
+  </si>
+  <si>
+    <t>Prueba 254</t>
+  </si>
+  <si>
+    <t>Prueba 255</t>
+  </si>
+  <si>
+    <t>Prueba 256</t>
+  </si>
+  <si>
+    <t>Prueba 257</t>
+  </si>
+  <si>
+    <t>Prueba 258</t>
+  </si>
+  <si>
+    <t>Prueba 259</t>
+  </si>
+  <si>
+    <t>Prueba 260</t>
+  </si>
+  <si>
+    <t>Prueba 261</t>
+  </si>
+  <si>
+    <t>Prueba 262</t>
+  </si>
+  <si>
+    <t>Prueba 263</t>
+  </si>
+  <si>
+    <t>Prueba 264</t>
+  </si>
+  <si>
+    <t>Prueba 265</t>
+  </si>
+  <si>
+    <t>Prueba 266</t>
+  </si>
+  <si>
+    <t>Prueba 267</t>
+  </si>
+  <si>
+    <t>Prueba 268</t>
+  </si>
+  <si>
+    <t>Prueba 269</t>
+  </si>
+  <si>
+    <t>Prueba 270</t>
+  </si>
+  <si>
+    <t>Prueba 271</t>
+  </si>
+  <si>
+    <t>Prueba 272</t>
+  </si>
+  <si>
+    <t>Prueba 273</t>
+  </si>
+  <si>
+    <t>Prueba 274</t>
+  </si>
+  <si>
+    <t>Prueba 275</t>
+  </si>
+  <si>
+    <t>Prueba 276</t>
+  </si>
+  <si>
+    <t>Prueba 277</t>
+  </si>
+  <si>
+    <t>Prueba 278</t>
+  </si>
+  <si>
+    <t>Prueba 279</t>
+  </si>
+  <si>
+    <t>Prueba 280</t>
+  </si>
+  <si>
+    <t>Prueba 281</t>
+  </si>
+  <si>
+    <t>Prueba 282</t>
+  </si>
+  <si>
+    <t>Prueba 283</t>
+  </si>
+  <si>
+    <t>Prueba 284</t>
+  </si>
+  <si>
+    <t>Prueba 285</t>
+  </si>
+  <si>
+    <t>Prueba 286</t>
+  </si>
+  <si>
+    <t>Prueba 287</t>
+  </si>
+  <si>
+    <t>Prueba 288</t>
+  </si>
+  <si>
+    <t>Prueba 289</t>
+  </si>
+  <si>
+    <t>Prueba 290</t>
+  </si>
+  <si>
+    <t>Prueba 291</t>
+  </si>
+  <si>
+    <t>Prueba 292</t>
+  </si>
+  <si>
+    <t>Prueba 293</t>
+  </si>
+  <si>
+    <t>Prueba 294</t>
+  </si>
+  <si>
+    <t>Prueba 295</t>
+  </si>
+  <si>
+    <t>Prueba 296</t>
+  </si>
+  <si>
+    <t>Prueba 297</t>
+  </si>
+  <si>
+    <t>Prueba 298</t>
+  </si>
+  <si>
+    <t>Prueba 299</t>
+  </si>
+  <si>
+    <t>Prueba 300</t>
+  </si>
+  <si>
+    <t>Prueba 301</t>
+  </si>
+  <si>
+    <t>Prueba 302</t>
+  </si>
+  <si>
+    <t>Prueba 303</t>
+  </si>
+  <si>
+    <t>Prueba 304</t>
+  </si>
+  <si>
+    <t>Prueba 305</t>
+  </si>
+  <si>
+    <t>Prueba 306</t>
+  </si>
+  <si>
+    <t>Prueba 307</t>
+  </si>
+  <si>
+    <t>Prueba 308</t>
+  </si>
+  <si>
+    <t>Prueba 309</t>
+  </si>
+  <si>
+    <t>Prueba 310</t>
+  </si>
+  <si>
+    <t>Prueba 311</t>
+  </si>
+  <si>
+    <t>Prueba 312</t>
+  </si>
+  <si>
+    <t>Prueba 313</t>
+  </si>
+  <si>
+    <t>Prueba 314</t>
+  </si>
+  <si>
+    <t>Prueba 315</t>
+  </si>
+  <si>
+    <t>Prueba 316</t>
+  </si>
+  <si>
+    <t>Prueba 317</t>
+  </si>
+  <si>
+    <t>Prueba 318</t>
+  </si>
+  <si>
+    <t>Prueba 319</t>
+  </si>
+  <si>
+    <t>Prueba 320</t>
+  </si>
+  <si>
+    <t>Prueba 321</t>
+  </si>
+  <si>
+    <t>Prueba 322</t>
+  </si>
+  <si>
+    <t>Prueba 323</t>
+  </si>
+  <si>
+    <t>Prueba 324</t>
+  </si>
+  <si>
+    <t>Prueba 325</t>
+  </si>
+  <si>
+    <t>Prueba 326</t>
+  </si>
+  <si>
+    <t>Prueba 327</t>
+  </si>
+  <si>
+    <t>Prueba 328</t>
+  </si>
+  <si>
+    <t>Prueba 329</t>
+  </si>
+  <si>
+    <t>Prueba 330</t>
+  </si>
+  <si>
+    <t>Prueba 331</t>
+  </si>
+  <si>
+    <t>Prueba 332</t>
+  </si>
+  <si>
+    <t>Prueba 333</t>
+  </si>
+  <si>
+    <t>Prueba 334</t>
+  </si>
+  <si>
+    <t>Prueba 335</t>
+  </si>
+  <si>
+    <t>Prueba 336</t>
+  </si>
+  <si>
+    <t>Prueba 337</t>
+  </si>
+  <si>
+    <t>Prueba 338</t>
+  </si>
+  <si>
+    <t>Prueba 339</t>
+  </si>
+  <si>
+    <t>Prueba 340</t>
+  </si>
+  <si>
+    <t>Prueba 341</t>
+  </si>
+  <si>
+    <t>Prueba 342</t>
+  </si>
+  <si>
+    <t>Prueba 343</t>
+  </si>
+  <si>
+    <t>Prueba 344</t>
+  </si>
+  <si>
+    <t>Prueba 345</t>
+  </si>
+  <si>
+    <t>Prueba 346</t>
+  </si>
+  <si>
+    <t>Prueba 347</t>
+  </si>
+  <si>
+    <t>Prueba 348</t>
+  </si>
+  <si>
+    <t>Prueba 349</t>
+  </si>
+  <si>
+    <t>Prueba 350</t>
+  </si>
+  <si>
+    <t>Prueba 351</t>
+  </si>
+  <si>
+    <t>Prueba 352</t>
+  </si>
+  <si>
+    <t>Prueba 353</t>
+  </si>
+  <si>
+    <t>Prueba 354</t>
+  </si>
+  <si>
+    <t>Prueba 355</t>
+  </si>
+  <si>
+    <t>Prueba 356</t>
+  </si>
+  <si>
+    <t>Prueba 357</t>
+  </si>
+  <si>
+    <t>Prueba 358</t>
+  </si>
+  <si>
+    <t>Prueba 359</t>
+  </si>
+  <si>
+    <t>Prueba 360</t>
+  </si>
+  <si>
+    <t>Prueba 361</t>
+  </si>
+  <si>
+    <t>Prueba 362</t>
+  </si>
+  <si>
+    <t>Prueba 363</t>
+  </si>
+  <si>
+    <t>Prueba 364</t>
+  </si>
+  <si>
+    <t>Prueba 365</t>
+  </si>
+  <si>
+    <t>Prueba 366</t>
+  </si>
+  <si>
+    <t>Prueba 367</t>
+  </si>
+  <si>
+    <t>Prueba 368</t>
+  </si>
+  <si>
+    <t>Prueba 369</t>
+  </si>
+  <si>
+    <t>Prueba 370</t>
+  </si>
+  <si>
+    <t>Prueba 371</t>
+  </si>
+  <si>
+    <t>Prueba 372</t>
+  </si>
+  <si>
+    <t>Prueba 373</t>
+  </si>
+  <si>
+    <t>Prueba 374</t>
+  </si>
+  <si>
+    <t>Prueba 375</t>
+  </si>
+  <si>
+    <t>Prueba 376</t>
+  </si>
+  <si>
+    <t>Prueba 377</t>
+  </si>
+  <si>
+    <t>Prueba 378</t>
+  </si>
+  <si>
+    <t>Prueba 379</t>
+  </si>
+  <si>
+    <t>Prueba 380</t>
+  </si>
+  <si>
+    <t>Prueba 381</t>
+  </si>
+  <si>
+    <t>Prueba 382</t>
+  </si>
+  <si>
+    <t>Prueba 383</t>
+  </si>
+  <si>
+    <t>Prueba 384</t>
+  </si>
+  <si>
+    <t>Prueba 385</t>
+  </si>
+  <si>
+    <t>Prueba 386</t>
+  </si>
+  <si>
+    <t>Prueba 387</t>
+  </si>
+  <si>
+    <t>Prueba 388</t>
+  </si>
+  <si>
+    <t>Prueba 389</t>
+  </si>
+  <si>
+    <t>Prueba 390</t>
+  </si>
+  <si>
+    <t>Prueba 391</t>
+  </si>
+  <si>
+    <t>Prueba 392</t>
+  </si>
+  <si>
+    <t>Prueba 393</t>
+  </si>
+  <si>
+    <t>Prueba 394</t>
+  </si>
+  <si>
+    <t>Prueba 395</t>
+  </si>
+  <si>
+    <t>Prueba 396</t>
+  </si>
+  <si>
+    <t>Prueba 397</t>
+  </si>
+  <si>
+    <t>Prueba 398</t>
+  </si>
+  <si>
+    <t>Prueba 399</t>
+  </si>
+  <si>
+    <t>Prueba 400</t>
+  </si>
+  <si>
+    <t>Prueba 401</t>
+  </si>
+  <si>
+    <t>Prueba 402</t>
+  </si>
+  <si>
+    <t>Prueba 403</t>
+  </si>
+  <si>
+    <t>Prueba 404</t>
+  </si>
+  <si>
+    <t>Prueba 405</t>
+  </si>
+  <si>
+    <t>Prueba 406</t>
+  </si>
+  <si>
+    <t>Prueba 407</t>
+  </si>
+  <si>
+    <t>Prueba 408</t>
+  </si>
+  <si>
+    <t>Prueba 409</t>
+  </si>
+  <si>
+    <t>Prueba 410</t>
+  </si>
+  <si>
+    <t>Prueba 411</t>
+  </si>
+  <si>
+    <t>Prueba 412</t>
+  </si>
+  <si>
+    <t>Prueba 413</t>
+  </si>
+  <si>
+    <t>Prueba 414</t>
+  </si>
+  <si>
+    <t>Prueba 415</t>
+  </si>
+  <si>
+    <t>Prueba 416</t>
+  </si>
+  <si>
+    <t>Prueba 417</t>
+  </si>
+  <si>
+    <t>Prueba 418</t>
+  </si>
+  <si>
+    <t>Prueba 419</t>
+  </si>
+  <si>
+    <t>Prueba 420</t>
+  </si>
+  <si>
+    <t>Prueba 421</t>
+  </si>
+  <si>
+    <t>Prueba 422</t>
+  </si>
+  <si>
+    <t>Prueba 423</t>
+  </si>
+  <si>
+    <t>Prueba 424</t>
+  </si>
+  <si>
+    <t>Prueba 425</t>
+  </si>
+  <si>
+    <t>Prueba 426</t>
+  </si>
+  <si>
+    <t>Prueba 427</t>
+  </si>
+  <si>
+    <t>Prueba 428</t>
+  </si>
+  <si>
+    <t>Prueba 429</t>
+  </si>
+  <si>
+    <t>Prueba 430</t>
+  </si>
+  <si>
+    <t>Prueba 431</t>
+  </si>
+  <si>
+    <t>Prueba 432</t>
+  </si>
+  <si>
+    <t>Prueba 433</t>
+  </si>
+  <si>
+    <t>Prueba 434</t>
+  </si>
+  <si>
+    <t>Prueba 435</t>
+  </si>
+  <si>
+    <t>Prueba 436</t>
+  </si>
+  <si>
+    <t>Prueba 437</t>
+  </si>
+  <si>
+    <t>Prueba 438</t>
+  </si>
+  <si>
+    <t>Prueba 439</t>
+  </si>
+  <si>
+    <t>Prueba 440</t>
+  </si>
+  <si>
+    <t>Prueba 441</t>
+  </si>
+  <si>
+    <t>Prueba 442</t>
+  </si>
+  <si>
+    <t>Prueba 443</t>
+  </si>
+  <si>
+    <t>Prueba 444</t>
+  </si>
+  <si>
+    <t>Prueba 445</t>
+  </si>
+  <si>
+    <t>Prueba 446</t>
+  </si>
+  <si>
+    <t>Prueba 447</t>
+  </si>
+  <si>
+    <t>Prueba 448</t>
+  </si>
+  <si>
+    <t>Prueba 449</t>
+  </si>
+  <si>
+    <t>Prueba 450</t>
+  </si>
+  <si>
+    <t>Prueba 451</t>
+  </si>
+  <si>
+    <t>Prueba 452</t>
+  </si>
+  <si>
+    <t>Prueba 453</t>
+  </si>
+  <si>
+    <t>Prueba 454</t>
+  </si>
+  <si>
+    <t>Prueba 455</t>
+  </si>
+  <si>
+    <t>Prueba 456</t>
+  </si>
+  <si>
+    <t>Prueba 457</t>
+  </si>
+  <si>
+    <t>Prueba 458</t>
+  </si>
+  <si>
+    <t>Prueba 459</t>
+  </si>
+  <si>
+    <t>Prueba 460</t>
+  </si>
+  <si>
+    <t>Prueba 461</t>
+  </si>
+  <si>
+    <t>Prueba 462</t>
+  </si>
+  <si>
+    <t>Prueba 463</t>
+  </si>
+  <si>
+    <t>Prueba 464</t>
+  </si>
+  <si>
+    <t>Prueba 465</t>
+  </si>
+  <si>
+    <t>Prueba 466</t>
+  </si>
+  <si>
+    <t>Prueba 467</t>
+  </si>
+  <si>
+    <t>Prueba 468</t>
+  </si>
+  <si>
+    <t>Prueba 469</t>
+  </si>
+  <si>
+    <t>Prueba 470</t>
+  </si>
+  <si>
+    <t>Prueba 471</t>
+  </si>
+  <si>
+    <t>Prueba 472</t>
+  </si>
+  <si>
+    <t>Prueba 473</t>
+  </si>
+  <si>
+    <t>Prueba 474</t>
+  </si>
+  <si>
+    <t>Prueba 475</t>
+  </si>
+  <si>
+    <t>Prueba 476</t>
+  </si>
+  <si>
+    <t>Prueba 477</t>
+  </si>
+  <si>
+    <t>Prueba 478</t>
+  </si>
+  <si>
+    <t>Prueba 479</t>
+  </si>
+  <si>
+    <t>Prueba 480</t>
+  </si>
+  <si>
+    <t>Prueba 481</t>
+  </si>
+  <si>
+    <t>Prueba 482</t>
+  </si>
+  <si>
+    <t>Prueba 483</t>
+  </si>
+  <si>
+    <t>Prueba 484</t>
+  </si>
+  <si>
+    <t>Prueba 485</t>
+  </si>
+  <si>
+    <t>Prueba 486</t>
+  </si>
+  <si>
+    <t>Prueba 487</t>
+  </si>
+  <si>
+    <t>Prueba 488</t>
+  </si>
+  <si>
+    <t>Prueba 489</t>
+  </si>
+  <si>
+    <t>Prueba 490</t>
+  </si>
+  <si>
+    <t>Prueba 491</t>
+  </si>
+  <si>
+    <t>Prueba 492</t>
+  </si>
+  <si>
+    <t>Prueba 493</t>
+  </si>
+  <si>
+    <t>Prueba 494</t>
+  </si>
+  <si>
+    <t>Prueba 495</t>
+  </si>
+  <si>
+    <t>Prueba 496</t>
+  </si>
+  <si>
+    <t>Prueba 497</t>
+  </si>
+  <si>
+    <t>Prueba 498</t>
+  </si>
+  <si>
+    <t>Prueba 499</t>
+  </si>
+  <si>
+    <t>Prueba 500</t>
+  </si>
+  <si>
+    <t>Prueba 501</t>
+  </si>
+  <si>
+    <t>Prueba 502</t>
+  </si>
+  <si>
+    <t>Prueba 503</t>
+  </si>
+  <si>
+    <t>Prueba 504</t>
+  </si>
+  <si>
+    <t>Prueba 505</t>
+  </si>
+  <si>
+    <t>Prueba 506</t>
+  </si>
+  <si>
+    <t>Prueba 507</t>
+  </si>
+  <si>
+    <t>Prueba 508</t>
+  </si>
+  <si>
+    <t>Prueba 509</t>
+  </si>
+  <si>
+    <t>Prueba 510</t>
+  </si>
+  <si>
+    <t>Prueba 511</t>
+  </si>
+  <si>
+    <t>Prueba 512</t>
+  </si>
+  <si>
+    <t>Prueba 513</t>
+  </si>
+  <si>
+    <t>Prueba 514</t>
+  </si>
+  <si>
+    <t>Prueba 515</t>
+  </si>
+  <si>
+    <t>Prueba 516</t>
+  </si>
+  <si>
+    <t>Prueba 517</t>
+  </si>
+  <si>
+    <t>Prueba 518</t>
+  </si>
+  <si>
+    <t>Prueba 519</t>
+  </si>
+  <si>
+    <t>Prueba 520</t>
+  </si>
+  <si>
+    <t>Prueba 521</t>
   </si>
 </sst>
 </file>
@@ -2452,7 +4015,7 @@
     <numFmt numFmtId="170" formatCode="0.000000000"/>
     <numFmt numFmtId="171" formatCode="_-&quot;S/&quot;\ * #,##0_-;\-&quot;S/&quot;\ * #,##0_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="60" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2853,6 +4416,12 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3874,7 +5443,7 @@
     <xf numFmtId="43" fontId="54" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="283">
+  <cellXfs count="282">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4580,9 +6149,6 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4697,6 +6263,12 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="7" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4705,12 +6277,6 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="7" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -10023,9 +11589,7 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Principal" displayName="Principal" ref="B18:BJ539" totalsRowShown="0" headerRowDxfId="122" tableBorderDxfId="121" headerRowCellStyle="Normal 10 2">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B19:BJ539">
-    <sortCondition ref="Y18:Y539"/>
-  </sortState>
+  <autoFilter ref="B18:BJ539" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="61">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="RESPONSABLE DE PRODUCCIÓN" dataDxfId="120" totalsRowDxfId="119"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="GEOGRAFÍA" dataDxfId="118" totalsRowDxfId="117"/>
@@ -19775,25 +21339,25 @@
     </row>
     <row r="2" spans="1:59" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="131"/>
-      <c r="B2" s="274" t="s">
+      <c r="B2" s="273" t="s">
         <v>341</v>
       </c>
-      <c r="C2" s="275"/>
-      <c r="D2" s="275"/>
-      <c r="E2" s="275"/>
-      <c r="F2" s="275"/>
-      <c r="G2" s="281">
+      <c r="C2" s="274"/>
+      <c r="D2" s="274"/>
+      <c r="E2" s="274"/>
+      <c r="F2" s="274"/>
+      <c r="G2" s="277">
         <v>46101</v>
       </c>
     </row>
     <row r="3" spans="1:59" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="131"/>
-      <c r="B3" s="276"/>
-      <c r="C3" s="277"/>
-      <c r="D3" s="277"/>
-      <c r="E3" s="277"/>
-      <c r="F3" s="277"/>
-      <c r="G3" s="282"/>
+      <c r="B3" s="275"/>
+      <c r="C3" s="276"/>
+      <c r="D3" s="276"/>
+      <c r="E3" s="276"/>
+      <c r="F3" s="276"/>
+      <c r="G3" s="278"/>
     </row>
     <row r="4" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A4" s="131"/>
@@ -20041,55 +21605,55 @@
       <c r="M17" s="20"/>
       <c r="N17" s="95"/>
       <c r="O17" s="21"/>
-      <c r="Q17" s="278" t="s">
+      <c r="Q17" s="279" t="s">
         <v>342</v>
       </c>
-      <c r="R17" s="279"/>
-      <c r="S17" s="280"/>
-      <c r="T17" s="278" t="s">
+      <c r="R17" s="280"/>
+      <c r="S17" s="281"/>
+      <c r="T17" s="279" t="s">
         <v>497</v>
       </c>
-      <c r="U17" s="279"/>
-      <c r="V17" s="279"/>
-      <c r="W17" s="279"/>
+      <c r="U17" s="280"/>
+      <c r="V17" s="280"/>
+      <c r="W17" s="280"/>
       <c r="X17" s="28"/>
       <c r="Y17" s="28"/>
       <c r="Z17" s="26"/>
       <c r="AA17" s="26"/>
       <c r="AB17" s="26"/>
-      <c r="AC17" s="273" t="s">
+      <c r="AC17" s="272" t="s">
         <v>331</v>
       </c>
-      <c r="AD17" s="273"/>
-      <c r="AE17" s="273"/>
-      <c r="AF17" s="273"/>
-      <c r="AG17" s="273"/>
-      <c r="AH17" s="273"/>
-      <c r="AI17" s="273"/>
-      <c r="AJ17" s="273"/>
-      <c r="AK17" s="273"/>
-      <c r="AL17" s="273"/>
-      <c r="AM17" s="273"/>
-      <c r="AN17" s="273"/>
-      <c r="AO17" s="273"/>
-      <c r="AP17" s="273"/>
-      <c r="AQ17" s="273"/>
-      <c r="AR17" s="273"/>
-      <c r="AS17" s="273"/>
-      <c r="AT17" s="273"/>
-      <c r="AU17" s="273"/>
-      <c r="AV17" s="273"/>
-      <c r="AW17" s="273"/>
-      <c r="AX17" s="273"/>
-      <c r="AY17" s="273"/>
-      <c r="AZ17" s="273"/>
-      <c r="BA17" s="273"/>
-      <c r="BB17" s="273"/>
-      <c r="BC17" s="273"/>
-      <c r="BD17" s="273"/>
-      <c r="BE17" s="273"/>
-      <c r="BF17" s="273"/>
-      <c r="BG17" s="273"/>
+      <c r="AD17" s="272"/>
+      <c r="AE17" s="272"/>
+      <c r="AF17" s="272"/>
+      <c r="AG17" s="272"/>
+      <c r="AH17" s="272"/>
+      <c r="AI17" s="272"/>
+      <c r="AJ17" s="272"/>
+      <c r="AK17" s="272"/>
+      <c r="AL17" s="272"/>
+      <c r="AM17" s="272"/>
+      <c r="AN17" s="272"/>
+      <c r="AO17" s="272"/>
+      <c r="AP17" s="272"/>
+      <c r="AQ17" s="272"/>
+      <c r="AR17" s="272"/>
+      <c r="AS17" s="272"/>
+      <c r="AT17" s="272"/>
+      <c r="AU17" s="272"/>
+      <c r="AV17" s="272"/>
+      <c r="AW17" s="272"/>
+      <c r="AX17" s="272"/>
+      <c r="AY17" s="272"/>
+      <c r="AZ17" s="272"/>
+      <c r="BA17" s="272"/>
+      <c r="BB17" s="272"/>
+      <c r="BC17" s="272"/>
+      <c r="BD17" s="272"/>
+      <c r="BE17" s="272"/>
+      <c r="BF17" s="272"/>
+      <c r="BG17" s="272"/>
       <c r="BH17" s="7"/>
     </row>
     <row r="18" spans="1:62" ht="41.4" x14ac:dyDescent="0.3">
@@ -20396,7 +21960,9 @@
       <c r="BG19" s="71"/>
       <c r="BH19" s="71"/>
       <c r="BI19" s="158"/>
-      <c r="BJ19" s="31"/>
+      <c r="BJ19" s="31" t="s">
+        <v>796</v>
+      </c>
     </row>
     <row r="20" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="131"/>
@@ -20516,7 +22082,9 @@
       <c r="BG20" s="71"/>
       <c r="BH20" s="71"/>
       <c r="BI20" s="2"/>
-      <c r="BJ20" s="31"/>
+      <c r="BJ20" s="31" t="s">
+        <v>797</v>
+      </c>
     </row>
     <row r="21" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="131"/>
@@ -20538,7 +22106,7 @@
       <c r="G21" s="229" t="s">
         <v>786</v>
       </c>
-      <c r="H21" s="254">
+      <c r="H21" s="253">
         <v>7.000000000000001E-4</v>
       </c>
       <c r="I21" s="162">
@@ -20636,7 +22204,9 @@
       <c r="BG21" s="71"/>
       <c r="BH21" s="71"/>
       <c r="BI21" s="2"/>
-      <c r="BJ21" s="31"/>
+      <c r="BJ21" s="31" t="s">
+        <v>798</v>
+      </c>
     </row>
     <row r="22" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="131"/>
@@ -20658,7 +22228,7 @@
       <c r="G22" s="229" t="s">
         <v>787</v>
       </c>
-      <c r="H22" s="254">
+      <c r="H22" s="253">
         <v>3.3E-4</v>
       </c>
       <c r="I22" s="162">
@@ -20756,7 +22326,9 @@
       <c r="BG22" s="71"/>
       <c r="BH22" s="71"/>
       <c r="BI22" s="2"/>
-      <c r="BJ22" s="31"/>
+      <c r="BJ22" s="31" t="s">
+        <v>799</v>
+      </c>
     </row>
     <row r="23" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="131"/>
@@ -20772,13 +22344,13 @@
       <c r="E23" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="F23" s="245">
+      <c r="F23" s="244">
         <v>1080745</v>
       </c>
-      <c r="G23" s="251" t="s">
+      <c r="G23" s="250" t="s">
         <v>788</v>
       </c>
-      <c r="H23" s="254">
+      <c r="H23" s="253">
         <v>862</v>
       </c>
       <c r="I23" s="162">
@@ -20876,7 +22448,9 @@
       <c r="BG23" s="71"/>
       <c r="BH23" s="71"/>
       <c r="BI23" s="2"/>
-      <c r="BJ23" s="31"/>
+      <c r="BJ23" s="31" t="s">
+        <v>800</v>
+      </c>
     </row>
     <row r="24" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="131"/>
@@ -20892,13 +22466,13 @@
       <c r="E24" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="F24" s="264">
+      <c r="F24" s="263">
         <v>1083381</v>
       </c>
-      <c r="G24" s="265" t="s">
+      <c r="G24" s="264" t="s">
         <v>790</v>
       </c>
-      <c r="H24" s="256">
+      <c r="H24" s="255">
         <v>57600</v>
       </c>
       <c r="I24" s="162">
@@ -20996,7 +22570,9 @@
       <c r="BG24" s="71"/>
       <c r="BH24" s="71"/>
       <c r="BI24" s="2"/>
-      <c r="BJ24" s="31"/>
+      <c r="BJ24" s="31" t="s">
+        <v>801</v>
+      </c>
     </row>
     <row r="25" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="131"/>
@@ -21120,7 +22696,9 @@
       <c r="BI25" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ25" s="31"/>
+      <c r="BJ25" s="31" t="s">
+        <v>802</v>
+      </c>
     </row>
     <row r="26" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="131"/>
@@ -21244,7 +22822,9 @@
       <c r="BI26" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ26" s="31"/>
+      <c r="BJ26" s="31" t="s">
+        <v>803</v>
+      </c>
     </row>
     <row r="27" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="131"/>
@@ -21364,7 +22944,9 @@
       <c r="BG27" s="71"/>
       <c r="BH27" s="71"/>
       <c r="BI27" s="158"/>
-      <c r="BJ27" s="31"/>
+      <c r="BJ27" s="31" t="s">
+        <v>804</v>
+      </c>
     </row>
     <row r="28" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="131"/>
@@ -21488,7 +23070,9 @@
       <c r="BI28" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ28" s="31"/>
+      <c r="BJ28" s="31" t="s">
+        <v>805</v>
+      </c>
     </row>
     <row r="29" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="131"/>
@@ -21612,7 +23196,9 @@
       <c r="BI29" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ29" s="31"/>
+      <c r="BJ29" s="31" t="s">
+        <v>806</v>
+      </c>
     </row>
     <row r="30" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="131"/>
@@ -21734,7 +23320,9 @@
       <c r="BI30" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ30" s="31"/>
+      <c r="BJ30" s="31" t="s">
+        <v>807</v>
+      </c>
     </row>
     <row r="31" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="131"/>
@@ -21750,10 +23338,10 @@
       <c r="E31" s="133" t="s">
         <v>398</v>
       </c>
-      <c r="F31" s="264">
+      <c r="F31" s="263">
         <v>1058451</v>
       </c>
-      <c r="G31" s="266" t="s">
+      <c r="G31" s="265" t="s">
         <v>268</v>
       </c>
       <c r="H31" s="162">
@@ -21856,7 +23444,9 @@
       <c r="BI31" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ31" s="31"/>
+      <c r="BJ31" s="31" t="s">
+        <v>808</v>
+      </c>
     </row>
     <row r="32" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="131"/>
@@ -21872,10 +23462,10 @@
       <c r="E32" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="F32" s="264">
+      <c r="F32" s="263">
         <v>1024997</v>
       </c>
-      <c r="G32" s="266" t="s">
+      <c r="G32" s="265" t="s">
         <v>62</v>
       </c>
       <c r="H32" s="162">
@@ -21980,7 +23570,9 @@
       <c r="BI32" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ32" s="31"/>
+      <c r="BJ32" s="31" t="s">
+        <v>809</v>
+      </c>
     </row>
     <row r="33" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="131"/>
@@ -22102,7 +23694,9 @@
       <c r="BI33" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ33" s="31"/>
+      <c r="BJ33" s="31" t="s">
+        <v>810</v>
+      </c>
     </row>
     <row r="34" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="131"/>
@@ -22224,7 +23818,9 @@
       <c r="BI34" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ34" s="31"/>
+      <c r="BJ34" s="31" t="s">
+        <v>811</v>
+      </c>
     </row>
     <row r="35" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="131"/>
@@ -22344,7 +23940,9 @@
       <c r="BG35" s="71"/>
       <c r="BH35" s="71"/>
       <c r="BI35" s="158"/>
-      <c r="BJ35" s="31"/>
+      <c r="BJ35" s="31" t="s">
+        <v>812</v>
+      </c>
     </row>
     <row r="36" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="131"/>
@@ -22468,7 +24066,9 @@
       <c r="BI36" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ36" s="31"/>
+      <c r="BJ36" s="31" t="s">
+        <v>813</v>
+      </c>
     </row>
     <row r="37" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="131"/>
@@ -22590,7 +24190,9 @@
       <c r="BI37" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ37" s="31"/>
+      <c r="BJ37" s="31" t="s">
+        <v>814</v>
+      </c>
     </row>
     <row r="38" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="131"/>
@@ -22714,7 +24316,9 @@
       <c r="BI38" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ38" s="31"/>
+      <c r="BJ38" s="31" t="s">
+        <v>815</v>
+      </c>
     </row>
     <row r="39" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="131"/>
@@ -22834,7 +24438,9 @@
       <c r="BG39" s="71"/>
       <c r="BH39" s="71"/>
       <c r="BI39" s="2"/>
-      <c r="BJ39" s="31"/>
+      <c r="BJ39" s="31" t="s">
+        <v>816</v>
+      </c>
     </row>
     <row r="40" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="131"/>
@@ -22958,7 +24564,9 @@
       <c r="BI40" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ40" s="31"/>
+      <c r="BJ40" s="31" t="s">
+        <v>817</v>
+      </c>
     </row>
     <row r="41" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="131"/>
@@ -22974,10 +24582,10 @@
       <c r="E41" s="133" t="s">
         <v>400</v>
       </c>
-      <c r="F41" s="269">
+      <c r="F41" s="268">
         <v>1024998</v>
       </c>
-      <c r="G41" s="270" t="s">
+      <c r="G41" s="269" t="s">
         <v>321</v>
       </c>
       <c r="H41" s="162">
@@ -23080,7 +24688,9 @@
       <c r="BI41" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ41" s="31"/>
+      <c r="BJ41" s="31" t="s">
+        <v>818</v>
+      </c>
     </row>
     <row r="42" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="131"/>
@@ -23202,7 +24812,9 @@
       <c r="BI42" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ42" s="31"/>
+      <c r="BJ42" s="31" t="s">
+        <v>819</v>
+      </c>
     </row>
     <row r="43" spans="1:62" ht="12.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="131"/>
@@ -23322,7 +24934,9 @@
       <c r="BG43" s="71"/>
       <c r="BH43" s="71"/>
       <c r="BI43" s="2"/>
-      <c r="BJ43" s="31"/>
+      <c r="BJ43" s="31" t="s">
+        <v>820</v>
+      </c>
     </row>
     <row r="44" spans="1:62" ht="12.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="131"/>
@@ -23446,7 +25060,9 @@
       <c r="BI44" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ44" s="31"/>
+      <c r="BJ44" s="31" t="s">
+        <v>821</v>
+      </c>
     </row>
     <row r="45" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="131"/>
@@ -23566,7 +25182,9 @@
       <c r="BG45" s="71"/>
       <c r="BH45" s="71"/>
       <c r="BI45" s="158"/>
-      <c r="BJ45" s="31"/>
+      <c r="BJ45" s="31" t="s">
+        <v>822</v>
+      </c>
     </row>
     <row r="46" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="131"/>
@@ -23688,7 +25306,9 @@
       <c r="BI46" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ46" s="31"/>
+      <c r="BJ46" s="31" t="s">
+        <v>823</v>
+      </c>
     </row>
     <row r="47" spans="1:62" ht="12.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="131"/>
@@ -23810,7 +25430,9 @@
       <c r="BI47" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ47" s="31"/>
+      <c r="BJ47" s="31" t="s">
+        <v>824</v>
+      </c>
     </row>
     <row r="48" spans="1:62" ht="12.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="131"/>
@@ -23934,7 +25556,9 @@
       <c r="BI48" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ48" s="31"/>
+      <c r="BJ48" s="31" t="s">
+        <v>825</v>
+      </c>
     </row>
     <row r="49" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="131"/>
@@ -24056,7 +25680,9 @@
       <c r="BI49" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ49" s="31"/>
+      <c r="BJ49" s="31" t="s">
+        <v>826</v>
+      </c>
     </row>
     <row r="50" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="131"/>
@@ -24072,10 +25698,10 @@
       <c r="E50" s="133" t="s">
         <v>403</v>
       </c>
-      <c r="F50" s="269">
+      <c r="F50" s="268">
         <v>1076300</v>
       </c>
-      <c r="G50" s="270" t="s">
+      <c r="G50" s="269" t="s">
         <v>690</v>
       </c>
       <c r="H50" s="162">
@@ -24180,7 +25806,9 @@
       <c r="BI50" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ50" s="31"/>
+      <c r="BJ50" s="31" t="s">
+        <v>827</v>
+      </c>
     </row>
     <row r="51" spans="1:62" ht="12.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="131"/>
@@ -24196,10 +25824,10 @@
       <c r="E51" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="F51" s="267">
+      <c r="F51" s="266">
         <v>1083117</v>
       </c>
-      <c r="G51" s="268" t="s">
+      <c r="G51" s="267" t="s">
         <v>779</v>
       </c>
       <c r="H51" s="162">
@@ -24300,7 +25928,9 @@
       <c r="BG51" s="71"/>
       <c r="BH51" s="71"/>
       <c r="BI51" s="2"/>
-      <c r="BJ51" s="31"/>
+      <c r="BJ51" s="31" t="s">
+        <v>828</v>
+      </c>
     </row>
     <row r="52" spans="1:62" ht="12.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="131"/>
@@ -24424,7 +26054,9 @@
       <c r="BI52" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ52" s="31"/>
+      <c r="BJ52" s="31" t="s">
+        <v>829</v>
+      </c>
     </row>
     <row r="53" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="131"/>
@@ -24546,7 +26178,9 @@
       <c r="BI53" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ53" s="31"/>
+      <c r="BJ53" s="31" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="54" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="131"/>
@@ -24670,7 +26304,9 @@
       <c r="BI54" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ54" s="31"/>
+      <c r="BJ54" s="31" t="s">
+        <v>831</v>
+      </c>
     </row>
     <row r="55" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="131"/>
@@ -24689,7 +26325,7 @@
       <c r="F55" s="217">
         <v>1060797</v>
       </c>
-      <c r="G55" s="272" t="s">
+      <c r="G55" s="271" t="s">
         <v>434</v>
       </c>
       <c r="H55" s="162">
@@ -24794,7 +26430,9 @@
       <c r="BI55" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ55" s="31"/>
+      <c r="BJ55" s="31" t="s">
+        <v>832</v>
+      </c>
     </row>
     <row r="56" spans="1:62" ht="12.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="131"/>
@@ -24810,10 +26448,10 @@
       <c r="E56" s="133" t="s">
         <v>313</v>
       </c>
-      <c r="F56" s="264">
+      <c r="F56" s="263">
         <v>1072351</v>
       </c>
-      <c r="G56" s="266" t="s">
+      <c r="G56" s="265" t="s">
         <v>595</v>
       </c>
       <c r="H56" s="162">
@@ -24916,7 +26554,9 @@
       <c r="BI56" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ56" s="31"/>
+      <c r="BJ56" s="31" t="s">
+        <v>833</v>
+      </c>
     </row>
     <row r="57" spans="1:62" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="131"/>
@@ -25040,7 +26680,9 @@
       <c r="BI57" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ57" s="31"/>
+      <c r="BJ57" s="31" t="s">
+        <v>834</v>
+      </c>
     </row>
     <row r="58" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="131"/>
@@ -25059,7 +26701,7 @@
       <c r="F58" s="217">
         <v>1058339</v>
       </c>
-      <c r="G58" s="272" t="s">
+      <c r="G58" s="271" t="s">
         <v>232</v>
       </c>
       <c r="H58" s="162">
@@ -25162,7 +26804,9 @@
       <c r="BI58" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ58" s="31"/>
+      <c r="BJ58" s="31" t="s">
+        <v>835</v>
+      </c>
     </row>
     <row r="59" spans="1:62" ht="12.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="131"/>
@@ -25286,7 +26930,9 @@
       <c r="BI59" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ59" s="31"/>
+      <c r="BJ59" s="31" t="s">
+        <v>836</v>
+      </c>
     </row>
     <row r="60" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="131"/>
@@ -25408,7 +27054,9 @@
       <c r="BI60" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ60" s="31"/>
+      <c r="BJ60" s="31" t="s">
+        <v>837</v>
+      </c>
     </row>
     <row r="61" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="131"/>
@@ -25424,10 +27072,10 @@
       <c r="E61" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="F61" s="264">
+      <c r="F61" s="263">
         <v>1068805</v>
       </c>
-      <c r="G61" s="266" t="s">
+      <c r="G61" s="265" t="s">
         <v>564</v>
       </c>
       <c r="H61" s="162">
@@ -25532,7 +27180,9 @@
       <c r="BI61" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ61" s="31"/>
+      <c r="BJ61" s="31" t="s">
+        <v>838</v>
+      </c>
     </row>
     <row r="62" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="131"/>
@@ -25656,7 +27306,9 @@
       <c r="BI62" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ62" s="31"/>
+      <c r="BJ62" s="31" t="s">
+        <v>839</v>
+      </c>
     </row>
     <row r="63" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="131"/>
@@ -25776,7 +27428,9 @@
       <c r="BG63" s="71"/>
       <c r="BH63" s="71"/>
       <c r="BI63" s="158"/>
-      <c r="BJ63" s="31"/>
+      <c r="BJ63" s="31" t="s">
+        <v>840</v>
+      </c>
     </row>
     <row r="64" spans="1:62" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="131"/>
@@ -25792,10 +27446,10 @@
       <c r="E64" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="F64" s="267">
+      <c r="F64" s="266">
         <v>1080747</v>
       </c>
-      <c r="G64" s="271" t="s">
+      <c r="G64" s="270" t="s">
         <v>782</v>
       </c>
       <c r="H64" s="162">
@@ -25896,7 +27550,9 @@
       <c r="BG64" s="71"/>
       <c r="BH64" s="71"/>
       <c r="BI64" s="2"/>
-      <c r="BJ64" s="31"/>
+      <c r="BJ64" s="31" t="s">
+        <v>841</v>
+      </c>
     </row>
     <row r="65" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="131"/>
@@ -25912,10 +27568,10 @@
       <c r="E65" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="F65" s="264">
+      <c r="F65" s="263">
         <v>1074077</v>
       </c>
-      <c r="G65" s="266" t="s">
+      <c r="G65" s="265" t="s">
         <v>696</v>
       </c>
       <c r="H65" s="162">
@@ -26020,7 +27676,9 @@
       <c r="BI65" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ65" s="31"/>
+      <c r="BJ65" s="31" t="s">
+        <v>842</v>
+      </c>
     </row>
     <row r="66" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="131"/>
@@ -26142,7 +27800,9 @@
       <c r="BI66" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ66" s="31"/>
+      <c r="BJ66" s="31" t="s">
+        <v>843</v>
+      </c>
     </row>
     <row r="67" spans="1:62" ht="12.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="131"/>
@@ -26158,10 +27818,10 @@
       <c r="E67" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="F67" s="266">
+      <c r="F67" s="265">
         <v>1083041</v>
       </c>
-      <c r="G67" s="266" t="s">
+      <c r="G67" s="265" t="s">
         <v>784</v>
       </c>
       <c r="H67" s="162">
@@ -26262,7 +27922,9 @@
       <c r="BG67" s="71"/>
       <c r="BH67" s="71"/>
       <c r="BI67" s="2"/>
-      <c r="BJ67" s="31"/>
+      <c r="BJ67" s="31" t="s">
+        <v>844</v>
+      </c>
     </row>
     <row r="68" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="131"/>
@@ -26386,7 +28048,9 @@
       <c r="BI68" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ68" s="31"/>
+      <c r="BJ68" s="31" t="s">
+        <v>845</v>
+      </c>
     </row>
     <row r="69" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="131"/>
@@ -26510,7 +28174,9 @@
       <c r="BI69" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ69" s="31"/>
+      <c r="BJ69" s="31" t="s">
+        <v>846</v>
+      </c>
     </row>
     <row r="70" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="131"/>
@@ -26634,7 +28300,9 @@
       <c r="BI70" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ70" s="31"/>
+      <c r="BJ70" s="31" t="s">
+        <v>847</v>
+      </c>
     </row>
     <row r="71" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="131"/>
@@ -26758,7 +28426,9 @@
       <c r="BI71" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ71" s="31"/>
+      <c r="BJ71" s="31" t="s">
+        <v>848</v>
+      </c>
     </row>
     <row r="72" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="131"/>
@@ -26774,10 +28444,10 @@
       <c r="E72" s="133" t="s">
         <v>307</v>
       </c>
-      <c r="F72" s="264">
+      <c r="F72" s="263">
         <v>1071764</v>
       </c>
-      <c r="G72" s="266" t="s">
+      <c r="G72" s="265" t="s">
         <v>604</v>
       </c>
       <c r="H72" s="162">
@@ -26882,7 +28552,9 @@
       <c r="BI72" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ72" s="31"/>
+      <c r="BJ72" s="31" t="s">
+        <v>849</v>
+      </c>
     </row>
     <row r="73" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="131"/>
@@ -27004,7 +28676,9 @@
       <c r="BI73" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ73" s="31"/>
+      <c r="BJ73" s="31" t="s">
+        <v>850</v>
+      </c>
     </row>
     <row r="74" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="131"/>
@@ -27124,7 +28798,9 @@
       <c r="BG74" s="71"/>
       <c r="BH74" s="71"/>
       <c r="BI74" s="2"/>
-      <c r="BJ74" s="31"/>
+      <c r="BJ74" s="31" t="s">
+        <v>851</v>
+      </c>
     </row>
     <row r="75" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="30" t="s">
@@ -27245,7 +28921,9 @@
       <c r="BI75" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ75" s="31"/>
+      <c r="BJ75" s="31" t="s">
+        <v>852</v>
+      </c>
     </row>
     <row r="76" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="131"/>
@@ -27367,7 +29045,9 @@
       <c r="BI76" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ76" s="31"/>
+      <c r="BJ76" s="31" t="s">
+        <v>853</v>
+      </c>
     </row>
     <row r="77" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="131"/>
@@ -27487,7 +29167,9 @@
       <c r="BG77" s="71"/>
       <c r="BH77" s="71"/>
       <c r="BI77" s="158"/>
-      <c r="BJ77" s="31"/>
+      <c r="BJ77" s="31" t="s">
+        <v>854</v>
+      </c>
     </row>
     <row r="78" spans="1:62" ht="12.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="131"/>
@@ -27607,7 +29289,9 @@
       <c r="BG78" s="71"/>
       <c r="BH78" s="71"/>
       <c r="BI78" s="2"/>
-      <c r="BJ78" s="31"/>
+      <c r="BJ78" s="31" t="s">
+        <v>855</v>
+      </c>
     </row>
     <row r="79" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="131"/>
@@ -27727,7 +29411,9 @@
       <c r="BG79" s="71"/>
       <c r="BH79" s="71"/>
       <c r="BI79" s="158"/>
-      <c r="BJ79" s="31"/>
+      <c r="BJ79" s="31" t="s">
+        <v>856</v>
+      </c>
     </row>
     <row r="80" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="131"/>
@@ -27743,10 +29429,10 @@
       <c r="E80" s="133" t="s">
         <v>403</v>
       </c>
-      <c r="F80" s="264">
+      <c r="F80" s="263">
         <v>1076301</v>
       </c>
-      <c r="G80" s="266" t="s">
+      <c r="G80" s="265" t="s">
         <v>691</v>
       </c>
       <c r="H80" s="162">
@@ -27849,7 +29535,9 @@
       <c r="BI80" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ80" s="31"/>
+      <c r="BJ80" s="31" t="s">
+        <v>857</v>
+      </c>
     </row>
     <row r="81" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="131"/>
@@ -27973,7 +29661,9 @@
       <c r="BI81" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ81" s="31"/>
+      <c r="BJ81" s="31" t="s">
+        <v>858</v>
+      </c>
     </row>
     <row r="82" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="131"/>
@@ -28097,7 +29787,9 @@
       <c r="BI82" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ82" s="31"/>
+      <c r="BJ82" s="31" t="s">
+        <v>859</v>
+      </c>
     </row>
     <row r="83" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="131"/>
@@ -28221,7 +29913,9 @@
       <c r="BI83" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ83" s="31"/>
+      <c r="BJ83" s="31" t="s">
+        <v>860</v>
+      </c>
     </row>
     <row r="84" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="131"/>
@@ -28237,10 +29931,10 @@
       <c r="E84" s="133" t="s">
         <v>313</v>
       </c>
-      <c r="F84" s="264">
+      <c r="F84" s="263">
         <v>1072813</v>
       </c>
-      <c r="G84" s="266" t="s">
+      <c r="G84" s="265" t="s">
         <v>612</v>
       </c>
       <c r="H84" s="162">
@@ -28341,7 +30035,9 @@
       <c r="BG84" s="71"/>
       <c r="BH84" s="71"/>
       <c r="BI84" s="158"/>
-      <c r="BJ84" s="31"/>
+      <c r="BJ84" s="31" t="s">
+        <v>861</v>
+      </c>
     </row>
     <row r="85" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="131"/>
@@ -28461,7 +30157,9 @@
       <c r="BG85" s="136"/>
       <c r="BH85" s="136"/>
       <c r="BI85" s="2"/>
-      <c r="BJ85" s="31"/>
+      <c r="BJ85" s="31" t="s">
+        <v>862</v>
+      </c>
     </row>
     <row r="86" spans="1:62" ht="12.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="131"/>
@@ -28585,7 +30283,9 @@
       <c r="BI86" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ86" s="31"/>
+      <c r="BJ86" s="31" t="s">
+        <v>863</v>
+      </c>
     </row>
     <row r="87" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="131"/>
@@ -28709,7 +30409,9 @@
       <c r="BI87" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ87" s="31"/>
+      <c r="BJ87" s="31" t="s">
+        <v>864</v>
+      </c>
     </row>
     <row r="88" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="131"/>
@@ -28725,10 +30427,10 @@
       <c r="E88" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="F88" s="264">
+      <c r="F88" s="263">
         <v>1060800</v>
       </c>
-      <c r="G88" s="266" t="s">
+      <c r="G88" s="265" t="s">
         <v>437</v>
       </c>
       <c r="H88" s="162">
@@ -28833,7 +30535,9 @@
       <c r="BI88" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ88" s="31"/>
+      <c r="BJ88" s="31" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="89" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="131"/>
@@ -28957,7 +30661,9 @@
       <c r="BI89" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ89" s="31"/>
+      <c r="BJ89" s="31" t="s">
+        <v>866</v>
+      </c>
     </row>
     <row r="90" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="131"/>
@@ -29081,7 +30787,9 @@
       <c r="BI90" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ90" s="31"/>
+      <c r="BJ90" s="31" t="s">
+        <v>867</v>
+      </c>
     </row>
     <row r="91" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="131"/>
@@ -29203,7 +30911,9 @@
       <c r="BI91" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ91" s="31"/>
+      <c r="BJ91" s="31" t="s">
+        <v>868</v>
+      </c>
     </row>
     <row r="92" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="131"/>
@@ -29219,10 +30929,10 @@
       <c r="E92" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="F92" s="264">
+      <c r="F92" s="263">
         <v>1072353</v>
       </c>
-      <c r="G92" s="266" t="s">
+      <c r="G92" s="265" t="s">
         <v>598</v>
       </c>
       <c r="H92" s="162">
@@ -29323,7 +31033,9 @@
       <c r="BG92" s="71"/>
       <c r="BH92" s="71"/>
       <c r="BI92" s="2"/>
-      <c r="BJ92" s="31"/>
+      <c r="BJ92" s="31" t="s">
+        <v>869</v>
+      </c>
     </row>
     <row r="93" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="131"/>
@@ -29445,7 +31157,9 @@
       <c r="BI93" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ93" s="31"/>
+      <c r="BJ93" s="31" t="s">
+        <v>870</v>
+      </c>
     </row>
     <row r="94" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="131"/>
@@ -29569,7 +31283,9 @@
       <c r="BI94" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ94" s="31"/>
+      <c r="BJ94" s="31" t="s">
+        <v>871</v>
+      </c>
     </row>
     <row r="95" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="131"/>
@@ -29691,7 +31407,9 @@
       <c r="BI95" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ95" s="31"/>
+      <c r="BJ95" s="31" t="s">
+        <v>872</v>
+      </c>
     </row>
     <row r="96" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="131"/>
@@ -29813,7 +31531,9 @@
       <c r="BI96" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ96" s="31"/>
+      <c r="BJ96" s="31" t="s">
+        <v>873</v>
+      </c>
     </row>
     <row r="97" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="131"/>
@@ -29937,7 +31657,9 @@
       <c r="BI97" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ97" s="31"/>
+      <c r="BJ97" s="31" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="98" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="131"/>
@@ -30057,7 +31779,9 @@
       <c r="BG98" s="71"/>
       <c r="BH98" s="71"/>
       <c r="BI98" s="158"/>
-      <c r="BJ98" s="31"/>
+      <c r="BJ98" s="31" t="s">
+        <v>875</v>
+      </c>
     </row>
     <row r="99" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="131"/>
@@ -30181,7 +31905,9 @@
       <c r="BI99" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ99" s="31"/>
+      <c r="BJ99" s="31" t="s">
+        <v>876</v>
+      </c>
     </row>
     <row r="100" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="131"/>
@@ -30305,7 +32031,9 @@
       <c r="BI100" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ100" s="31"/>
+      <c r="BJ100" s="31" t="s">
+        <v>877</v>
+      </c>
     </row>
     <row r="101" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="131"/>
@@ -30425,7 +32153,9 @@
       <c r="BG101" s="71"/>
       <c r="BH101" s="71"/>
       <c r="BI101" s="2"/>
-      <c r="BJ101" s="31"/>
+      <c r="BJ101" s="31" t="s">
+        <v>878</v>
+      </c>
     </row>
     <row r="102" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="131"/>
@@ -30547,7 +32277,9 @@
       <c r="BI102" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ102" s="31"/>
+      <c r="BJ102" s="31" t="s">
+        <v>879</v>
+      </c>
     </row>
     <row r="103" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="131"/>
@@ -30667,7 +32399,9 @@
       <c r="BG103" s="71"/>
       <c r="BH103" s="71"/>
       <c r="BI103" s="158"/>
-      <c r="BJ103" s="31"/>
+      <c r="BJ103" s="31" t="s">
+        <v>880</v>
+      </c>
     </row>
     <row r="104" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="131"/>
@@ -30791,7 +32525,9 @@
       <c r="BI104" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ104" s="31"/>
+      <c r="BJ104" s="31" t="s">
+        <v>881</v>
+      </c>
     </row>
     <row r="105" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="131"/>
@@ -30911,7 +32647,9 @@
       <c r="BG105" s="71"/>
       <c r="BH105" s="71"/>
       <c r="BI105" s="2"/>
-      <c r="BJ105" s="31"/>
+      <c r="BJ105" s="31" t="s">
+        <v>882</v>
+      </c>
     </row>
     <row r="106" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="131"/>
@@ -31033,7 +32771,9 @@
       <c r="BI106" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ106" s="31"/>
+      <c r="BJ106" s="31" t="s">
+        <v>883</v>
+      </c>
     </row>
     <row r="107" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="131"/>
@@ -31049,10 +32789,10 @@
       <c r="E107" s="133" t="s">
         <v>313</v>
       </c>
-      <c r="F107" s="269">
+      <c r="F107" s="268">
         <v>1072352</v>
       </c>
-      <c r="G107" s="270" t="s">
+      <c r="G107" s="269" t="s">
         <v>592</v>
       </c>
       <c r="H107" s="162">
@@ -31153,7 +32893,9 @@
       <c r="BG107" s="71"/>
       <c r="BH107" s="71"/>
       <c r="BI107" s="158"/>
-      <c r="BJ107" s="31"/>
+      <c r="BJ107" s="31" t="s">
+        <v>884</v>
+      </c>
     </row>
     <row r="108" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="131"/>
@@ -31169,10 +32911,10 @@
       <c r="E108" s="133" t="s">
         <v>311</v>
       </c>
-      <c r="F108" s="264">
+      <c r="F108" s="263">
         <v>1080750</v>
       </c>
-      <c r="G108" s="266" t="s">
+      <c r="G108" s="265" t="s">
         <v>770</v>
       </c>
       <c r="H108" s="162">
@@ -31273,7 +33015,9 @@
       <c r="BG108" s="71"/>
       <c r="BH108" s="71"/>
       <c r="BI108" s="158"/>
-      <c r="BJ108" s="31"/>
+      <c r="BJ108" s="31" t="s">
+        <v>885</v>
+      </c>
     </row>
     <row r="109" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="131"/>
@@ -31289,10 +33033,10 @@
       <c r="E109" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="F109" s="267">
+      <c r="F109" s="266">
         <v>1082951</v>
       </c>
-      <c r="G109" s="268" t="s">
+      <c r="G109" s="267" t="s">
         <v>783</v>
       </c>
       <c r="H109" s="162">
@@ -31393,7 +33137,9 @@
       <c r="BG109" s="71"/>
       <c r="BH109" s="71"/>
       <c r="BI109" s="2"/>
-      <c r="BJ109" s="31"/>
+      <c r="BJ109" s="31" t="s">
+        <v>886</v>
+      </c>
     </row>
     <row r="110" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="131"/>
@@ -31517,7 +33263,9 @@
       <c r="BI110" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ110" s="31"/>
+      <c r="BJ110" s="31" t="s">
+        <v>887</v>
+      </c>
     </row>
     <row r="111" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="131"/>
@@ -31533,10 +33281,10 @@
       <c r="E111" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="F111" s="266">
+      <c r="F111" s="265">
         <v>1069728</v>
       </c>
-      <c r="G111" s="266" t="s">
+      <c r="G111" s="265" t="s">
         <v>568</v>
       </c>
       <c r="H111" s="162">
@@ -31641,7 +33389,9 @@
       <c r="BI111" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ111" s="31"/>
+      <c r="BJ111" s="31" t="s">
+        <v>888</v>
+      </c>
     </row>
     <row r="112" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="131"/>
@@ -31761,7 +33511,9 @@
       <c r="BG112" s="71"/>
       <c r="BH112" s="71"/>
       <c r="BI112" s="158"/>
-      <c r="BJ112" s="31"/>
+      <c r="BJ112" s="31" t="s">
+        <v>889</v>
+      </c>
     </row>
     <row r="113" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="131"/>
@@ -31885,7 +33637,9 @@
       <c r="BI113" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ113" s="31"/>
+      <c r="BJ113" s="31" t="s">
+        <v>890</v>
+      </c>
     </row>
     <row r="114" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A114" s="131"/>
@@ -32009,7 +33763,9 @@
       <c r="BI114" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ114" s="31"/>
+      <c r="BJ114" s="31" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="115" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="131"/>
@@ -32025,10 +33781,10 @@
       <c r="E115" s="133" t="s">
         <v>314</v>
       </c>
-      <c r="F115" s="269">
+      <c r="F115" s="268">
         <v>1083252</v>
       </c>
-      <c r="G115" s="270" t="s">
+      <c r="G115" s="269" t="s">
         <v>776</v>
       </c>
       <c r="H115" s="162">
@@ -32131,7 +33887,9 @@
       <c r="BI115" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ115" s="31"/>
+      <c r="BJ115" s="31" t="s">
+        <v>892</v>
+      </c>
     </row>
     <row r="116" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="131"/>
@@ -32147,10 +33905,10 @@
       <c r="E116" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="F116" s="266">
+      <c r="F116" s="265">
         <v>1075503</v>
       </c>
-      <c r="G116" s="266" t="s">
+      <c r="G116" s="265" t="s">
         <v>643</v>
       </c>
       <c r="H116" s="162">
@@ -32255,7 +34013,9 @@
       <c r="BI116" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ116" s="31"/>
+      <c r="BJ116" s="31" t="s">
+        <v>893</v>
+      </c>
     </row>
     <row r="117" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="131"/>
@@ -32375,7 +34135,9 @@
       <c r="BG117" s="71"/>
       <c r="BH117" s="71"/>
       <c r="BI117" s="2"/>
-      <c r="BJ117" s="31"/>
+      <c r="BJ117" s="31" t="s">
+        <v>894</v>
+      </c>
     </row>
     <row r="118" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="131"/>
@@ -32497,7 +34259,9 @@
       <c r="BI118" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ118" s="31"/>
+      <c r="BJ118" s="31" t="s">
+        <v>895</v>
+      </c>
     </row>
     <row r="119" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="131"/>
@@ -32617,7 +34381,9 @@
       <c r="BG119" s="71"/>
       <c r="BH119" s="71"/>
       <c r="BI119" s="2"/>
-      <c r="BJ119" s="31"/>
+      <c r="BJ119" s="31" t="s">
+        <v>896</v>
+      </c>
     </row>
     <row r="120" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="131"/>
@@ -32737,7 +34503,9 @@
       <c r="BG120" s="71"/>
       <c r="BH120" s="71"/>
       <c r="BI120" s="158"/>
-      <c r="BJ120" s="31"/>
+      <c r="BJ120" s="31" t="s">
+        <v>897</v>
+      </c>
     </row>
     <row r="121" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="131"/>
@@ -32857,7 +34625,9 @@
       <c r="BG121" s="71"/>
       <c r="BH121" s="71"/>
       <c r="BI121" s="2"/>
-      <c r="BJ121" s="31"/>
+      <c r="BJ121" s="31" t="s">
+        <v>898</v>
+      </c>
     </row>
     <row r="122" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="131"/>
@@ -32979,7 +34749,9 @@
       <c r="BI122" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ122" s="31"/>
+      <c r="BJ122" s="31" t="s">
+        <v>899</v>
+      </c>
     </row>
     <row r="123" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="131"/>
@@ -32995,10 +34767,10 @@
       <c r="E123" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="F123" s="266">
+      <c r="F123" s="265">
         <v>1076303</v>
       </c>
-      <c r="G123" s="266" t="s">
+      <c r="G123" s="265" t="s">
         <v>693</v>
       </c>
       <c r="H123" s="162">
@@ -33103,7 +34875,9 @@
       <c r="BI123" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ123" s="31"/>
+      <c r="BJ123" s="31" t="s">
+        <v>900</v>
+      </c>
     </row>
     <row r="124" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="131"/>
@@ -33227,7 +35001,9 @@
       <c r="BI124" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ124" s="31"/>
+      <c r="BJ124" s="31" t="s">
+        <v>901</v>
+      </c>
     </row>
     <row r="125" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="131"/>
@@ -33347,7 +35123,9 @@
       <c r="BG125" s="71"/>
       <c r="BH125" s="71"/>
       <c r="BI125" s="2"/>
-      <c r="BJ125" s="31"/>
+      <c r="BJ125" s="31" t="s">
+        <v>902</v>
+      </c>
     </row>
     <row r="126" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="131"/>
@@ -33471,7 +35249,9 @@
       <c r="BI126" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ126" s="31"/>
+      <c r="BJ126" s="31" t="s">
+        <v>903</v>
+      </c>
     </row>
     <row r="127" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="131"/>
@@ -33487,10 +35267,10 @@
       <c r="E127" s="133" t="s">
         <v>307</v>
       </c>
-      <c r="F127" s="264">
+      <c r="F127" s="263">
         <v>1077101</v>
       </c>
-      <c r="G127" s="266" t="s">
+      <c r="G127" s="265" t="s">
         <v>677</v>
       </c>
       <c r="H127" s="162">
@@ -33593,7 +35373,9 @@
       <c r="BI127" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ127" s="31"/>
+      <c r="BJ127" s="31" t="s">
+        <v>904</v>
+      </c>
     </row>
     <row r="128" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="131"/>
@@ -33715,7 +35497,9 @@
       <c r="BI128" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ128" s="31"/>
+      <c r="BJ128" s="31" t="s">
+        <v>905</v>
+      </c>
     </row>
     <row r="129" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="131"/>
@@ -33837,7 +35621,9 @@
       <c r="BI129" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ129" s="31"/>
+      <c r="BJ129" s="31" t="s">
+        <v>906</v>
+      </c>
     </row>
     <row r="130" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="131"/>
@@ -33957,7 +35743,9 @@
       <c r="BG130" s="71"/>
       <c r="BH130" s="71"/>
       <c r="BI130" s="158"/>
-      <c r="BJ130" s="31"/>
+      <c r="BJ130" s="31" t="s">
+        <v>907</v>
+      </c>
     </row>
     <row r="131" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="131"/>
@@ -33973,10 +35761,10 @@
       <c r="E131" s="121" t="s">
         <v>307</v>
       </c>
-      <c r="F131" s="264">
+      <c r="F131" s="263">
         <v>1062351</v>
       </c>
-      <c r="G131" s="266" t="s">
+      <c r="G131" s="265" t="s">
         <v>412</v>
       </c>
       <c r="H131" s="162">
@@ -34081,7 +35869,9 @@
       <c r="BI131" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ131" s="31"/>
+      <c r="BJ131" s="31" t="s">
+        <v>908</v>
+      </c>
     </row>
     <row r="132" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="131"/>
@@ -34205,7 +35995,9 @@
       <c r="BI132" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ132" s="31"/>
+      <c r="BJ132" s="31" t="s">
+        <v>909</v>
+      </c>
     </row>
     <row r="133" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="131"/>
@@ -34329,7 +36121,9 @@
       <c r="BI133" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ133" s="31"/>
+      <c r="BJ133" s="31" t="s">
+        <v>910</v>
+      </c>
     </row>
     <row r="134" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="131"/>
@@ -34345,10 +36139,10 @@
       <c r="E134" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="F134" s="266">
+      <c r="F134" s="265">
         <v>1076131</v>
       </c>
-      <c r="G134" s="266" t="s">
+      <c r="G134" s="265" t="s">
         <v>682</v>
       </c>
       <c r="H134" s="162">
@@ -34453,7 +36247,9 @@
       <c r="BI134" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ134" s="31"/>
+      <c r="BJ134" s="31" t="s">
+        <v>911</v>
+      </c>
     </row>
     <row r="135" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="131"/>
@@ -34575,7 +36371,9 @@
       <c r="BI135" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ135" s="31"/>
+      <c r="BJ135" s="31" t="s">
+        <v>912</v>
+      </c>
     </row>
     <row r="136" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="131"/>
@@ -34695,7 +36493,9 @@
       <c r="BG136" s="136"/>
       <c r="BH136" s="136"/>
       <c r="BI136" s="2"/>
-      <c r="BJ136" s="31"/>
+      <c r="BJ136" s="31" t="s">
+        <v>913</v>
+      </c>
     </row>
     <row r="137" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="131"/>
@@ -34819,7 +36619,9 @@
       <c r="BI137" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ137" s="31"/>
+      <c r="BJ137" s="31" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="138" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="131"/>
@@ -34941,7 +36743,9 @@
       <c r="BI138" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ138" s="31"/>
+      <c r="BJ138" s="31" t="s">
+        <v>915</v>
+      </c>
     </row>
     <row r="139" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="131"/>
@@ -35065,7 +36869,9 @@
       <c r="BI139" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ139" s="31"/>
+      <c r="BJ139" s="31" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="140" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="131"/>
@@ -35081,10 +36887,10 @@
       <c r="E140" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="F140" s="264">
+      <c r="F140" s="263">
         <v>1080748</v>
       </c>
-      <c r="G140" s="266" t="s">
+      <c r="G140" s="265" t="s">
         <v>768</v>
       </c>
       <c r="H140" s="162">
@@ -35189,7 +36995,9 @@
       <c r="BI140" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ140" s="31"/>
+      <c r="BJ140" s="31" t="s">
+        <v>917</v>
+      </c>
     </row>
     <row r="141" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="131"/>
@@ -35311,7 +37119,9 @@
       <c r="BI141" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ141" s="31"/>
+      <c r="BJ141" s="31" t="s">
+        <v>918</v>
+      </c>
     </row>
     <row r="142" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="131"/>
@@ -35435,7 +37245,9 @@
       <c r="BI142" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ142" s="31"/>
+      <c r="BJ142" s="31" t="s">
+        <v>919</v>
+      </c>
     </row>
     <row r="143" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="131"/>
@@ -35559,7 +37371,9 @@
       <c r="BI143" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ143" s="31"/>
+      <c r="BJ143" s="31" t="s">
+        <v>920</v>
+      </c>
     </row>
     <row r="144" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="131"/>
@@ -35575,10 +37389,10 @@
       <c r="E144" s="133" t="s">
         <v>311</v>
       </c>
-      <c r="F144" s="264">
+      <c r="F144" s="263">
         <v>1078887</v>
       </c>
-      <c r="G144" s="266" t="s">
+      <c r="G144" s="265" t="s">
         <v>721</v>
       </c>
       <c r="H144" s="162">
@@ -35681,7 +37495,9 @@
       <c r="BI144" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ144" s="31"/>
+      <c r="BJ144" s="31" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="145" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="131"/>
@@ -35803,7 +37619,9 @@
       <c r="BI145" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ145" s="31"/>
+      <c r="BJ145" s="31" t="s">
+        <v>922</v>
+      </c>
     </row>
     <row r="146" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="131"/>
@@ -35927,7 +37745,9 @@
       <c r="BI146" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ146" s="31"/>
+      <c r="BJ146" s="31" t="s">
+        <v>923</v>
+      </c>
     </row>
     <row r="147" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="131"/>
@@ -36051,7 +37871,9 @@
       <c r="BI147" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ147" s="31"/>
+      <c r="BJ147" s="31" t="s">
+        <v>924</v>
+      </c>
     </row>
     <row r="148" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="131"/>
@@ -36067,10 +37889,10 @@
       <c r="E148" s="133" t="s">
         <v>401</v>
       </c>
-      <c r="F148" s="269">
+      <c r="F148" s="268">
         <v>1076365</v>
       </c>
-      <c r="G148" s="270" t="s">
+      <c r="G148" s="269" t="s">
         <v>724</v>
       </c>
       <c r="H148" s="162">
@@ -36171,7 +37993,9 @@
       <c r="BG148" s="71"/>
       <c r="BH148" s="71"/>
       <c r="BI148" s="158"/>
-      <c r="BJ148" s="31"/>
+      <c r="BJ148" s="31" t="s">
+        <v>925</v>
+      </c>
     </row>
     <row r="149" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="131"/>
@@ -36187,13 +38011,13 @@
       <c r="E149" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="F149" s="267">
+      <c r="F149" s="266">
         <v>1080746</v>
       </c>
-      <c r="G149" s="271" t="s">
+      <c r="G149" s="270" t="s">
         <v>789</v>
       </c>
-      <c r="H149" s="254">
+      <c r="H149" s="253">
         <v>6537</v>
       </c>
       <c r="I149" s="162">
@@ -36291,7 +38115,9 @@
       <c r="BG149" s="71"/>
       <c r="BH149" s="71"/>
       <c r="BI149" s="2"/>
-      <c r="BJ149" s="31"/>
+      <c r="BJ149" s="31" t="s">
+        <v>926</v>
+      </c>
     </row>
     <row r="150" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="131"/>
@@ -36307,10 +38133,10 @@
       <c r="E150" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="F150" s="264">
+      <c r="F150" s="263">
         <v>1075854</v>
       </c>
-      <c r="G150" s="266" t="s">
+      <c r="G150" s="265" t="s">
         <v>689</v>
       </c>
       <c r="H150" s="162">
@@ -36415,7 +38241,9 @@
       <c r="BI150" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ150" s="31"/>
+      <c r="BJ150" s="31" t="s">
+        <v>927</v>
+      </c>
     </row>
     <row r="151" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="131"/>
@@ -36535,7 +38363,9 @@
       <c r="BG151" s="204"/>
       <c r="BH151" s="204"/>
       <c r="BI151" s="205"/>
-      <c r="BJ151" s="31"/>
+      <c r="BJ151" s="31" t="s">
+        <v>928</v>
+      </c>
     </row>
     <row r="152" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="131"/>
@@ -36551,10 +38381,10 @@
       <c r="E152" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="F152" s="264">
+      <c r="F152" s="263">
         <v>1078161</v>
       </c>
-      <c r="G152" s="266" t="s">
+      <c r="G152" s="265" t="s">
         <v>705</v>
       </c>
       <c r="H152" s="162">
@@ -36655,7 +38485,9 @@
       <c r="BG152" s="71"/>
       <c r="BH152" s="71"/>
       <c r="BI152" s="158"/>
-      <c r="BJ152" s="31"/>
+      <c r="BJ152" s="31" t="s">
+        <v>929</v>
+      </c>
     </row>
     <row r="153" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="131"/>
@@ -36777,7 +38609,9 @@
       <c r="BI153" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ153" s="31"/>
+      <c r="BJ153" s="31" t="s">
+        <v>930</v>
+      </c>
     </row>
     <row r="154" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="131"/>
@@ -36899,7 +38733,9 @@
       <c r="BI154" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ154" s="31"/>
+      <c r="BJ154" s="31" t="s">
+        <v>931</v>
+      </c>
     </row>
     <row r="155" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="131"/>
@@ -37023,7 +38859,9 @@
       <c r="BI155" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ155" s="31"/>
+      <c r="BJ155" s="31" t="s">
+        <v>932</v>
+      </c>
     </row>
     <row r="156" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="131"/>
@@ -37143,7 +38981,9 @@
       <c r="BG156" s="71"/>
       <c r="BH156" s="71"/>
       <c r="BI156" s="158"/>
-      <c r="BJ156" s="31"/>
+      <c r="BJ156" s="31" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="157" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A157" s="131"/>
@@ -37267,7 +39107,9 @@
       <c r="BI157" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ157" s="31"/>
+      <c r="BJ157" s="31" t="s">
+        <v>934</v>
+      </c>
     </row>
     <row r="158" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="131"/>
@@ -37391,7 +39233,9 @@
       <c r="BI158" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ158" s="31"/>
+      <c r="BJ158" s="31" t="s">
+        <v>935</v>
+      </c>
     </row>
     <row r="159" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="131"/>
@@ -37515,7 +39359,9 @@
       <c r="BI159" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ159" s="31"/>
+      <c r="BJ159" s="31" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="160" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="131"/>
@@ -37639,7 +39485,9 @@
       <c r="BI160" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ160" s="31"/>
+      <c r="BJ160" s="31" t="s">
+        <v>937</v>
+      </c>
     </row>
     <row r="161" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="131"/>
@@ -37655,10 +39503,10 @@
       <c r="E161" s="133" t="s">
         <v>311</v>
       </c>
-      <c r="F161" s="266">
+      <c r="F161" s="265">
         <v>1068804</v>
       </c>
-      <c r="G161" s="266" t="s">
+      <c r="G161" s="265" t="s">
         <v>563</v>
       </c>
       <c r="H161" s="162">
@@ -37763,7 +39611,9 @@
       <c r="BI161" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ161" s="31"/>
+      <c r="BJ161" s="31" t="s">
+        <v>938</v>
+      </c>
     </row>
     <row r="162" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="131"/>
@@ -37885,7 +39735,9 @@
       <c r="BI162" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ162" s="31"/>
+      <c r="BJ162" s="31" t="s">
+        <v>939</v>
+      </c>
     </row>
     <row r="163" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="131"/>
@@ -38005,7 +39857,9 @@
       <c r="BG163" s="71"/>
       <c r="BH163" s="71"/>
       <c r="BI163" s="158"/>
-      <c r="BJ163" s="31"/>
+      <c r="BJ163" s="31" t="s">
+        <v>940</v>
+      </c>
     </row>
     <row r="164" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="131"/>
@@ -38129,7 +39983,9 @@
       <c r="BI164" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ164" s="31"/>
+      <c r="BJ164" s="31" t="s">
+        <v>941</v>
+      </c>
     </row>
     <row r="165" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="131"/>
@@ -38253,7 +40109,9 @@
       <c r="BI165" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ165" s="31"/>
+      <c r="BJ165" s="31" t="s">
+        <v>942</v>
+      </c>
     </row>
     <row r="166" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="131"/>
@@ -38377,7 +40235,9 @@
       <c r="BI166" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ166" s="31"/>
+      <c r="BJ166" s="31" t="s">
+        <v>943</v>
+      </c>
     </row>
     <row r="167" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="131"/>
@@ -38501,7 +40361,9 @@
       <c r="BI167" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ167" s="31"/>
+      <c r="BJ167" s="31" t="s">
+        <v>944</v>
+      </c>
     </row>
     <row r="168" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="131"/>
@@ -38621,7 +40483,9 @@
       <c r="BG168" s="71"/>
       <c r="BH168" s="71"/>
       <c r="BI168" s="158"/>
-      <c r="BJ168" s="31"/>
+      <c r="BJ168" s="31" t="s">
+        <v>945</v>
+      </c>
     </row>
     <row r="169" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="131"/>
@@ -38743,7 +40607,9 @@
       <c r="BI169" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ169" s="31"/>
+      <c r="BJ169" s="31" t="s">
+        <v>946</v>
+      </c>
     </row>
     <row r="170" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="131"/>
@@ -38867,7 +40733,9 @@
       <c r="BI170" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ170" s="31"/>
+      <c r="BJ170" s="31" t="s">
+        <v>947</v>
+      </c>
     </row>
     <row r="171" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="131"/>
@@ -38987,7 +40855,9 @@
       <c r="BG171" s="71"/>
       <c r="BH171" s="71"/>
       <c r="BI171" s="158"/>
-      <c r="BJ171" s="31"/>
+      <c r="BJ171" s="31" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="172" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="131"/>
@@ -39003,10 +40873,10 @@
       <c r="E172" s="133" t="s">
         <v>311</v>
       </c>
-      <c r="F172" s="264">
+      <c r="F172" s="263">
         <v>1078888</v>
       </c>
-      <c r="G172" s="266" t="s">
+      <c r="G172" s="265" t="s">
         <v>717</v>
       </c>
       <c r="H172" s="162">
@@ -39107,7 +40977,9 @@
       <c r="BG172" s="136"/>
       <c r="BH172" s="136"/>
       <c r="BI172" s="158"/>
-      <c r="BJ172" s="31"/>
+      <c r="BJ172" s="31" t="s">
+        <v>949</v>
+      </c>
     </row>
     <row r="173" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="131"/>
@@ -39231,7 +41103,9 @@
       <c r="BI173" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ173" s="31"/>
+      <c r="BJ173" s="31" t="s">
+        <v>950</v>
+      </c>
     </row>
     <row r="174" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="131"/>
@@ -39355,7 +41229,9 @@
       <c r="BI174" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ174" s="31"/>
+      <c r="BJ174" s="31" t="s">
+        <v>951</v>
+      </c>
     </row>
     <row r="175" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="131"/>
@@ -39477,7 +41353,9 @@
       <c r="BI175" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ175" s="31"/>
+      <c r="BJ175" s="31" t="s">
+        <v>952</v>
+      </c>
     </row>
     <row r="176" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="131"/>
@@ -39601,7 +41479,9 @@
       <c r="BI176" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ176" s="31"/>
+      <c r="BJ176" s="31" t="s">
+        <v>953</v>
+      </c>
     </row>
     <row r="177" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="131"/>
@@ -39617,10 +41497,10 @@
       <c r="E177" s="133" t="s">
         <v>311</v>
       </c>
-      <c r="F177" s="264">
+      <c r="F177" s="263">
         <v>1080401</v>
       </c>
-      <c r="G177" s="266" t="s">
+      <c r="G177" s="265" t="s">
         <v>754</v>
       </c>
       <c r="H177" s="162">
@@ -39721,7 +41601,9 @@
       <c r="BG177" s="71"/>
       <c r="BH177" s="71"/>
       <c r="BI177" s="158"/>
-      <c r="BJ177" s="31"/>
+      <c r="BJ177" s="31" t="s">
+        <v>954</v>
+      </c>
     </row>
     <row r="178" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="131"/>
@@ -39843,7 +41725,9 @@
       <c r="BI178" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ178" s="31"/>
+      <c r="BJ178" s="31" t="s">
+        <v>955</v>
+      </c>
     </row>
     <row r="179" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A179" s="131"/>
@@ -39967,7 +41851,9 @@
       <c r="BI179" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ179" s="31"/>
+      <c r="BJ179" s="31" t="s">
+        <v>956</v>
+      </c>
     </row>
     <row r="180" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="131"/>
@@ -40089,7 +41975,9 @@
       <c r="BI180" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ180" s="31"/>
+      <c r="BJ180" s="31" t="s">
+        <v>957</v>
+      </c>
     </row>
     <row r="181" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="131"/>
@@ -40211,7 +42099,9 @@
       <c r="BI181" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ181" s="31"/>
+      <c r="BJ181" s="31" t="s">
+        <v>958</v>
+      </c>
     </row>
     <row r="182" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A182" s="131"/>
@@ -40335,7 +42225,9 @@
       <c r="BI182" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ182" s="31"/>
+      <c r="BJ182" s="31" t="s">
+        <v>959</v>
+      </c>
     </row>
     <row r="183" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A183" s="131"/>
@@ -40459,7 +42351,9 @@
       <c r="BI183" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ183" s="31"/>
+      <c r="BJ183" s="31" t="s">
+        <v>960</v>
+      </c>
     </row>
     <row r="184" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="131"/>
@@ -40579,7 +42473,9 @@
       <c r="BG184" s="71"/>
       <c r="BH184" s="71"/>
       <c r="BI184" s="158"/>
-      <c r="BJ184" s="31"/>
+      <c r="BJ184" s="31" t="s">
+        <v>961</v>
+      </c>
     </row>
     <row r="185" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="131"/>
@@ -40703,7 +42599,9 @@
       <c r="BI185" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ185" s="31"/>
+      <c r="BJ185" s="31" t="s">
+        <v>962</v>
+      </c>
     </row>
     <row r="186" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="131"/>
@@ -40827,7 +42725,9 @@
       <c r="BI186" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ186" s="31"/>
+      <c r="BJ186" s="31" t="s">
+        <v>963</v>
+      </c>
     </row>
     <row r="187" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="131"/>
@@ -40951,7 +42851,9 @@
       <c r="BI187" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ187" s="31"/>
+      <c r="BJ187" s="31" t="s">
+        <v>964</v>
+      </c>
     </row>
     <row r="188" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="131"/>
@@ -41075,7 +42977,9 @@
       <c r="BI188" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ188" s="31"/>
+      <c r="BJ188" s="31" t="s">
+        <v>965</v>
+      </c>
     </row>
     <row r="189" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="131"/>
@@ -41199,7 +43103,9 @@
       <c r="BI189" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ189" s="31"/>
+      <c r="BJ189" s="31" t="s">
+        <v>966</v>
+      </c>
     </row>
     <row r="190" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="131"/>
@@ -41319,7 +43225,9 @@
       <c r="BG190" s="71"/>
       <c r="BH190" s="71"/>
       <c r="BI190" s="2"/>
-      <c r="BJ190" s="31"/>
+      <c r="BJ190" s="31" t="s">
+        <v>967</v>
+      </c>
     </row>
     <row r="191" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="131"/>
@@ -41443,7 +43351,9 @@
       <c r="BI191" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ191" s="31"/>
+      <c r="BJ191" s="31" t="s">
+        <v>968</v>
+      </c>
     </row>
     <row r="192" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="131"/>
@@ -41459,10 +43369,10 @@
       <c r="E192" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="F192" s="264">
+      <c r="F192" s="263">
         <v>1078355</v>
       </c>
-      <c r="G192" s="266" t="s">
+      <c r="G192" s="265" t="s">
         <v>706</v>
       </c>
       <c r="H192" s="162">
@@ -41567,7 +43477,9 @@
       <c r="BI192" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ192" s="31"/>
+      <c r="BJ192" s="31" t="s">
+        <v>969</v>
+      </c>
     </row>
     <row r="193" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="131"/>
@@ -41691,7 +43603,9 @@
       <c r="BI193" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ193" s="31"/>
+      <c r="BJ193" s="31" t="s">
+        <v>970</v>
+      </c>
     </row>
     <row r="194" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="131"/>
@@ -41707,10 +43621,10 @@
       <c r="E194" s="133" t="s">
         <v>311</v>
       </c>
-      <c r="F194" s="264">
+      <c r="F194" s="263">
         <v>1080400</v>
       </c>
-      <c r="G194" s="266" t="s">
+      <c r="G194" s="265" t="s">
         <v>753</v>
       </c>
       <c r="H194" s="162">
@@ -41815,7 +43729,9 @@
       <c r="BI194" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ194" s="31"/>
+      <c r="BJ194" s="31" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="195" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="131"/>
@@ -41939,7 +43855,9 @@
       <c r="BI195" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ195" s="31"/>
+      <c r="BJ195" s="31" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="196" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="131"/>
@@ -42059,7 +43977,9 @@
       <c r="BG196" s="71"/>
       <c r="BH196" s="71"/>
       <c r="BI196" s="2"/>
-      <c r="BJ196" s="31"/>
+      <c r="BJ196" s="31" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="197" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="131"/>
@@ -42183,7 +44103,9 @@
       <c r="BI197" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ197" s="31"/>
+      <c r="BJ197" s="31" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="198" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="131"/>
@@ -42303,7 +44225,9 @@
       <c r="BG198" s="71"/>
       <c r="BH198" s="71"/>
       <c r="BI198" s="158"/>
-      <c r="BJ198" s="31"/>
+      <c r="BJ198" s="31" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="199" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="131"/>
@@ -42425,7 +44349,9 @@
       <c r="BI199" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ199" s="31"/>
+      <c r="BJ199" s="31" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="200" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="131"/>
@@ -42549,7 +44475,9 @@
       <c r="BI200" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ200" s="31"/>
+      <c r="BJ200" s="31" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="201" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="131"/>
@@ -42671,7 +44599,9 @@
       <c r="BI201" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ201" s="31"/>
+      <c r="BJ201" s="31" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="202" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="131"/>
@@ -42795,7 +44725,9 @@
       <c r="BI202" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ202" s="31"/>
+      <c r="BJ202" s="31" t="s">
+        <v>979</v>
+      </c>
     </row>
     <row r="203" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="131"/>
@@ -42919,7 +44851,9 @@
       <c r="BI203" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ203" s="31"/>
+      <c r="BJ203" s="31" t="s">
+        <v>980</v>
+      </c>
     </row>
     <row r="204" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="131"/>
@@ -43041,7 +44975,9 @@
       <c r="BI204" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ204" s="31"/>
+      <c r="BJ204" s="31" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="205" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="131"/>
@@ -43161,7 +45097,9 @@
       <c r="BG205" s="174"/>
       <c r="BH205" s="174"/>
       <c r="BI205" s="2"/>
-      <c r="BJ205" s="31"/>
+      <c r="BJ205" s="31" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="206" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="131"/>
@@ -43285,7 +45223,9 @@
       <c r="BI206" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ206" s="31"/>
+      <c r="BJ206" s="31" t="s">
+        <v>983</v>
+      </c>
     </row>
     <row r="207" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="131"/>
@@ -43409,7 +45349,9 @@
       <c r="BI207" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ207" s="31"/>
+      <c r="BJ207" s="31" t="s">
+        <v>984</v>
+      </c>
     </row>
     <row r="208" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="131"/>
@@ -43529,7 +45471,9 @@
       <c r="BG208" s="71"/>
       <c r="BH208" s="71"/>
       <c r="BI208" s="158"/>
-      <c r="BJ208" s="31"/>
+      <c r="BJ208" s="31" t="s">
+        <v>985</v>
+      </c>
     </row>
     <row r="209" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="131"/>
@@ -43649,7 +45593,9 @@
       <c r="BG209" s="71"/>
       <c r="BH209" s="71"/>
       <c r="BI209" s="158"/>
-      <c r="BJ209" s="31"/>
+      <c r="BJ209" s="31" t="s">
+        <v>986</v>
+      </c>
     </row>
     <row r="210" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="131"/>
@@ -43773,7 +45719,9 @@
       <c r="BI210" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ210" s="31"/>
+      <c r="BJ210" s="31" t="s">
+        <v>987</v>
+      </c>
     </row>
     <row r="211" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="131"/>
@@ -43897,7 +45845,9 @@
       <c r="BI211" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ211" s="31"/>
+      <c r="BJ211" s="31" t="s">
+        <v>988</v>
+      </c>
     </row>
     <row r="212" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="131"/>
@@ -44021,7 +45971,9 @@
       <c r="BI212" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ212" s="31"/>
+      <c r="BJ212" s="31" t="s">
+        <v>989</v>
+      </c>
     </row>
     <row r="213" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="131"/>
@@ -44145,7 +46097,9 @@
       <c r="BI213" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ213" s="31"/>
+      <c r="BJ213" s="31" t="s">
+        <v>990</v>
+      </c>
     </row>
     <row r="214" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="131"/>
@@ -44265,7 +46219,9 @@
       <c r="BG214" s="71"/>
       <c r="BH214" s="71"/>
       <c r="BI214" s="2"/>
-      <c r="BJ214" s="31"/>
+      <c r="BJ214" s="31" t="s">
+        <v>991</v>
+      </c>
     </row>
     <row r="215" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="131"/>
@@ -44389,7 +46345,9 @@
       <c r="BI215" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ215" s="31"/>
+      <c r="BJ215" s="31" t="s">
+        <v>992</v>
+      </c>
     </row>
     <row r="216" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="131"/>
@@ -44509,7 +46467,9 @@
       <c r="BG216" s="71"/>
       <c r="BH216" s="71"/>
       <c r="BI216" s="2"/>
-      <c r="BJ216" s="31"/>
+      <c r="BJ216" s="31" t="s">
+        <v>993</v>
+      </c>
     </row>
     <row r="217" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="131"/>
@@ -44633,7 +46593,9 @@
       <c r="BI217" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ217" s="31"/>
+      <c r="BJ217" s="31" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="218" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="131"/>
@@ -44757,7 +46719,9 @@
       <c r="BI218" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ218" s="31"/>
+      <c r="BJ218" s="31" t="s">
+        <v>995</v>
+      </c>
     </row>
     <row r="219" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="131"/>
@@ -44881,7 +46845,9 @@
       <c r="BI219" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ219" s="31"/>
+      <c r="BJ219" s="31" t="s">
+        <v>996</v>
+      </c>
     </row>
     <row r="220" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="131"/>
@@ -45005,7 +46971,9 @@
       <c r="BI220" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ220" s="31"/>
+      <c r="BJ220" s="31" t="s">
+        <v>997</v>
+      </c>
     </row>
     <row r="221" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="131"/>
@@ -45125,7 +47093,9 @@
       <c r="BG221" s="71"/>
       <c r="BH221" s="71"/>
       <c r="BI221" s="158"/>
-      <c r="BJ221" s="31"/>
+      <c r="BJ221" s="31" t="s">
+        <v>998</v>
+      </c>
     </row>
     <row r="222" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="131"/>
@@ -45249,7 +47219,9 @@
       <c r="BI222" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ222" s="31"/>
+      <c r="BJ222" s="31" t="s">
+        <v>999</v>
+      </c>
     </row>
     <row r="223" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="131"/>
@@ -45371,7 +47343,9 @@
       <c r="BI223" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ223" s="31"/>
+      <c r="BJ223" s="31" t="s">
+        <v>1000</v>
+      </c>
     </row>
     <row r="224" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="131"/>
@@ -45491,7 +47465,9 @@
       <c r="BG224" s="152"/>
       <c r="BH224" s="152"/>
       <c r="BI224" s="158"/>
-      <c r="BJ224" s="31"/>
+      <c r="BJ224" s="31" t="s">
+        <v>1001</v>
+      </c>
     </row>
     <row r="225" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="131"/>
@@ -45613,7 +47589,9 @@
       <c r="BI225" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ225" s="31"/>
+      <c r="BJ225" s="31" t="s">
+        <v>1002</v>
+      </c>
     </row>
     <row r="226" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="131"/>
@@ -45737,7 +47715,9 @@
       <c r="BI226" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ226" s="31"/>
+      <c r="BJ226" s="31" t="s">
+        <v>1003</v>
+      </c>
     </row>
     <row r="227" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="131"/>
@@ -45859,7 +47839,9 @@
       <c r="BI227" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ227" s="31"/>
+      <c r="BJ227" s="31" t="s">
+        <v>1004</v>
+      </c>
     </row>
     <row r="228" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="131"/>
@@ -45981,7 +47963,9 @@
       <c r="BI228" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ228" s="31"/>
+      <c r="BJ228" s="31" t="s">
+        <v>1005</v>
+      </c>
     </row>
     <row r="229" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="131"/>
@@ -46105,7 +48089,9 @@
       <c r="BI229" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ229" s="31"/>
+      <c r="BJ229" s="31" t="s">
+        <v>1006</v>
+      </c>
     </row>
     <row r="230" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="131"/>
@@ -46225,7 +48211,9 @@
       <c r="BG230" s="71"/>
       <c r="BH230" s="71"/>
       <c r="BI230" s="158"/>
-      <c r="BJ230" s="31"/>
+      <c r="BJ230" s="31" t="s">
+        <v>1007</v>
+      </c>
     </row>
     <row r="231" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="131"/>
@@ -46347,7 +48335,9 @@
       <c r="BI231" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ231" s="31"/>
+      <c r="BJ231" s="31" t="s">
+        <v>1008</v>
+      </c>
     </row>
     <row r="232" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="131"/>
@@ -46471,7 +48461,9 @@
       <c r="BI232" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ232" s="31"/>
+      <c r="BJ232" s="31" t="s">
+        <v>1009</v>
+      </c>
     </row>
     <row r="233" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="131"/>
@@ -46591,7 +48583,9 @@
       <c r="BG233" s="152"/>
       <c r="BH233" s="152"/>
       <c r="BI233" s="158"/>
-      <c r="BJ233" s="31"/>
+      <c r="BJ233" s="31" t="s">
+        <v>1010</v>
+      </c>
     </row>
     <row r="234" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="131"/>
@@ -46715,7 +48709,9 @@
       <c r="BI234" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ234" s="31"/>
+      <c r="BJ234" s="31" t="s">
+        <v>1011</v>
+      </c>
     </row>
     <row r="235" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="131"/>
@@ -46837,7 +48833,9 @@
       <c r="BI235" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ235" s="31"/>
+      <c r="BJ235" s="31" t="s">
+        <v>1012</v>
+      </c>
     </row>
     <row r="236" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="131"/>
@@ -46957,7 +48955,9 @@
       <c r="BG236" s="71"/>
       <c r="BH236" s="71"/>
       <c r="BI236" s="158"/>
-      <c r="BJ236" s="31"/>
+      <c r="BJ236" s="31" t="s">
+        <v>1013</v>
+      </c>
     </row>
     <row r="237" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="131"/>
@@ -47081,7 +49081,9 @@
       <c r="BI237" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ237" s="31"/>
+      <c r="BJ237" s="31" t="s">
+        <v>1014</v>
+      </c>
     </row>
     <row r="238" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="131"/>
@@ -47203,7 +49205,9 @@
       <c r="BI238" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ238" s="31"/>
+      <c r="BJ238" s="31" t="s">
+        <v>1015</v>
+      </c>
     </row>
     <row r="239" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="131"/>
@@ -47327,7 +49331,9 @@
       <c r="BI239" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ239" s="31"/>
+      <c r="BJ239" s="31" t="s">
+        <v>1016</v>
+      </c>
     </row>
     <row r="240" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="131"/>
@@ -47451,7 +49457,9 @@
       <c r="BI240" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ240" s="31"/>
+      <c r="BJ240" s="31" t="s">
+        <v>1017</v>
+      </c>
     </row>
     <row r="241" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="131"/>
@@ -47573,7 +49581,9 @@
       <c r="BI241" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ241" s="31"/>
+      <c r="BJ241" s="31" t="s">
+        <v>1018</v>
+      </c>
     </row>
     <row r="242" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="131"/>
@@ -47697,7 +49707,9 @@
       <c r="BI242" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ242" s="31"/>
+      <c r="BJ242" s="31" t="s">
+        <v>1019</v>
+      </c>
     </row>
     <row r="243" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="131"/>
@@ -47821,7 +49833,9 @@
       <c r="BI243" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ243" s="31"/>
+      <c r="BJ243" s="31" t="s">
+        <v>1020</v>
+      </c>
     </row>
     <row r="244" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="131"/>
@@ -47945,7 +49959,9 @@
       <c r="BI244" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ244" s="31"/>
+      <c r="BJ244" s="31" t="s">
+        <v>1021</v>
+      </c>
     </row>
     <row r="245" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="131"/>
@@ -48069,7 +50085,9 @@
       <c r="BI245" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ245" s="31"/>
+      <c r="BJ245" s="31" t="s">
+        <v>1022</v>
+      </c>
     </row>
     <row r="246" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="131"/>
@@ -48189,7 +50207,9 @@
       <c r="BG246" s="71"/>
       <c r="BH246" s="72"/>
       <c r="BI246" s="158"/>
-      <c r="BJ246" s="31"/>
+      <c r="BJ246" s="31" t="s">
+        <v>1023</v>
+      </c>
     </row>
     <row r="247" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="131"/>
@@ -48313,7 +50333,9 @@
       <c r="BI247" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ247" s="31"/>
+      <c r="BJ247" s="31" t="s">
+        <v>1024</v>
+      </c>
     </row>
     <row r="248" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="131"/>
@@ -48435,7 +50457,9 @@
       <c r="BI248" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ248" s="31"/>
+      <c r="BJ248" s="31" t="s">
+        <v>1025</v>
+      </c>
     </row>
     <row r="249" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="131"/>
@@ -48559,7 +50583,9 @@
       <c r="BI249" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ249" s="31"/>
+      <c r="BJ249" s="31" t="s">
+        <v>1026</v>
+      </c>
     </row>
     <row r="250" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="131"/>
@@ -48681,7 +50707,9 @@
       <c r="BI250" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ250" s="31"/>
+      <c r="BJ250" s="31" t="s">
+        <v>1027</v>
+      </c>
     </row>
     <row r="251" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="131"/>
@@ -48803,7 +50831,9 @@
       <c r="BI251" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ251" s="31"/>
+      <c r="BJ251" s="31" t="s">
+        <v>1028</v>
+      </c>
     </row>
     <row r="252" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="131"/>
@@ -48923,7 +50953,9 @@
       <c r="BG252" s="71"/>
       <c r="BH252" s="71"/>
       <c r="BI252" s="158"/>
-      <c r="BJ252" s="31"/>
+      <c r="BJ252" s="31" t="s">
+        <v>1029</v>
+      </c>
     </row>
     <row r="253" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="131"/>
@@ -49047,7 +51079,9 @@
       <c r="BI253" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ253" s="31"/>
+      <c r="BJ253" s="31" t="s">
+        <v>1030</v>
+      </c>
     </row>
     <row r="254" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="131"/>
@@ -49171,7 +51205,9 @@
       <c r="BI254" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ254" s="31"/>
+      <c r="BJ254" s="31" t="s">
+        <v>1031</v>
+      </c>
     </row>
     <row r="255" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="131"/>
@@ -49295,7 +51331,9 @@
       <c r="BI255" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ255" s="31"/>
+      <c r="BJ255" s="31" t="s">
+        <v>1032</v>
+      </c>
     </row>
     <row r="256" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="131"/>
@@ -49415,7 +51453,9 @@
       <c r="BG256" s="174"/>
       <c r="BH256" s="177"/>
       <c r="BI256" s="2"/>
-      <c r="BJ256" s="31"/>
+      <c r="BJ256" s="31" t="s">
+        <v>1033</v>
+      </c>
     </row>
     <row r="257" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="131"/>
@@ -49539,7 +51579,9 @@
       <c r="BI257" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ257" s="31"/>
+      <c r="BJ257" s="31" t="s">
+        <v>1034</v>
+      </c>
     </row>
     <row r="258" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="131"/>
@@ -49627,39 +51669,41 @@
       <c r="AC258" s="11" t="s">
         <v>791</v>
       </c>
-      <c r="AD258" s="263"/>
-      <c r="AE258" s="263"/>
-      <c r="AF258" s="263"/>
-      <c r="AG258" s="263"/>
-      <c r="AH258" s="263"/>
-      <c r="AI258" s="263"/>
-      <c r="AJ258" s="263"/>
-      <c r="AK258" s="263"/>
-      <c r="AL258" s="263"/>
-      <c r="AM258" s="263"/>
-      <c r="AN258" s="263"/>
-      <c r="AO258" s="263"/>
-      <c r="AP258" s="263"/>
+      <c r="AD258" s="262"/>
+      <c r="AE258" s="262"/>
+      <c r="AF258" s="262"/>
+      <c r="AG258" s="262"/>
+      <c r="AH258" s="262"/>
+      <c r="AI258" s="262"/>
+      <c r="AJ258" s="262"/>
+      <c r="AK258" s="262"/>
+      <c r="AL258" s="262"/>
+      <c r="AM258" s="262"/>
+      <c r="AN258" s="262"/>
+      <c r="AO258" s="262"/>
+      <c r="AP258" s="262"/>
       <c r="AQ258" s="71"/>
       <c r="AR258" s="71"/>
-      <c r="AS258" s="263"/>
-      <c r="AT258" s="263"/>
-      <c r="AU258" s="263"/>
-      <c r="AV258" s="263"/>
-      <c r="AW258" s="263"/>
-      <c r="AX258" s="263"/>
-      <c r="AY258" s="263"/>
-      <c r="AZ258" s="263"/>
-      <c r="BA258" s="263"/>
-      <c r="BB258" s="263"/>
-      <c r="BC258" s="263"/>
-      <c r="BD258" s="263"/>
+      <c r="AS258" s="262"/>
+      <c r="AT258" s="262"/>
+      <c r="AU258" s="262"/>
+      <c r="AV258" s="262"/>
+      <c r="AW258" s="262"/>
+      <c r="AX258" s="262"/>
+      <c r="AY258" s="262"/>
+      <c r="AZ258" s="262"/>
+      <c r="BA258" s="262"/>
+      <c r="BB258" s="262"/>
+      <c r="BC258" s="262"/>
+      <c r="BD258" s="262"/>
       <c r="BE258" s="71"/>
       <c r="BF258" s="71"/>
       <c r="BG258" s="71"/>
-      <c r="BH258" s="263"/>
+      <c r="BH258" s="262"/>
       <c r="BI258" s="158"/>
-      <c r="BJ258" s="31"/>
+      <c r="BJ258" s="31" t="s">
+        <v>1035</v>
+      </c>
     </row>
     <row r="259" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="131"/>
@@ -49783,7 +51827,9 @@
       <c r="BI259" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ259" s="31"/>
+      <c r="BJ259" s="31" t="s">
+        <v>1036</v>
+      </c>
     </row>
     <row r="260" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="131"/>
@@ -49907,7 +51953,9 @@
       <c r="BI260" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ260" s="31"/>
+      <c r="BJ260" s="31" t="s">
+        <v>1037</v>
+      </c>
     </row>
     <row r="261" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="131"/>
@@ -49980,7 +52028,7 @@
       <c r="X261" s="9">
         <v>0</v>
       </c>
-      <c r="Y261" s="260" t="s">
+      <c r="Y261" s="259" t="s">
         <v>574</v>
       </c>
       <c r="Z261" s="9" t="s">
@@ -50027,7 +52075,9 @@
       <c r="BG261" s="177"/>
       <c r="BH261" s="177"/>
       <c r="BI261" s="2"/>
-      <c r="BJ261" s="31"/>
+      <c r="BJ261" s="31" t="s">
+        <v>1038</v>
+      </c>
     </row>
     <row r="262" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="131"/>
@@ -50151,7 +52201,9 @@
       <c r="BI262" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ262" s="31"/>
+      <c r="BJ262" s="31" t="s">
+        <v>1039</v>
+      </c>
     </row>
     <row r="263" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="131"/>
@@ -50273,7 +52325,9 @@
       <c r="BI263" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ263" s="31"/>
+      <c r="BJ263" s="31" t="s">
+        <v>1040</v>
+      </c>
     </row>
     <row r="264" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="131"/>
@@ -50397,7 +52451,9 @@
       <c r="BI264" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ264" s="31"/>
+      <c r="BJ264" s="31" t="s">
+        <v>1041</v>
+      </c>
     </row>
     <row r="265" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="131"/>
@@ -50517,7 +52573,9 @@
       <c r="BG265" s="71"/>
       <c r="BH265" s="71"/>
       <c r="BI265" s="158"/>
-      <c r="BJ265" s="31"/>
+      <c r="BJ265" s="31" t="s">
+        <v>1042</v>
+      </c>
     </row>
     <row r="266" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="131"/>
@@ -50639,7 +52697,9 @@
       <c r="BI266" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ266" s="31"/>
+      <c r="BJ266" s="31" t="s">
+        <v>1043</v>
+      </c>
     </row>
     <row r="267" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A267" s="131"/>
@@ -50759,7 +52819,9 @@
       <c r="BG267" s="71"/>
       <c r="BH267" s="71"/>
       <c r="BI267" s="158"/>
-      <c r="BJ267" s="31"/>
+      <c r="BJ267" s="31" t="s">
+        <v>1044</v>
+      </c>
     </row>
     <row r="268" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="131"/>
@@ -50883,7 +52945,9 @@
       <c r="BI268" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ268" s="31"/>
+      <c r="BJ268" s="31" t="s">
+        <v>1045</v>
+      </c>
     </row>
     <row r="269" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A269" s="131"/>
@@ -51007,7 +53071,9 @@
       <c r="BI269" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ269" s="31"/>
+      <c r="BJ269" s="31" t="s">
+        <v>1046</v>
+      </c>
     </row>
     <row r="270" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A270" s="131"/>
@@ -51131,7 +53197,9 @@
       <c r="BI270" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ270" s="31"/>
+      <c r="BJ270" s="31" t="s">
+        <v>1047</v>
+      </c>
     </row>
     <row r="271" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A271" s="131"/>
@@ -51204,7 +53272,7 @@
       <c r="X271" s="9">
         <v>0</v>
       </c>
-      <c r="Y271" s="261" t="s">
+      <c r="Y271" s="260" t="s">
         <v>574</v>
       </c>
       <c r="Z271" s="9" t="s">
@@ -51251,7 +53319,9 @@
       <c r="BG271" s="182"/>
       <c r="BH271" s="182"/>
       <c r="BI271" s="158"/>
-      <c r="BJ271" s="31"/>
+      <c r="BJ271" s="31" t="s">
+        <v>1048</v>
+      </c>
     </row>
     <row r="272" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A272" s="131"/>
@@ -51375,7 +53445,9 @@
       <c r="BI272" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ272" s="31"/>
+      <c r="BJ272" s="31" t="s">
+        <v>1049</v>
+      </c>
     </row>
     <row r="273" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A273" s="131"/>
@@ -51499,7 +53571,9 @@
       <c r="BI273" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ273" s="31"/>
+      <c r="BJ273" s="31" t="s">
+        <v>1050</v>
+      </c>
     </row>
     <row r="274" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A274" s="131"/>
@@ -51623,7 +53697,9 @@
       <c r="BI274" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ274" s="31"/>
+      <c r="BJ274" s="31" t="s">
+        <v>1051</v>
+      </c>
     </row>
     <row r="275" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A275" s="131"/>
@@ -51745,7 +53821,9 @@
       <c r="BI275" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ275" s="31"/>
+      <c r="BJ275" s="31" t="s">
+        <v>1052</v>
+      </c>
     </row>
     <row r="276" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A276" s="131"/>
@@ -51761,10 +53839,10 @@
       <c r="E276" s="145" t="s">
         <v>397</v>
       </c>
-      <c r="F276" s="244">
+      <c r="F276" s="243">
         <v>1051098</v>
       </c>
-      <c r="G276" s="250" t="s">
+      <c r="G276" s="249" t="s">
         <v>167</v>
       </c>
       <c r="H276" s="162">
@@ -51869,7 +53947,9 @@
       <c r="BI276" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ276" s="31"/>
+      <c r="BJ276" s="31" t="s">
+        <v>1053</v>
+      </c>
     </row>
     <row r="277" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A277" s="131"/>
@@ -51993,7 +54073,9 @@
       <c r="BI277" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ277" s="31"/>
+      <c r="BJ277" s="31" t="s">
+        <v>1054</v>
+      </c>
     </row>
     <row r="278" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A278" s="131"/>
@@ -52115,7 +54197,9 @@
       <c r="BI278" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ278" s="31"/>
+      <c r="BJ278" s="31" t="s">
+        <v>1055</v>
+      </c>
     </row>
     <row r="279" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A279" s="131"/>
@@ -52239,7 +54323,9 @@
       <c r="BI279" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ279" s="31"/>
+      <c r="BJ279" s="31" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="280" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A280" s="131"/>
@@ -52363,7 +54449,9 @@
       <c r="BI280" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ280" s="31"/>
+      <c r="BJ280" s="31" t="s">
+        <v>1057</v>
+      </c>
     </row>
     <row r="281" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A281" s="131"/>
@@ -52487,7 +54575,9 @@
       <c r="BI281" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ281" s="31"/>
+      <c r="BJ281" s="31" t="s">
+        <v>1058</v>
+      </c>
     </row>
     <row r="282" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A282" s="131"/>
@@ -52609,7 +54699,9 @@
       <c r="BI282" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ282" s="31"/>
+      <c r="BJ282" s="31" t="s">
+        <v>1059</v>
+      </c>
     </row>
     <row r="283" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A283" s="131"/>
@@ -52731,7 +54823,9 @@
       <c r="BI283" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ283" s="31"/>
+      <c r="BJ283" s="31" t="s">
+        <v>1060</v>
+      </c>
     </row>
     <row r="284" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A284" s="131"/>
@@ -52853,7 +54947,9 @@
       <c r="BI284" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ284" s="31"/>
+      <c r="BJ284" s="31" t="s">
+        <v>1061</v>
+      </c>
     </row>
     <row r="285" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A285" s="131"/>
@@ -52975,7 +55071,9 @@
       <c r="BI285" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ285" s="31"/>
+      <c r="BJ285" s="31" t="s">
+        <v>1062</v>
+      </c>
     </row>
     <row r="286" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A286" s="131"/>
@@ -53099,7 +55197,9 @@
       <c r="BI286" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ286" s="31"/>
+      <c r="BJ286" s="31" t="s">
+        <v>1063</v>
+      </c>
     </row>
     <row r="287" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A287" s="131"/>
@@ -53219,7 +55319,9 @@
       <c r="BG287" s="174"/>
       <c r="BH287" s="174"/>
       <c r="BI287" s="2"/>
-      <c r="BJ287" s="31"/>
+      <c r="BJ287" s="31" t="s">
+        <v>1064</v>
+      </c>
     </row>
     <row r="288" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A288" s="131"/>
@@ -53343,7 +55445,9 @@
       <c r="BI288" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ288" s="31"/>
+      <c r="BJ288" s="31" t="s">
+        <v>1065</v>
+      </c>
     </row>
     <row r="289" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A289" s="131"/>
@@ -53467,7 +55571,9 @@
       <c r="BI289" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ289" s="31"/>
+      <c r="BJ289" s="31" t="s">
+        <v>1066</v>
+      </c>
     </row>
     <row r="290" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A290" s="131"/>
@@ -53591,7 +55697,9 @@
       <c r="BI290" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ290" s="31"/>
+      <c r="BJ290" s="31" t="s">
+        <v>1067</v>
+      </c>
     </row>
     <row r="291" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A291" s="131"/>
@@ -53713,7 +55821,9 @@
       <c r="BI291" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ291" s="31"/>
+      <c r="BJ291" s="31" t="s">
+        <v>1068</v>
+      </c>
     </row>
     <row r="292" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A292" s="131"/>
@@ -53835,7 +55945,9 @@
       <c r="BI292" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ292" s="31"/>
+      <c r="BJ292" s="31" t="s">
+        <v>1069</v>
+      </c>
     </row>
     <row r="293" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A293" s="131"/>
@@ -53959,7 +56071,9 @@
       <c r="BI293" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ293" s="31"/>
+      <c r="BJ293" s="31" t="s">
+        <v>1070</v>
+      </c>
     </row>
     <row r="294" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A294" s="131"/>
@@ -54083,7 +56197,9 @@
       <c r="BI294" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ294" s="31"/>
+      <c r="BJ294" s="31" t="s">
+        <v>1071</v>
+      </c>
     </row>
     <row r="295" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B295" s="30" t="s">
@@ -54206,7 +56322,9 @@
       <c r="BI295" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ295" s="31"/>
+      <c r="BJ295" s="31" t="s">
+        <v>1072</v>
+      </c>
     </row>
     <row r="296" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B296" s="30" t="s">
@@ -54329,7 +56447,9 @@
       <c r="BI296" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ296" s="31"/>
+      <c r="BJ296" s="31" t="s">
+        <v>1073</v>
+      </c>
     </row>
     <row r="297" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B297" s="30" t="s">
@@ -54448,7 +56568,9 @@
       <c r="BG297" s="71"/>
       <c r="BH297" s="71"/>
       <c r="BI297" s="158"/>
-      <c r="BJ297" s="31"/>
+      <c r="BJ297" s="31" t="s">
+        <v>1074</v>
+      </c>
     </row>
     <row r="298" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B298" s="30" t="s">
@@ -54569,7 +56691,9 @@
       <c r="BI298" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ298" s="31"/>
+      <c r="BJ298" s="31" t="s">
+        <v>1075</v>
+      </c>
     </row>
     <row r="299" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B299" s="30" t="s">
@@ -54690,7 +56814,9 @@
       <c r="BI299" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ299" s="31"/>
+      <c r="BJ299" s="31" t="s">
+        <v>1076</v>
+      </c>
     </row>
     <row r="300" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B300" s="30" t="s">
@@ -54813,7 +56939,9 @@
       <c r="BI300" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ300" s="31"/>
+      <c r="BJ300" s="31" t="s">
+        <v>1077</v>
+      </c>
     </row>
     <row r="301" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B301" s="30" t="s">
@@ -54934,7 +57062,9 @@
       <c r="BI301" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ301" s="31"/>
+      <c r="BJ301" s="31" t="s">
+        <v>1078</v>
+      </c>
     </row>
     <row r="302" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B302" s="30" t="s">
@@ -55055,7 +57185,9 @@
       <c r="BI302" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ302" s="31"/>
+      <c r="BJ302" s="31" t="s">
+        <v>1079</v>
+      </c>
     </row>
     <row r="303" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B303" s="30" t="s">
@@ -55178,7 +57310,9 @@
       <c r="BI303" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ303" s="31"/>
+      <c r="BJ303" s="31" t="s">
+        <v>1080</v>
+      </c>
     </row>
     <row r="304" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B304" s="30" t="s">
@@ -55297,7 +57431,9 @@
       <c r="BG304" s="71"/>
       <c r="BH304" s="71"/>
       <c r="BI304" s="158"/>
-      <c r="BJ304" s="31"/>
+      <c r="BJ304" s="31" t="s">
+        <v>1081</v>
+      </c>
     </row>
     <row r="305" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B305" s="30" t="s">
@@ -55418,7 +57554,9 @@
       <c r="BI305" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ305" s="31"/>
+      <c r="BJ305" s="31" t="s">
+        <v>1082</v>
+      </c>
     </row>
     <row r="306" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B306" s="30" t="s">
@@ -55537,7 +57675,9 @@
       <c r="BG306" s="71"/>
       <c r="BH306" s="71"/>
       <c r="BI306" s="158"/>
-      <c r="BJ306" s="31"/>
+      <c r="BJ306" s="31" t="s">
+        <v>1083</v>
+      </c>
     </row>
     <row r="307" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B307" s="30" t="s">
@@ -55660,7 +57800,9 @@
       <c r="BI307" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ307" s="31"/>
+      <c r="BJ307" s="31" t="s">
+        <v>1084</v>
+      </c>
     </row>
     <row r="308" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B308" s="30" t="s">
@@ -55783,7 +57925,9 @@
       <c r="BI308" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ308" s="31"/>
+      <c r="BJ308" s="31" t="s">
+        <v>1085</v>
+      </c>
     </row>
     <row r="309" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B309" s="30" t="s">
@@ -55904,7 +58048,9 @@
       <c r="BI309" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ309" s="31"/>
+      <c r="BJ309" s="31" t="s">
+        <v>1086</v>
+      </c>
     </row>
     <row r="310" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B310" s="30" t="s">
@@ -56027,7 +58173,9 @@
       <c r="BI310" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ310" s="31"/>
+      <c r="BJ310" s="31" t="s">
+        <v>1087</v>
+      </c>
     </row>
     <row r="311" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B311" s="30" t="s">
@@ -56146,7 +58294,9 @@
       <c r="BG311" s="71"/>
       <c r="BH311" s="71"/>
       <c r="BI311" s="158"/>
-      <c r="BJ311" s="31"/>
+      <c r="BJ311" s="31" t="s">
+        <v>1088</v>
+      </c>
     </row>
     <row r="312" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B312" s="30" t="s">
@@ -56269,7 +58419,9 @@
       <c r="BI312" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ312" s="31"/>
+      <c r="BJ312" s="31" t="s">
+        <v>1089</v>
+      </c>
     </row>
     <row r="313" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B313" s="30" t="s">
@@ -56392,7 +58544,9 @@
       <c r="BI313" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ313" s="31"/>
+      <c r="BJ313" s="31" t="s">
+        <v>1090</v>
+      </c>
     </row>
     <row r="314" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B314" s="30" t="s">
@@ -56515,7 +58669,9 @@
       <c r="BI314" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ314" s="31"/>
+      <c r="BJ314" s="31" t="s">
+        <v>1091</v>
+      </c>
     </row>
     <row r="315" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B315" s="30" t="s">
@@ -56636,7 +58792,9 @@
       <c r="BI315" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ315" s="31"/>
+      <c r="BJ315" s="31" t="s">
+        <v>1092</v>
+      </c>
     </row>
     <row r="316" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B316" s="30" t="s">
@@ -56759,7 +58917,9 @@
       <c r="BI316" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ316" s="31"/>
+      <c r="BJ316" s="31" t="s">
+        <v>1093</v>
+      </c>
     </row>
     <row r="317" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B317" s="30" t="s">
@@ -56878,7 +59038,9 @@
       <c r="BG317" s="71"/>
       <c r="BH317" s="71"/>
       <c r="BI317" s="2"/>
-      <c r="BJ317" s="31"/>
+      <c r="BJ317" s="31" t="s">
+        <v>1094</v>
+      </c>
     </row>
     <row r="318" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B318" s="30" t="s">
@@ -56999,7 +59161,9 @@
       <c r="BI318" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ318" s="31"/>
+      <c r="BJ318" s="31" t="s">
+        <v>1095</v>
+      </c>
     </row>
     <row r="319" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B319" s="30" t="s">
@@ -57122,7 +59286,9 @@
       <c r="BI319" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ319" s="31"/>
+      <c r="BJ319" s="31" t="s">
+        <v>1096</v>
+      </c>
     </row>
     <row r="320" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B320" s="30" t="s">
@@ -57241,7 +59407,9 @@
       <c r="BG320" s="71"/>
       <c r="BH320" s="71"/>
       <c r="BI320" s="158"/>
-      <c r="BJ320" s="31"/>
+      <c r="BJ320" s="31" t="s">
+        <v>1097</v>
+      </c>
     </row>
     <row r="321" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B321" s="30" t="s">
@@ -57360,7 +59528,9 @@
       <c r="BG321" s="152"/>
       <c r="BH321" s="152"/>
       <c r="BI321" s="158"/>
-      <c r="BJ321" s="31"/>
+      <c r="BJ321" s="31" t="s">
+        <v>1098</v>
+      </c>
     </row>
     <row r="322" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B322" s="30" t="s">
@@ -57481,7 +59651,9 @@
       <c r="BI322" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ322" s="31"/>
+      <c r="BJ322" s="31" t="s">
+        <v>1099</v>
+      </c>
     </row>
     <row r="323" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B323" s="30" t="s">
@@ -57604,7 +59776,9 @@
       <c r="BI323" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ323" s="31"/>
+      <c r="BJ323" s="31" t="s">
+        <v>1100</v>
+      </c>
     </row>
     <row r="324" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B324" s="30" t="s">
@@ -57723,7 +59897,9 @@
       <c r="BG324" s="71"/>
       <c r="BH324" s="71"/>
       <c r="BI324" s="158"/>
-      <c r="BJ324" s="31"/>
+      <c r="BJ324" s="31" t="s">
+        <v>1101</v>
+      </c>
     </row>
     <row r="325" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B325" s="30" t="s">
@@ -57844,7 +60020,9 @@
       <c r="BI325" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ325" s="31"/>
+      <c r="BJ325" s="31" t="s">
+        <v>1102</v>
+      </c>
     </row>
     <row r="326" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B326" s="30" t="s">
@@ -57965,7 +60143,9 @@
       <c r="BI326" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ326" s="31"/>
+      <c r="BJ326" s="31" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="327" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B327" s="30" t="s">
@@ -58084,7 +60264,9 @@
       <c r="BG327" s="71"/>
       <c r="BH327" s="71"/>
       <c r="BI327" s="158"/>
-      <c r="BJ327" s="31"/>
+      <c r="BJ327" s="31" t="s">
+        <v>1104</v>
+      </c>
     </row>
     <row r="328" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B328" s="30" t="s">
@@ -58203,7 +60385,9 @@
       <c r="BG328" s="71"/>
       <c r="BH328" s="71"/>
       <c r="BI328" s="158"/>
-      <c r="BJ328" s="31"/>
+      <c r="BJ328" s="31" t="s">
+        <v>1105</v>
+      </c>
     </row>
     <row r="329" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B329" s="30" t="s">
@@ -58322,7 +60506,9 @@
       <c r="BG329" s="71"/>
       <c r="BH329" s="71"/>
       <c r="BI329" s="158"/>
-      <c r="BJ329" s="31"/>
+      <c r="BJ329" s="31" t="s">
+        <v>1106</v>
+      </c>
     </row>
     <row r="330" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B330" s="30" t="s">
@@ -58441,7 +60627,9 @@
       <c r="BG330" s="71"/>
       <c r="BH330" s="71"/>
       <c r="BI330" s="158"/>
-      <c r="BJ330" s="31"/>
+      <c r="BJ330" s="31" t="s">
+        <v>1107</v>
+      </c>
     </row>
     <row r="331" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B331" s="30" t="s">
@@ -58564,7 +60752,9 @@
       <c r="BI331" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ331" s="31"/>
+      <c r="BJ331" s="31" t="s">
+        <v>1108</v>
+      </c>
     </row>
     <row r="332" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B332" s="30" t="s">
@@ -58687,7 +60877,9 @@
       <c r="BI332" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ332" s="31"/>
+      <c r="BJ332" s="31" t="s">
+        <v>1109</v>
+      </c>
     </row>
     <row r="333" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B333" s="30" t="s">
@@ -58810,7 +61002,9 @@
       <c r="BI333" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ333" s="31"/>
+      <c r="BJ333" s="31" t="s">
+        <v>1110</v>
+      </c>
     </row>
     <row r="334" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B334" s="30" t="s">
@@ -58933,7 +61127,9 @@
       <c r="BI334" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ334" s="31"/>
+      <c r="BJ334" s="31" t="s">
+        <v>1111</v>
+      </c>
     </row>
     <row r="335" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B335" s="30" t="s">
@@ -59056,7 +61252,9 @@
       <c r="BI335" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ335" s="31"/>
+      <c r="BJ335" s="31" t="s">
+        <v>1112</v>
+      </c>
     </row>
     <row r="336" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B336" s="30" t="s">
@@ -59179,7 +61377,9 @@
       <c r="BI336" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ336" s="31"/>
+      <c r="BJ336" s="31" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="337" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B337" s="30" t="s">
@@ -59302,7 +61502,9 @@
       <c r="BI337" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ337" s="31"/>
+      <c r="BJ337" s="31" t="s">
+        <v>1114</v>
+      </c>
     </row>
     <row r="338" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B338" s="30" t="s">
@@ -59423,7 +61625,9 @@
       <c r="BI338" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ338" s="31"/>
+      <c r="BJ338" s="31" t="s">
+        <v>1115</v>
+      </c>
     </row>
     <row r="339" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B339" s="30" t="s">
@@ -59544,7 +61748,9 @@
       <c r="BI339" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ339" s="31"/>
+      <c r="BJ339" s="31" t="s">
+        <v>1116</v>
+      </c>
     </row>
     <row r="340" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B340" s="30" t="s">
@@ -59667,7 +61873,9 @@
       <c r="BI340" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ340" s="31"/>
+      <c r="BJ340" s="31" t="s">
+        <v>1117</v>
+      </c>
     </row>
     <row r="341" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B341" s="30" t="s">
@@ -59788,7 +61996,9 @@
       <c r="BI341" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ341" s="31"/>
+      <c r="BJ341" s="31" t="s">
+        <v>1118</v>
+      </c>
     </row>
     <row r="342" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B342" s="30" t="s">
@@ -59909,7 +62119,9 @@
       <c r="BI342" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ342" s="31"/>
+      <c r="BJ342" s="31" t="s">
+        <v>1119</v>
+      </c>
     </row>
     <row r="343" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B343" s="30" t="s">
@@ -60030,7 +62242,9 @@
       <c r="BI343" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ343" s="31"/>
+      <c r="BJ343" s="31" t="s">
+        <v>1120</v>
+      </c>
     </row>
     <row r="344" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B344" s="30" t="s">
@@ -60153,7 +62367,9 @@
       <c r="BI344" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ344" s="31"/>
+      <c r="BJ344" s="31" t="s">
+        <v>1121</v>
+      </c>
     </row>
     <row r="345" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B345" s="30" t="s">
@@ -60276,7 +62492,9 @@
       <c r="BI345" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ345" s="31"/>
+      <c r="BJ345" s="31" t="s">
+        <v>1122</v>
+      </c>
     </row>
     <row r="346" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B346" s="30" t="s">
@@ -60399,7 +62617,9 @@
       <c r="BI346" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ346" s="31"/>
+      <c r="BJ346" s="31" t="s">
+        <v>1123</v>
+      </c>
     </row>
     <row r="347" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B347" s="30" t="s">
@@ -60522,7 +62742,9 @@
       <c r="BI347" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ347" s="31"/>
+      <c r="BJ347" s="31" t="s">
+        <v>1124</v>
+      </c>
     </row>
     <row r="348" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B348" s="30" t="s">
@@ -60645,7 +62867,9 @@
       <c r="BI348" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ348" s="31"/>
+      <c r="BJ348" s="31" t="s">
+        <v>1125</v>
+      </c>
     </row>
     <row r="349" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B349" s="30" t="s">
@@ -60768,7 +62992,9 @@
       <c r="BI349" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ349" s="31"/>
+      <c r="BJ349" s="31" t="s">
+        <v>1126</v>
+      </c>
     </row>
     <row r="350" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B350" s="30" t="s">
@@ -60891,7 +63117,9 @@
       <c r="BI350" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ350" s="31"/>
+      <c r="BJ350" s="31" t="s">
+        <v>1127</v>
+      </c>
     </row>
     <row r="351" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B351" s="30" t="s">
@@ -61014,7 +63242,9 @@
       <c r="BI351" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ351" s="31"/>
+      <c r="BJ351" s="31" t="s">
+        <v>1128</v>
+      </c>
     </row>
     <row r="352" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B352" s="30" t="s">
@@ -61135,7 +63365,9 @@
       <c r="BI352" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ352" s="31"/>
+      <c r="BJ352" s="31" t="s">
+        <v>1129</v>
+      </c>
     </row>
     <row r="353" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B353" s="30" t="s">
@@ -61258,7 +63490,9 @@
       <c r="BI353" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ353" s="31"/>
+      <c r="BJ353" s="31" t="s">
+        <v>1130</v>
+      </c>
     </row>
     <row r="354" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B354" s="30" t="s">
@@ -61379,7 +63613,9 @@
       <c r="BI354" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ354" s="31"/>
+      <c r="BJ354" s="31" t="s">
+        <v>1131</v>
+      </c>
     </row>
     <row r="355" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B355" s="30" t="s">
@@ -61502,7 +63738,9 @@
       <c r="BI355" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ355" s="31"/>
+      <c r="BJ355" s="31" t="s">
+        <v>1132</v>
+      </c>
     </row>
     <row r="356" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B356" s="30" t="s">
@@ -61625,7 +63863,9 @@
       <c r="BI356" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ356" s="31"/>
+      <c r="BJ356" s="31" t="s">
+        <v>1133</v>
+      </c>
     </row>
     <row r="357" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B357" s="30" t="s">
@@ -61748,7 +63988,9 @@
       <c r="BI357" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ357" s="31"/>
+      <c r="BJ357" s="31" t="s">
+        <v>1134</v>
+      </c>
     </row>
     <row r="358" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B358" s="30" t="s">
@@ -61871,7 +64113,9 @@
       <c r="BI358" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ358" s="31"/>
+      <c r="BJ358" s="31" t="s">
+        <v>1135</v>
+      </c>
     </row>
     <row r="359" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B359" s="30" t="s">
@@ -61992,7 +64236,9 @@
       <c r="BI359" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ359" s="31"/>
+      <c r="BJ359" s="31" t="s">
+        <v>1136</v>
+      </c>
     </row>
     <row r="360" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B360" s="30" t="s">
@@ -62115,7 +64361,9 @@
       <c r="BI360" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ360" s="31"/>
+      <c r="BJ360" s="31" t="s">
+        <v>1137</v>
+      </c>
     </row>
     <row r="361" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B361" s="30" t="s">
@@ -62236,7 +64484,9 @@
       <c r="BI361" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ361" s="31"/>
+      <c r="BJ361" s="31" t="s">
+        <v>1138</v>
+      </c>
     </row>
     <row r="362" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B362" s="30" t="s">
@@ -62359,7 +64609,9 @@
       <c r="BI362" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ362" s="31"/>
+      <c r="BJ362" s="31" t="s">
+        <v>1139</v>
+      </c>
     </row>
     <row r="363" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B363" s="30" t="s">
@@ -62482,7 +64734,9 @@
       <c r="BI363" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ363" s="31"/>
+      <c r="BJ363" s="31" t="s">
+        <v>1140</v>
+      </c>
     </row>
     <row r="364" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B364" s="30" t="s">
@@ -62601,7 +64855,9 @@
       <c r="BG364" s="71"/>
       <c r="BH364" s="71"/>
       <c r="BI364" s="2"/>
-      <c r="BJ364" s="31"/>
+      <c r="BJ364" s="31" t="s">
+        <v>1141</v>
+      </c>
     </row>
     <row r="365" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B365" s="30" t="s">
@@ -62724,7 +64980,9 @@
       <c r="BI365" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ365" s="31"/>
+      <c r="BJ365" s="31" t="s">
+        <v>1142</v>
+      </c>
     </row>
     <row r="366" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B366" s="30" t="s">
@@ -62847,7 +65105,9 @@
       <c r="BI366" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ366" s="31"/>
+      <c r="BJ366" s="31" t="s">
+        <v>1143</v>
+      </c>
     </row>
     <row r="367" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B367" s="30" t="s">
@@ -62970,7 +65230,9 @@
       <c r="BI367" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ367" s="31"/>
+      <c r="BJ367" s="31" t="s">
+        <v>1144</v>
+      </c>
     </row>
     <row r="368" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B368" s="30" t="s">
@@ -63093,7 +65355,9 @@
       <c r="BI368" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ368" s="31"/>
+      <c r="BJ368" s="31" t="s">
+        <v>1145</v>
+      </c>
     </row>
     <row r="369" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B369" s="30" t="s">
@@ -63216,7 +65480,9 @@
       <c r="BI369" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ369" s="31"/>
+      <c r="BJ369" s="31" t="s">
+        <v>1146</v>
+      </c>
     </row>
     <row r="370" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B370" s="30" t="s">
@@ -63339,7 +65605,9 @@
       <c r="BI370" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ370" s="31"/>
+      <c r="BJ370" s="31" t="s">
+        <v>1147</v>
+      </c>
     </row>
     <row r="371" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B371" s="30" t="s">
@@ -63460,7 +65728,9 @@
       <c r="BI371" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ371" s="31"/>
+      <c r="BJ371" s="31" t="s">
+        <v>1148</v>
+      </c>
     </row>
     <row r="372" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B372" s="30" t="s">
@@ -63583,7 +65853,9 @@
       <c r="BI372" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ372" s="31"/>
+      <c r="BJ372" s="31" t="s">
+        <v>1149</v>
+      </c>
     </row>
     <row r="373" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B373" s="30" t="s">
@@ -63706,7 +65978,9 @@
       <c r="BI373" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="BJ373" s="31"/>
+      <c r="BJ373" s="31" t="s">
+        <v>1150</v>
+      </c>
     </row>
     <row r="374" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B374" s="30" t="s">
@@ -63829,7 +66103,9 @@
       <c r="BI374" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ374" s="31"/>
+      <c r="BJ374" s="31" t="s">
+        <v>1151</v>
+      </c>
     </row>
     <row r="375" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B375" s="30" t="s">
@@ -63952,7 +66228,9 @@
       <c r="BI375" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ375" s="31"/>
+      <c r="BJ375" s="31" t="s">
+        <v>1152</v>
+      </c>
     </row>
     <row r="376" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B376" s="30" t="s">
@@ -64075,7 +66353,9 @@
       <c r="BI376" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ376" s="31"/>
+      <c r="BJ376" s="31" t="s">
+        <v>1153</v>
+      </c>
     </row>
     <row r="377" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B377" s="30" t="s">
@@ -64198,7 +66478,9 @@
       <c r="BI377" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ377" s="31"/>
+      <c r="BJ377" s="31" t="s">
+        <v>1154</v>
+      </c>
     </row>
     <row r="378" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B378" s="30" t="s">
@@ -64321,7 +66603,9 @@
       <c r="BI378" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ378" s="31"/>
+      <c r="BJ378" s="31" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="379" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B379" s="30" t="s">
@@ -64444,7 +66728,9 @@
       <c r="BI379" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ379" s="31"/>
+      <c r="BJ379" s="31" t="s">
+        <v>1156</v>
+      </c>
     </row>
     <row r="380" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B380" s="30" t="s">
@@ -64567,7 +66853,9 @@
       <c r="BI380" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ380" s="31"/>
+      <c r="BJ380" s="31" t="s">
+        <v>1157</v>
+      </c>
     </row>
     <row r="381" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B381" s="30" t="s">
@@ -64690,7 +66978,9 @@
       <c r="BI381" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ381" s="31"/>
+      <c r="BJ381" s="31" t="s">
+        <v>1158</v>
+      </c>
     </row>
     <row r="382" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B382" s="30" t="s">
@@ -64813,7 +67103,9 @@
       <c r="BI382" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ382" s="31"/>
+      <c r="BJ382" s="31" t="s">
+        <v>1159</v>
+      </c>
     </row>
     <row r="383" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B383" s="30" t="s">
@@ -64936,7 +67228,9 @@
       <c r="BI383" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ383" s="31"/>
+      <c r="BJ383" s="31" t="s">
+        <v>1160</v>
+      </c>
     </row>
     <row r="384" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B384" s="30" t="s">
@@ -65059,7 +67353,9 @@
       <c r="BI384" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ384" s="31"/>
+      <c r="BJ384" s="31" t="s">
+        <v>1161</v>
+      </c>
     </row>
     <row r="385" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B385" s="30" t="s">
@@ -65182,7 +67478,9 @@
       <c r="BI385" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ385" s="31"/>
+      <c r="BJ385" s="31" t="s">
+        <v>1162</v>
+      </c>
     </row>
     <row r="386" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B386" s="30" t="s">
@@ -65305,7 +67603,9 @@
       <c r="BI386" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ386" s="31"/>
+      <c r="BJ386" s="31" t="s">
+        <v>1163</v>
+      </c>
     </row>
     <row r="387" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B387" s="30" t="s">
@@ -65428,7 +67728,9 @@
       <c r="BI387" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ387" s="31"/>
+      <c r="BJ387" s="31" t="s">
+        <v>1164</v>
+      </c>
     </row>
     <row r="388" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B388" s="30" t="s">
@@ -65551,7 +67853,9 @@
       <c r="BI388" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ388" s="31"/>
+      <c r="BJ388" s="31" t="s">
+        <v>1165</v>
+      </c>
     </row>
     <row r="389" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B389" s="30" t="s">
@@ -65674,7 +67978,9 @@
       <c r="BI389" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ389" s="31"/>
+      <c r="BJ389" s="31" t="s">
+        <v>1166</v>
+      </c>
     </row>
     <row r="390" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B390" s="30" t="s">
@@ -65797,7 +68103,9 @@
       <c r="BI390" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ390" s="31"/>
+      <c r="BJ390" s="31" t="s">
+        <v>1167</v>
+      </c>
     </row>
     <row r="391" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B391" s="30" t="s">
@@ -65920,7 +68228,9 @@
       <c r="BI391" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ391" s="31"/>
+      <c r="BJ391" s="31" t="s">
+        <v>1168</v>
+      </c>
     </row>
     <row r="392" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B392" s="30" t="s">
@@ -66043,7 +68353,9 @@
       <c r="BI392" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ392" s="31"/>
+      <c r="BJ392" s="31" t="s">
+        <v>1169</v>
+      </c>
     </row>
     <row r="393" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B393" s="30" t="s">
@@ -66166,7 +68478,9 @@
       <c r="BI393" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ393" s="31"/>
+      <c r="BJ393" s="31" t="s">
+        <v>1170</v>
+      </c>
     </row>
     <row r="394" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B394" s="30" t="s">
@@ -66289,7 +68603,9 @@
       <c r="BI394" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ394" s="31"/>
+      <c r="BJ394" s="31" t="s">
+        <v>1171</v>
+      </c>
     </row>
     <row r="395" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B395" s="30" t="s">
@@ -66412,7 +68728,9 @@
       <c r="BI395" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ395" s="31"/>
+      <c r="BJ395" s="31" t="s">
+        <v>1172</v>
+      </c>
     </row>
     <row r="396" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B396" s="30" t="s">
@@ -66535,7 +68853,9 @@
       <c r="BI396" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ396" s="31"/>
+      <c r="BJ396" s="31" t="s">
+        <v>1173</v>
+      </c>
     </row>
     <row r="397" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B397" s="30" t="s">
@@ -66658,7 +68978,9 @@
       <c r="BI397" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ397" s="31"/>
+      <c r="BJ397" s="31" t="s">
+        <v>1174</v>
+      </c>
     </row>
     <row r="398" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B398" s="30" t="s">
@@ -66781,7 +69103,9 @@
       <c r="BI398" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ398" s="31"/>
+      <c r="BJ398" s="31" t="s">
+        <v>1175</v>
+      </c>
     </row>
     <row r="399" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B399" s="30" t="s">
@@ -66904,7 +69228,9 @@
       <c r="BI399" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ399" s="31"/>
+      <c r="BJ399" s="31" t="s">
+        <v>1176</v>
+      </c>
     </row>
     <row r="400" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B400" s="30" t="s">
@@ -67027,7 +69353,9 @@
       <c r="BI400" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ400" s="31"/>
+      <c r="BJ400" s="31" t="s">
+        <v>1177</v>
+      </c>
     </row>
     <row r="401" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B401" s="30" t="s">
@@ -67150,7 +69478,9 @@
       <c r="BI401" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ401" s="31"/>
+      <c r="BJ401" s="31" t="s">
+        <v>1178</v>
+      </c>
     </row>
     <row r="402" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B402" s="30" t="s">
@@ -67273,7 +69603,9 @@
       <c r="BI402" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ402" s="31"/>
+      <c r="BJ402" s="31" t="s">
+        <v>1179</v>
+      </c>
     </row>
     <row r="403" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B403" s="30" t="s">
@@ -67396,7 +69728,9 @@
       <c r="BI403" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ403" s="31"/>
+      <c r="BJ403" s="31" t="s">
+        <v>1180</v>
+      </c>
     </row>
     <row r="404" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B404" s="30" t="s">
@@ -67519,7 +69853,9 @@
       <c r="BI404" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ404" s="31"/>
+      <c r="BJ404" s="31" t="s">
+        <v>1181</v>
+      </c>
     </row>
     <row r="405" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B405" s="30" t="s">
@@ -67642,7 +69978,9 @@
       <c r="BI405" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ405" s="31"/>
+      <c r="BJ405" s="31" t="s">
+        <v>1182</v>
+      </c>
     </row>
     <row r="406" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B406" s="30" t="s">
@@ -67763,7 +70101,9 @@
       <c r="BI406" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ406" s="31"/>
+      <c r="BJ406" s="31" t="s">
+        <v>1183</v>
+      </c>
     </row>
     <row r="407" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B407" s="30" t="s">
@@ -67886,7 +70226,9 @@
       <c r="BI407" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ407" s="31"/>
+      <c r="BJ407" s="31" t="s">
+        <v>1184</v>
+      </c>
     </row>
     <row r="408" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B408" s="30" t="s">
@@ -68007,7 +70349,9 @@
       <c r="BI408" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ408" s="31"/>
+      <c r="BJ408" s="31" t="s">
+        <v>1185</v>
+      </c>
     </row>
     <row r="409" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B409" s="30" t="s">
@@ -68128,7 +70472,9 @@
       <c r="BI409" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ409" s="31"/>
+      <c r="BJ409" s="31" t="s">
+        <v>1186</v>
+      </c>
     </row>
     <row r="410" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B410" s="30" t="s">
@@ -68251,7 +70597,9 @@
       <c r="BI410" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ410" s="31"/>
+      <c r="BJ410" s="31" t="s">
+        <v>1187</v>
+      </c>
     </row>
     <row r="411" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B411" s="30" t="s">
@@ -68374,7 +70722,9 @@
       <c r="BI411" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ411" s="31"/>
+      <c r="BJ411" s="31" t="s">
+        <v>1188</v>
+      </c>
     </row>
     <row r="412" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B412" s="30" t="s">
@@ -68495,7 +70845,9 @@
       <c r="BI412" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ412" s="31"/>
+      <c r="BJ412" s="31" t="s">
+        <v>1189</v>
+      </c>
     </row>
     <row r="413" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B413" s="30" t="s">
@@ -68618,7 +70970,9 @@
       <c r="BI413" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ413" s="31"/>
+      <c r="BJ413" s="31" t="s">
+        <v>1190</v>
+      </c>
     </row>
     <row r="414" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B414" s="30" t="s">
@@ -68741,7 +71095,9 @@
       <c r="BI414" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ414" s="31"/>
+      <c r="BJ414" s="31" t="s">
+        <v>1191</v>
+      </c>
     </row>
     <row r="415" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B415" s="30" t="s">
@@ -68864,7 +71220,9 @@
       <c r="BI415" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ415" s="31"/>
+      <c r="BJ415" s="31" t="s">
+        <v>1192</v>
+      </c>
     </row>
     <row r="416" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B416" s="30" t="s">
@@ -68985,7 +71343,9 @@
       <c r="BI416" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ416" s="31"/>
+      <c r="BJ416" s="31" t="s">
+        <v>1193</v>
+      </c>
     </row>
     <row r="417" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B417" s="30" t="s">
@@ -69108,7 +71468,9 @@
       <c r="BI417" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ417" s="31"/>
+      <c r="BJ417" s="31" t="s">
+        <v>1194</v>
+      </c>
     </row>
     <row r="418" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B418" s="30" t="s">
@@ -69231,7 +71593,9 @@
       <c r="BI418" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ418" s="31"/>
+      <c r="BJ418" s="31" t="s">
+        <v>1195</v>
+      </c>
     </row>
     <row r="419" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B419" s="30" t="s">
@@ -69352,7 +71716,9 @@
       <c r="BI419" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ419" s="31"/>
+      <c r="BJ419" s="31" t="s">
+        <v>1196</v>
+      </c>
     </row>
     <row r="420" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B420" s="30" t="s">
@@ -69475,7 +71841,9 @@
       <c r="BI420" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ420" s="31"/>
+      <c r="BJ420" s="31" t="s">
+        <v>1197</v>
+      </c>
     </row>
     <row r="421" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B421" s="30" t="s">
@@ -69598,7 +71966,9 @@
       <c r="BI421" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ421" s="31"/>
+      <c r="BJ421" s="31" t="s">
+        <v>1198</v>
+      </c>
     </row>
     <row r="422" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B422" s="30" t="s">
@@ -69721,7 +72091,9 @@
       <c r="BI422" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ422" s="31"/>
+      <c r="BJ422" s="31" t="s">
+        <v>1199</v>
+      </c>
     </row>
     <row r="423" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B423" s="30" t="s">
@@ -69844,7 +72216,9 @@
       <c r="BI423" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ423" s="31"/>
+      <c r="BJ423" s="31" t="s">
+        <v>1200</v>
+      </c>
     </row>
     <row r="424" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B424" s="30" t="s">
@@ -69967,7 +72341,9 @@
       <c r="BI424" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ424" s="31"/>
+      <c r="BJ424" s="31" t="s">
+        <v>1201</v>
+      </c>
     </row>
     <row r="425" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B425" s="30" t="s">
@@ -70088,7 +72464,9 @@
       <c r="BI425" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ425" s="31"/>
+      <c r="BJ425" s="31" t="s">
+        <v>1202</v>
+      </c>
     </row>
     <row r="426" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B426" s="30" t="s">
@@ -70211,7 +72589,9 @@
       <c r="BI426" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ426" s="31"/>
+      <c r="BJ426" s="31" t="s">
+        <v>1203</v>
+      </c>
     </row>
     <row r="427" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B427" s="30" t="s">
@@ -70334,7 +72714,9 @@
       <c r="BI427" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ427" s="31"/>
+      <c r="BJ427" s="31" t="s">
+        <v>1204</v>
+      </c>
     </row>
     <row r="428" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B428" s="30" t="s">
@@ -70457,7 +72839,9 @@
       <c r="BI428" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ428" s="31"/>
+      <c r="BJ428" s="31" t="s">
+        <v>1205</v>
+      </c>
     </row>
     <row r="429" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B429" s="30" t="s">
@@ -70580,7 +72964,9 @@
       <c r="BI429" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ429" s="31"/>
+      <c r="BJ429" s="31" t="s">
+        <v>1206</v>
+      </c>
     </row>
     <row r="430" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B430" s="30" t="s">
@@ -70703,7 +73089,9 @@
       <c r="BI430" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ430" s="31"/>
+      <c r="BJ430" s="31" t="s">
+        <v>1207</v>
+      </c>
     </row>
     <row r="431" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B431" s="30" t="s">
@@ -70826,7 +73214,9 @@
       <c r="BI431" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ431" s="31"/>
+      <c r="BJ431" s="31" t="s">
+        <v>1208</v>
+      </c>
     </row>
     <row r="432" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B432" s="30" t="s">
@@ -70949,7 +73339,9 @@
       <c r="BI432" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ432" s="31"/>
+      <c r="BJ432" s="31" t="s">
+        <v>1209</v>
+      </c>
     </row>
     <row r="433" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B433" s="30" t="s">
@@ -71072,7 +73464,9 @@
       <c r="BI433" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ433" s="31"/>
+      <c r="BJ433" s="31" t="s">
+        <v>1210</v>
+      </c>
     </row>
     <row r="434" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B434" s="30" t="s">
@@ -71195,7 +73589,9 @@
       <c r="BI434" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ434" s="31"/>
+      <c r="BJ434" s="31" t="s">
+        <v>1211</v>
+      </c>
     </row>
     <row r="435" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B435" s="30" t="s">
@@ -71318,7 +73714,9 @@
       <c r="BI435" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ435" s="31"/>
+      <c r="BJ435" s="31" t="s">
+        <v>1212</v>
+      </c>
     </row>
     <row r="436" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B436" s="30" t="s">
@@ -71441,7 +73839,9 @@
       <c r="BI436" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ436" s="31"/>
+      <c r="BJ436" s="31" t="s">
+        <v>1213</v>
+      </c>
     </row>
     <row r="437" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B437" s="30" t="s">
@@ -71564,7 +73964,9 @@
       <c r="BI437" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ437" s="31"/>
+      <c r="BJ437" s="31" t="s">
+        <v>1214</v>
+      </c>
     </row>
     <row r="438" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B438" s="30" t="s">
@@ -71687,7 +74089,9 @@
       <c r="BI438" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ438" s="31"/>
+      <c r="BJ438" s="31" t="s">
+        <v>1215</v>
+      </c>
     </row>
     <row r="439" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B439" s="30" t="s">
@@ -71810,7 +74214,9 @@
       <c r="BI439" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ439" s="31"/>
+      <c r="BJ439" s="31" t="s">
+        <v>1216</v>
+      </c>
     </row>
     <row r="440" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B440" s="30" t="s">
@@ -71933,7 +74339,9 @@
       <c r="BI440" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ440" s="31"/>
+      <c r="BJ440" s="31" t="s">
+        <v>1217</v>
+      </c>
     </row>
     <row r="441" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B441" s="30" t="s">
@@ -72056,7 +74464,9 @@
       <c r="BI441" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ441" s="31"/>
+      <c r="BJ441" s="31" t="s">
+        <v>1218</v>
+      </c>
     </row>
     <row r="442" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B442" s="30" t="s">
@@ -72179,7 +74589,9 @@
       <c r="BI442" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ442" s="31"/>
+      <c r="BJ442" s="31" t="s">
+        <v>1219</v>
+      </c>
     </row>
     <row r="443" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B443" s="30" t="s">
@@ -72302,7 +74714,9 @@
       <c r="BI443" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ443" s="31"/>
+      <c r="BJ443" s="31" t="s">
+        <v>1220</v>
+      </c>
     </row>
     <row r="444" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B444" s="30" t="s">
@@ -72425,7 +74839,9 @@
       <c r="BI444" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ444" s="31"/>
+      <c r="BJ444" s="31" t="s">
+        <v>1221</v>
+      </c>
     </row>
     <row r="445" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B445" s="30" t="s">
@@ -72548,7 +74964,9 @@
       <c r="BI445" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ445" s="31"/>
+      <c r="BJ445" s="31" t="s">
+        <v>1222</v>
+      </c>
     </row>
     <row r="446" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B446" s="30" t="s">
@@ -72671,7 +75089,9 @@
       <c r="BI446" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ446" s="31"/>
+      <c r="BJ446" s="31" t="s">
+        <v>1223</v>
+      </c>
     </row>
     <row r="447" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B447" s="30" t="s">
@@ -72794,7 +75214,9 @@
       <c r="BI447" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ447" s="31"/>
+      <c r="BJ447" s="31" t="s">
+        <v>1224</v>
+      </c>
     </row>
     <row r="448" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B448" s="30" t="s">
@@ -72917,7 +75339,9 @@
       <c r="BI448" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ448" s="31"/>
+      <c r="BJ448" s="31" t="s">
+        <v>1225</v>
+      </c>
     </row>
     <row r="449" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B449" s="30" t="s">
@@ -73040,7 +75464,9 @@
       <c r="BI449" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ449" s="31"/>
+      <c r="BJ449" s="31" t="s">
+        <v>1226</v>
+      </c>
     </row>
     <row r="450" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B450" s="30" t="s">
@@ -73163,7 +75589,9 @@
       <c r="BI450" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ450" s="31"/>
+      <c r="BJ450" s="31" t="s">
+        <v>1227</v>
+      </c>
     </row>
     <row r="451" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B451" s="30" t="s">
@@ -73286,7 +75714,9 @@
       <c r="BI451" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ451" s="31"/>
+      <c r="BJ451" s="31" t="s">
+        <v>1228</v>
+      </c>
     </row>
     <row r="452" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B452" s="30" t="s">
@@ -73409,7 +75839,9 @@
       <c r="BI452" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ452" s="31"/>
+      <c r="BJ452" s="31" t="s">
+        <v>1229</v>
+      </c>
     </row>
     <row r="453" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B453" s="30" t="s">
@@ -73532,7 +75964,9 @@
       <c r="BI453" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ453" s="31"/>
+      <c r="BJ453" s="31" t="s">
+        <v>1230</v>
+      </c>
     </row>
     <row r="454" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B454" s="30" t="s">
@@ -73655,7 +76089,9 @@
       <c r="BI454" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ454" s="31"/>
+      <c r="BJ454" s="31" t="s">
+        <v>1231</v>
+      </c>
     </row>
     <row r="455" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B455" s="30" t="s">
@@ -73778,7 +76214,9 @@
       <c r="BI455" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ455" s="31"/>
+      <c r="BJ455" s="31" t="s">
+        <v>1232</v>
+      </c>
     </row>
     <row r="456" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B456" s="30" t="s">
@@ -73901,7 +76339,9 @@
       <c r="BI456" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ456" s="31"/>
+      <c r="BJ456" s="31" t="s">
+        <v>1233</v>
+      </c>
     </row>
     <row r="457" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B457" s="30" t="s">
@@ -74024,7 +76464,9 @@
       <c r="BI457" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ457" s="31"/>
+      <c r="BJ457" s="31" t="s">
+        <v>1234</v>
+      </c>
     </row>
     <row r="458" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B458" s="30" t="s">
@@ -74147,7 +76589,9 @@
       <c r="BI458" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ458" s="31"/>
+      <c r="BJ458" s="31" t="s">
+        <v>1235</v>
+      </c>
     </row>
     <row r="459" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B459" s="30" t="s">
@@ -74270,7 +76714,9 @@
       <c r="BI459" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ459" s="31"/>
+      <c r="BJ459" s="31" t="s">
+        <v>1236</v>
+      </c>
     </row>
     <row r="460" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B460" s="30" t="s">
@@ -74393,7 +76839,9 @@
       <c r="BI460" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ460" s="31"/>
+      <c r="BJ460" s="31" t="s">
+        <v>1237</v>
+      </c>
     </row>
     <row r="461" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B461" s="30" t="s">
@@ -74516,7 +76964,9 @@
       <c r="BI461" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ461" s="31"/>
+      <c r="BJ461" s="31" t="s">
+        <v>1238</v>
+      </c>
     </row>
     <row r="462" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B462" s="30" t="s">
@@ -74639,7 +77089,9 @@
       <c r="BI462" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ462" s="31"/>
+      <c r="BJ462" s="31" t="s">
+        <v>1239</v>
+      </c>
     </row>
     <row r="463" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B463" s="30" t="s">
@@ -74762,7 +77214,9 @@
       <c r="BI463" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ463" s="31"/>
+      <c r="BJ463" s="31" t="s">
+        <v>1240</v>
+      </c>
     </row>
     <row r="464" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B464" s="30" t="s">
@@ -74885,7 +77339,9 @@
       <c r="BI464" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ464" s="31"/>
+      <c r="BJ464" s="31" t="s">
+        <v>1241</v>
+      </c>
     </row>
     <row r="465" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B465" s="30" t="s">
@@ -75008,7 +77464,9 @@
       <c r="BI465" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ465" s="31"/>
+      <c r="BJ465" s="31" t="s">
+        <v>1242</v>
+      </c>
     </row>
     <row r="466" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B466" s="30" t="s">
@@ -75131,7 +77589,9 @@
       <c r="BI466" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ466" s="31"/>
+      <c r="BJ466" s="31" t="s">
+        <v>1243</v>
+      </c>
     </row>
     <row r="467" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B467" s="30" t="s">
@@ -75254,7 +77714,9 @@
       <c r="BI467" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ467" s="31"/>
+      <c r="BJ467" s="31" t="s">
+        <v>1244</v>
+      </c>
     </row>
     <row r="468" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B468" s="30" t="s">
@@ -75377,7 +77839,9 @@
       <c r="BI468" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ468" s="31"/>
+      <c r="BJ468" s="31" t="s">
+        <v>1245</v>
+      </c>
     </row>
     <row r="469" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B469" s="30" t="s">
@@ -75500,7 +77964,9 @@
       <c r="BI469" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ469" s="31"/>
+      <c r="BJ469" s="31" t="s">
+        <v>1246</v>
+      </c>
     </row>
     <row r="470" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B470" s="30" t="s">
@@ -75623,7 +78089,9 @@
       <c r="BI470" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ470" s="31"/>
+      <c r="BJ470" s="31" t="s">
+        <v>1247</v>
+      </c>
     </row>
     <row r="471" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B471" s="30" t="s">
@@ -75746,7 +78214,9 @@
       <c r="BI471" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ471" s="31"/>
+      <c r="BJ471" s="31" t="s">
+        <v>1248</v>
+      </c>
     </row>
     <row r="472" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B472" s="30" t="s">
@@ -75869,7 +78339,9 @@
       <c r="BI472" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ472" s="31"/>
+      <c r="BJ472" s="31" t="s">
+        <v>1249</v>
+      </c>
     </row>
     <row r="473" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B473" s="30" t="s">
@@ -75992,7 +78464,9 @@
       <c r="BI473" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ473" s="31"/>
+      <c r="BJ473" s="31" t="s">
+        <v>1250</v>
+      </c>
     </row>
     <row r="474" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B474" s="30" t="s">
@@ -76115,7 +78589,9 @@
       <c r="BI474" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ474" s="31"/>
+      <c r="BJ474" s="31" t="s">
+        <v>1251</v>
+      </c>
     </row>
     <row r="475" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B475" s="30" t="s">
@@ -76238,7 +78714,9 @@
       <c r="BI475" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ475" s="31"/>
+      <c r="BJ475" s="31" t="s">
+        <v>1252</v>
+      </c>
     </row>
     <row r="476" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B476" s="30" t="s">
@@ -76361,7 +78839,9 @@
       <c r="BI476" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ476" s="31"/>
+      <c r="BJ476" s="31" t="s">
+        <v>1253</v>
+      </c>
     </row>
     <row r="477" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B477" s="30" t="s">
@@ -76484,7 +78964,9 @@
       <c r="BI477" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ477" s="31"/>
+      <c r="BJ477" s="31" t="s">
+        <v>1254</v>
+      </c>
     </row>
     <row r="478" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B478" s="30" t="s">
@@ -76607,7 +79089,9 @@
       <c r="BI478" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ478" s="31"/>
+      <c r="BJ478" s="31" t="s">
+        <v>1255</v>
+      </c>
     </row>
     <row r="479" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B479" s="30" t="s">
@@ -76730,7 +79214,9 @@
       <c r="BI479" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ479" s="31"/>
+      <c r="BJ479" s="31" t="s">
+        <v>1256</v>
+      </c>
     </row>
     <row r="480" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B480" s="30" t="s">
@@ -76853,7 +79339,9 @@
       <c r="BI480" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ480" s="31"/>
+      <c r="BJ480" s="31" t="s">
+        <v>1257</v>
+      </c>
     </row>
     <row r="481" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B481" s="30" t="s">
@@ -76976,7 +79464,9 @@
       <c r="BI481" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ481" s="31"/>
+      <c r="BJ481" s="31" t="s">
+        <v>1258</v>
+      </c>
     </row>
     <row r="482" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B482" s="30" t="s">
@@ -77099,7 +79589,9 @@
       <c r="BI482" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ482" s="31"/>
+      <c r="BJ482" s="31" t="s">
+        <v>1259</v>
+      </c>
     </row>
     <row r="483" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B483" s="30" t="s">
@@ -77222,7 +79714,9 @@
       <c r="BI483" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ483" s="31"/>
+      <c r="BJ483" s="31" t="s">
+        <v>1260</v>
+      </c>
     </row>
     <row r="484" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B484" s="30" t="s">
@@ -77345,7 +79839,9 @@
       <c r="BI484" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ484" s="31"/>
+      <c r="BJ484" s="31" t="s">
+        <v>1261</v>
+      </c>
     </row>
     <row r="485" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B485" s="30" t="s">
@@ -77468,7 +79964,9 @@
       <c r="BI485" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ485" s="31"/>
+      <c r="BJ485" s="31" t="s">
+        <v>1262</v>
+      </c>
     </row>
     <row r="486" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B486" s="30" t="s">
@@ -77591,7 +80089,9 @@
       <c r="BI486" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ486" s="31"/>
+      <c r="BJ486" s="31" t="s">
+        <v>1263</v>
+      </c>
     </row>
     <row r="487" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B487" s="30" t="s">
@@ -77714,7 +80214,9 @@
       <c r="BI487" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ487" s="31"/>
+      <c r="BJ487" s="31" t="s">
+        <v>1264</v>
+      </c>
     </row>
     <row r="488" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B488" s="30" t="s">
@@ -77837,7 +80339,9 @@
       <c r="BI488" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ488" s="31"/>
+      <c r="BJ488" s="31" t="s">
+        <v>1265</v>
+      </c>
     </row>
     <row r="489" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B489" s="30" t="s">
@@ -77960,7 +80464,9 @@
       <c r="BI489" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ489" s="31"/>
+      <c r="BJ489" s="31" t="s">
+        <v>1266</v>
+      </c>
     </row>
     <row r="490" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B490" s="30" t="s">
@@ -78083,7 +80589,9 @@
       <c r="BI490" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ490" s="31"/>
+      <c r="BJ490" s="31" t="s">
+        <v>1267</v>
+      </c>
     </row>
     <row r="491" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B491" s="30" t="s">
@@ -78206,7 +80714,9 @@
       <c r="BI491" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ491" s="31"/>
+      <c r="BJ491" s="31" t="s">
+        <v>1268</v>
+      </c>
     </row>
     <row r="492" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B492" s="30" t="s">
@@ -78329,7 +80839,9 @@
       <c r="BI492" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ492" s="31"/>
+      <c r="BJ492" s="31" t="s">
+        <v>1269</v>
+      </c>
     </row>
     <row r="493" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B493" s="30" t="s">
@@ -78452,7 +80964,9 @@
       <c r="BI493" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ493" s="31"/>
+      <c r="BJ493" s="31" t="s">
+        <v>1270</v>
+      </c>
     </row>
     <row r="494" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B494" s="30" t="s">
@@ -78575,7 +81089,9 @@
       <c r="BI494" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ494" s="31"/>
+      <c r="BJ494" s="31" t="s">
+        <v>1271</v>
+      </c>
     </row>
     <row r="495" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B495" s="30" t="s">
@@ -78698,7 +81214,9 @@
       <c r="BI495" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ495" s="31"/>
+      <c r="BJ495" s="31" t="s">
+        <v>1272</v>
+      </c>
     </row>
     <row r="496" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B496" s="30" t="s">
@@ -78821,7 +81339,9 @@
       <c r="BI496" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ496" s="31"/>
+      <c r="BJ496" s="31" t="s">
+        <v>1273</v>
+      </c>
     </row>
     <row r="497" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B497" s="30" t="s">
@@ -78944,7 +81464,9 @@
       <c r="BI497" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ497" s="31"/>
+      <c r="BJ497" s="31" t="s">
+        <v>1274</v>
+      </c>
     </row>
     <row r="498" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B498" s="30" t="s">
@@ -79067,7 +81589,9 @@
       <c r="BI498" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ498" s="31"/>
+      <c r="BJ498" s="31" t="s">
+        <v>1275</v>
+      </c>
     </row>
     <row r="499" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B499" s="30" t="s">
@@ -79190,7 +81714,9 @@
       <c r="BI499" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ499" s="31"/>
+      <c r="BJ499" s="31" t="s">
+        <v>1276</v>
+      </c>
     </row>
     <row r="500" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B500" s="30" t="s">
@@ -79313,7 +81839,9 @@
       <c r="BI500" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ500" s="31"/>
+      <c r="BJ500" s="31" t="s">
+        <v>1277</v>
+      </c>
     </row>
     <row r="501" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B501" s="30" t="s">
@@ -79436,7 +81964,9 @@
       <c r="BI501" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ501" s="31"/>
+      <c r="BJ501" s="31" t="s">
+        <v>1278</v>
+      </c>
     </row>
     <row r="502" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B502" s="30" t="s">
@@ -79559,7 +82089,9 @@
       <c r="BI502" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ502" s="31"/>
+      <c r="BJ502" s="31" t="s">
+        <v>1279</v>
+      </c>
     </row>
     <row r="503" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B503" s="30" t="s">
@@ -79682,7 +82214,9 @@
       <c r="BI503" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ503" s="31"/>
+      <c r="BJ503" s="31" t="s">
+        <v>1280</v>
+      </c>
     </row>
     <row r="504" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B504" s="30" t="s">
@@ -79805,7 +82339,9 @@
       <c r="BI504" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ504" s="31"/>
+      <c r="BJ504" s="31" t="s">
+        <v>1281</v>
+      </c>
     </row>
     <row r="505" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B505" s="30" t="s">
@@ -79928,7 +82464,9 @@
       <c r="BI505" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ505" s="31"/>
+      <c r="BJ505" s="31" t="s">
+        <v>1282</v>
+      </c>
     </row>
     <row r="506" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B506" s="30" t="s">
@@ -80051,7 +82589,9 @@
       <c r="BI506" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ506" s="31"/>
+      <c r="BJ506" s="31" t="s">
+        <v>1283</v>
+      </c>
     </row>
     <row r="507" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B507" s="30" t="s">
@@ -80174,7 +82714,9 @@
       <c r="BI507" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ507" s="31"/>
+      <c r="BJ507" s="31" t="s">
+        <v>1284</v>
+      </c>
     </row>
     <row r="508" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B508" s="30" t="s">
@@ -80297,7 +82839,9 @@
       <c r="BI508" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ508" s="31"/>
+      <c r="BJ508" s="31" t="s">
+        <v>1285</v>
+      </c>
     </row>
     <row r="509" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B509" s="30" t="s">
@@ -80420,7 +82964,9 @@
       <c r="BI509" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ509" s="31"/>
+      <c r="BJ509" s="31" t="s">
+        <v>1286</v>
+      </c>
     </row>
     <row r="510" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B510" s="30" t="s">
@@ -80543,7 +83089,9 @@
       <c r="BI510" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ510" s="31"/>
+      <c r="BJ510" s="31" t="s">
+        <v>1287</v>
+      </c>
     </row>
     <row r="511" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B511" s="30" t="s">
@@ -80666,7 +83214,9 @@
       <c r="BI511" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ511" s="31"/>
+      <c r="BJ511" s="31" t="s">
+        <v>1288</v>
+      </c>
     </row>
     <row r="512" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B512" s="30" t="s">
@@ -80789,7 +83339,9 @@
       <c r="BI512" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ512" s="31"/>
+      <c r="BJ512" s="31" t="s">
+        <v>1289</v>
+      </c>
     </row>
     <row r="513" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B513" s="30" t="s">
@@ -80912,7 +83464,9 @@
       <c r="BI513" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ513" s="31"/>
+      <c r="BJ513" s="31" t="s">
+        <v>1290</v>
+      </c>
     </row>
     <row r="514" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B514" s="30" t="s">
@@ -81035,7 +83589,9 @@
       <c r="BI514" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ514" s="31"/>
+      <c r="BJ514" s="31" t="s">
+        <v>1291</v>
+      </c>
     </row>
     <row r="515" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B515" s="30" t="s">
@@ -81044,7 +83600,7 @@
       <c r="C515" s="195" t="s">
         <v>5</v>
       </c>
-      <c r="D515" s="241" t="s">
+      <c r="D515" s="240" t="s">
         <v>396</v>
       </c>
       <c r="E515" s="209" t="s">
@@ -81158,7 +83714,9 @@
       <c r="BI515" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ515" s="31"/>
+      <c r="BJ515" s="31" t="s">
+        <v>1292</v>
+      </c>
     </row>
     <row r="516" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B516" s="30" t="s">
@@ -81167,7 +83725,7 @@
       <c r="C516" s="195" t="s">
         <v>5</v>
       </c>
-      <c r="D516" s="241" t="s">
+      <c r="D516" s="240" t="s">
         <v>308</v>
       </c>
       <c r="E516" s="209" t="s">
@@ -81281,7 +83839,9 @@
       <c r="BI516" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ516" s="31"/>
+      <c r="BJ516" s="31" t="s">
+        <v>1293</v>
+      </c>
     </row>
     <row r="517" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B517" s="30" t="s">
@@ -81290,7 +83850,7 @@
       <c r="C517" s="195" t="s">
         <v>5</v>
       </c>
-      <c r="D517" s="241" t="s">
+      <c r="D517" s="240" t="s">
         <v>396</v>
       </c>
       <c r="E517" s="209" t="s">
@@ -81404,7 +83964,9 @@
       <c r="BI517" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ517" s="31"/>
+      <c r="BJ517" s="31" t="s">
+        <v>1294</v>
+      </c>
     </row>
     <row r="518" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B518" s="30" t="s">
@@ -81413,7 +83975,7 @@
       <c r="C518" s="195" t="s">
         <v>5</v>
       </c>
-      <c r="D518" s="241" t="s">
+      <c r="D518" s="240" t="s">
         <v>308</v>
       </c>
       <c r="E518" s="209" t="s">
@@ -81525,7 +84087,9 @@
       <c r="BI518" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ518" s="31"/>
+      <c r="BJ518" s="31" t="s">
+        <v>1295</v>
+      </c>
     </row>
     <row r="519" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B519" s="30" t="s">
@@ -81534,7 +84098,7 @@
       <c r="C519" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="D519" s="241" t="s">
+      <c r="D519" s="240" t="s">
         <v>308</v>
       </c>
       <c r="E519" s="209" t="s">
@@ -81646,7 +84210,9 @@
       <c r="BI519" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ519" s="31"/>
+      <c r="BJ519" s="31" t="s">
+        <v>1296</v>
+      </c>
     </row>
     <row r="520" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B520" s="30" t="s">
@@ -81769,7 +84335,9 @@
       <c r="BI520" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ520" s="31"/>
+      <c r="BJ520" s="31" t="s">
+        <v>1297</v>
+      </c>
     </row>
     <row r="521" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B521" s="30" t="s">
@@ -81890,7 +84458,9 @@
       <c r="BI521" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ521" s="31"/>
+      <c r="BJ521" s="31" t="s">
+        <v>1298</v>
+      </c>
     </row>
     <row r="522" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B522" s="30" t="s">
@@ -82011,7 +84581,9 @@
       <c r="BI522" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ522" s="31"/>
+      <c r="BJ522" s="31" t="s">
+        <v>1299</v>
+      </c>
     </row>
     <row r="523" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B523" s="30" t="s">
@@ -82132,7 +84704,9 @@
       <c r="BI523" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ523" s="31"/>
+      <c r="BJ523" s="31" t="s">
+        <v>1300</v>
+      </c>
     </row>
     <row r="524" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B524" s="30" t="s">
@@ -82253,7 +84827,9 @@
       <c r="BI524" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ524" s="31"/>
+      <c r="BJ524" s="31" t="s">
+        <v>1301</v>
+      </c>
     </row>
     <row r="525" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B525" s="30" t="s">
@@ -82374,7 +84950,9 @@
       <c r="BI525" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ525" s="67"/>
+      <c r="BJ525" s="31" t="s">
+        <v>1302</v>
+      </c>
     </row>
     <row r="526" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B526" s="30" t="s">
@@ -82495,7 +85073,9 @@
       <c r="BI526" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ526" s="67"/>
+      <c r="BJ526" s="31" t="s">
+        <v>1303</v>
+      </c>
     </row>
     <row r="527" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B527" s="30" t="s">
@@ -82510,10 +85090,10 @@
       <c r="E527" s="209" t="s">
         <v>319</v>
       </c>
-      <c r="F527" s="247">
+      <c r="F527" s="246">
         <v>1072625</v>
       </c>
-      <c r="G527" s="253" t="s">
+      <c r="G527" s="252" t="s">
         <v>623</v>
       </c>
       <c r="H527" s="162">
@@ -82616,7 +85196,9 @@
       <c r="BI527" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ527" s="67"/>
+      <c r="BJ527" s="31" t="s">
+        <v>1304</v>
+      </c>
     </row>
     <row r="528" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B528" s="30" t="s">
@@ -82737,7 +85319,9 @@
       <c r="BI528" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ528" s="67"/>
+      <c r="BJ528" s="31" t="s">
+        <v>1305</v>
+      </c>
     </row>
     <row r="529" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B529" s="30" t="s">
@@ -82858,7 +85442,9 @@
       <c r="BI529" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ529" s="67"/>
+      <c r="BJ529" s="31" t="s">
+        <v>1306</v>
+      </c>
     </row>
     <row r="530" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B530" s="30" t="s">
@@ -82979,7 +85565,9 @@
       <c r="BI530" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ530" s="67"/>
+      <c r="BJ530" s="31" t="s">
+        <v>1307</v>
+      </c>
     </row>
     <row r="531" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B531" s="30" t="s">
@@ -83100,7 +85688,9 @@
       <c r="BI531" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ531" s="67"/>
+      <c r="BJ531" s="31" t="s">
+        <v>1308</v>
+      </c>
     </row>
     <row r="532" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B532" s="30" t="s">
@@ -83115,10 +85705,10 @@
       <c r="E532" s="223" t="s">
         <v>307</v>
       </c>
-      <c r="F532" s="246">
+      <c r="F532" s="245">
         <v>1074078</v>
       </c>
-      <c r="G532" s="252" t="s">
+      <c r="G532" s="251" t="s">
         <v>680</v>
       </c>
       <c r="H532" s="222">
@@ -83221,7 +85811,9 @@
       <c r="BI532" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ532" s="67"/>
+      <c r="BJ532" s="31" t="s">
+        <v>1309</v>
+      </c>
     </row>
     <row r="533" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B533" s="30" t="s">
@@ -83342,7 +85934,9 @@
       <c r="BI533" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ533" s="67"/>
+      <c r="BJ533" s="31" t="s">
+        <v>1310</v>
+      </c>
     </row>
     <row r="534" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B534" s="30" t="s">
@@ -83463,7 +86057,9 @@
       <c r="BI534" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ534" s="67"/>
+      <c r="BJ534" s="31" t="s">
+        <v>1311</v>
+      </c>
     </row>
     <row r="535" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B535" s="30" t="s">
@@ -83481,10 +86077,10 @@
       <c r="F535" s="139">
         <v>1067806</v>
       </c>
-      <c r="G535" s="248" t="s">
+      <c r="G535" s="247" t="s">
         <v>638</v>
       </c>
-      <c r="H535" s="255">
+      <c r="H535" s="254">
         <v>0</v>
       </c>
       <c r="I535" s="162">
@@ -83584,7 +86180,9 @@
       <c r="BI535" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ535" s="67"/>
+      <c r="BJ535" s="31" t="s">
+        <v>1312</v>
+      </c>
     </row>
     <row r="536" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B536" s="30" t="s">
@@ -83599,13 +86197,13 @@
       <c r="E536" s="233" t="s">
         <v>319</v>
       </c>
-      <c r="F536" s="243">
+      <c r="F536" s="242">
         <v>1072517</v>
       </c>
-      <c r="G536" s="249" t="s">
+      <c r="G536" s="248" t="s">
         <v>637</v>
       </c>
-      <c r="H536" s="255">
+      <c r="H536" s="254">
         <v>0</v>
       </c>
       <c r="I536" s="162">
@@ -83705,7 +86303,9 @@
       <c r="BI536" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ536" s="67"/>
+      <c r="BJ536" s="31" t="s">
+        <v>1313</v>
+      </c>
     </row>
     <row r="537" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B537" s="30" t="s">
@@ -83726,7 +86326,7 @@
       <c r="G537" s="50" t="s">
         <v>663</v>
       </c>
-      <c r="H537" s="255">
+      <c r="H537" s="254">
         <v>0</v>
       </c>
       <c r="I537" s="162">
@@ -83826,7 +86426,9 @@
       <c r="BI537" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ537" s="67"/>
+      <c r="BJ537" s="31" t="s">
+        <v>1314</v>
+      </c>
     </row>
     <row r="538" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B538" s="30">
@@ -83847,7 +86449,7 @@
       <c r="G538" s="50" t="s">
         <v>674</v>
       </c>
-      <c r="H538" s="255">
+      <c r="H538" s="254">
         <v>0</v>
       </c>
       <c r="I538" s="162">
@@ -83947,7 +86549,9 @@
       <c r="BI538" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="BJ538" s="67"/>
+      <c r="BJ538" s="31" t="s">
+        <v>1315</v>
+      </c>
     </row>
     <row r="539" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B539" s="187" t="s">
@@ -83962,13 +86566,13 @@
       <c r="E539" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="F539" s="242">
+      <c r="F539" s="241">
         <v>1058418</v>
       </c>
-      <c r="G539" s="240" t="s">
+      <c r="G539" s="239" t="s">
         <v>235</v>
       </c>
-      <c r="H539" s="257">
+      <c r="H539" s="256">
         <v>0</v>
       </c>
       <c r="I539" s="188">
@@ -83983,16 +86587,16 @@
       <c r="L539" s="236">
         <v>0</v>
       </c>
-      <c r="M539" s="258">
+      <c r="M539" s="257">
         <v>0</v>
       </c>
       <c r="N539" s="236">
         <v>0</v>
       </c>
-      <c r="O539" s="259">
-        <v>0</v>
-      </c>
-      <c r="P539" s="258">
+      <c r="O539" s="258">
+        <v>0</v>
+      </c>
+      <c r="P539" s="257">
         <v>0</v>
       </c>
       <c r="Q539" s="119">
@@ -84019,7 +86623,7 @@
       <c r="X539" s="106">
         <v>0</v>
       </c>
-      <c r="Y539" s="260" t="s">
+      <c r="Y539" s="259" t="s">
         <v>574</v>
       </c>
       <c r="Z539" s="106" t="s">
@@ -84031,7 +86635,7 @@
       <c r="AB539" s="237">
         <v>0</v>
       </c>
-      <c r="AC539" s="262" t="s">
+      <c r="AC539" s="261" t="s">
         <v>791</v>
       </c>
       <c r="AD539" s="177"/>
@@ -84068,7 +86672,9 @@
       <c r="BI539" s="238" t="s">
         <v>1</v>
       </c>
-      <c r="BJ539" s="239"/>
+      <c r="BJ539" s="31" t="s">
+        <v>1316</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -84078,6 +86684,7 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="T17:W17"/>
   </mergeCells>
+  <phoneticPr fontId="59" type="noConversion"/>
   <conditionalFormatting sqref="M18:O18">
     <cfRule type="expression" dxfId="159" priority="162" stopIfTrue="1">
       <formula>"g4&gt;1"</formula>

--- a/datos_stock.xlsx
+++ b/datos_stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fpjmojeda\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA699B8-2A14-40AF-870C-1F435DB60639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D600A7-AA8D-4F72-B4F3-C8F3A0491B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12300" tabRatio="813" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5183" uniqueCount="836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5184" uniqueCount="837">
   <si>
     <t>GLINA. MONTBLANC ESTUCHE16ESTX7UN INT NG GEMA</t>
   </si>
@@ -2451,9 +2451,6 @@
     <t>Existirá ingreso de 40,250 und que brinda una cobertura de 32 días e ingresará entre el 07/04/26 - 13/04/26</t>
   </si>
   <si>
-    <t>Existirá ingreso de 126,864 und que brinda una cobertura de 4 días e ingresará entre el 07/04/26 - 13/04/26</t>
-  </si>
-  <si>
     <t>Marca privada B2B</t>
   </si>
   <si>
@@ -2551,6 +2548,15 @@
   </si>
   <si>
     <t>Cocoa Winters RTS Cjx13ux90g</t>
+  </si>
+  <si>
+    <t>El 13/04 ingresa 8,400 und
+El 14/04 ingresa el 35,000 und
+El 16/04 ingresa 99,000 und
+El 17/04 ingresa 99,000 und</t>
+  </si>
+  <si>
+    <t>El 14/04 ingresa 27,264 und</t>
   </si>
 </sst>
 </file>
@@ -3819,7 +3825,7 @@
     <xf numFmtId="43" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="208">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4393,6 +4399,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4423,11 +4435,8 @@
     <xf numFmtId="3" fontId="3" fillId="7" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -4490,2638 +4499,7 @@
     <cellStyle name="Título 3" xfId="13" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="26" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="237">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="171" formatCode="_-&quot;S/&quot;\ * #,##0_-;\-&quot;S/&quot;\ * #,##0_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="171" formatCode="_-&quot;S/&quot;\ * #,##0_-;\-&quot;S/&quot;\ * #,##0_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dotted">
-          <color indexed="64"/>
-        </left>
-        <right style="dotted">
-          <color indexed="64"/>
-        </right>
-        <top style="dotted">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="204">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -7884,6 +5262,46 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="dashed">
@@ -7896,6 +5314,48 @@
           <color indexed="64"/>
         </top>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -7944,12 +5404,17 @@
         <sz val="10"/>
         <color auto="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -7959,7 +5424,11 @@
         <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -8008,12 +5477,17 @@
         <sz val="10"/>
         <color auto="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -8023,7 +5497,11 @@
         <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -8072,12 +5550,17 @@
         <sz val="10"/>
         <color auto="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -8087,7 +5570,11 @@
         <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -8136,12 +5623,17 @@
         <sz val="10"/>
         <color auto="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -8151,7 +5643,11 @@
         <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -8200,12 +5696,17 @@
         <sz val="10"/>
         <color auto="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -8215,7 +5716,11 @@
         <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -8264,12 +5769,17 @@
         <sz val="10"/>
         <color auto="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -8279,7 +5789,11 @@
         <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -8328,12 +5842,17 @@
         <sz val="10"/>
         <color auto="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -8343,7 +5862,11 @@
         <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -8392,12 +5915,17 @@
         <sz val="10"/>
         <color auto="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -8407,7 +5935,11 @@
         <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -8456,12 +5988,17 @@
         <sz val="10"/>
         <color auto="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -8471,7 +6008,11 @@
         <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -8520,12 +6061,17 @@
         <sz val="10"/>
         <color auto="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -8535,7 +6081,11 @@
         <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -8584,12 +6134,17 @@
         <sz val="10"/>
         <color auto="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -8599,7 +6154,11 @@
         <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -8648,12 +6207,17 @@
         <sz val="10"/>
         <color auto="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -8663,7 +6227,11 @@
         <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -8712,12 +6280,17 @@
         <sz val="10"/>
         <color auto="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -8727,7 +6300,11 @@
         <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -8776,12 +6353,17 @@
         <sz val="10"/>
         <color auto="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -8791,7 +6373,11 @@
         <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -8840,6 +6426,47 @@
         <sz val="10"/>
         <color auto="1"/>
         <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
@@ -8872,6 +6499,47 @@
         <sz val="10"/>
         <color auto="1"/>
         <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
@@ -8888,6 +6556,1065 @@
           <color indexed="64"/>
         </top>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -8936,12 +7663,11 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -8951,7 +7677,11 @@
         <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -9000,12 +7730,11 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <numFmt numFmtId="171" formatCode="_-&quot;S/&quot;\ * #,##0_-;\-&quot;S/&quot;\ * #,##0_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -9015,7 +7744,11 @@
         <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -9064,6 +7797,41 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="171" formatCode="_-&quot;S/&quot;\ * #,##0_-;\-&quot;S/&quot;\ * #,##0_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
@@ -9080,6 +7848,175 @@
           <color indexed="64"/>
         </top>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -9127,11 +8064,11 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -9141,7 +8078,11 @@
         <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -9189,11 +8130,10 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -9203,7 +8143,11 @@
         <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -9251,6 +8195,40 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
@@ -9282,6 +8260,40 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
@@ -9297,6 +8309,171 @@
           <color indexed="64"/>
         </top>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -9345,12 +8522,11 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <numFmt numFmtId="13" formatCode="0%"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -9361,6 +8537,8 @@
           <color indexed="64"/>
         </top>
         <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -9409,12 +8587,11 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
+      <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="dashed">
           <color indexed="64"/>
         </left>
@@ -9425,6 +8602,8 @@
           <color indexed="64"/>
         </top>
         <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -9473,10 +8652,45 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <numFmt numFmtId="13" formatCode="0%"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="dashed">
@@ -9489,6 +8703,41 @@
           <color indexed="64"/>
         </top>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -9537,6 +8786,175 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
@@ -9556,6 +8974,41 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -9571,6 +9024,33 @@
         <bottom style="dotted">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dotted">
+          <color indexed="64"/>
+        </left>
+        <right style="dotted">
+          <color indexed="64"/>
+        </right>
+        <top style="dotted">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -9632,12 +9112,86 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -9666,6 +9220,41 @@
         </right>
         <top/>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -9713,6 +9302,40 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
@@ -9729,6 +9352,38 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <left style="dashed">
           <color indexed="64"/>
@@ -9740,6 +9395,30 @@
           <color indexed="64"/>
         </top>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -10077,34 +9756,34 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="PivotStyleMedium6 2" table="0" count="13" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="236"/>
-      <tableStyleElement type="headerRow" dxfId="235"/>
-      <tableStyleElement type="totalRow" dxfId="234"/>
-      <tableStyleElement type="firstRowStripe" dxfId="233"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="232"/>
-      <tableStyleElement type="firstHeaderCell" dxfId="231"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="230"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="229"/>
-      <tableStyleElement type="firstColumnSubheading" dxfId="228"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="227"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="226"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="225"/>
-      <tableStyleElement type="pageFieldValues" dxfId="224"/>
+      <tableStyleElement type="wholeTable" dxfId="203"/>
+      <tableStyleElement type="headerRow" dxfId="202"/>
+      <tableStyleElement type="totalRow" dxfId="201"/>
+      <tableStyleElement type="firstRowStripe" dxfId="200"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="199"/>
+      <tableStyleElement type="firstHeaderCell" dxfId="198"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="197"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="196"/>
+      <tableStyleElement type="firstColumnSubheading" dxfId="195"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="194"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="193"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="192"/>
+      <tableStyleElement type="pageFieldValues" dxfId="191"/>
     </tableStyle>
     <tableStyle name="PivotStyleMedium6 3" table="0" count="13" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" dxfId="223"/>
-      <tableStyleElement type="headerRow" dxfId="222"/>
-      <tableStyleElement type="totalRow" dxfId="221"/>
-      <tableStyleElement type="firstRowStripe" dxfId="220"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="219"/>
-      <tableStyleElement type="firstHeaderCell" dxfId="218"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="217"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="216"/>
-      <tableStyleElement type="firstColumnSubheading" dxfId="215"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="214"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="213"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="212"/>
-      <tableStyleElement type="pageFieldValues" dxfId="211"/>
+      <tableStyleElement type="wholeTable" dxfId="190"/>
+      <tableStyleElement type="headerRow" dxfId="189"/>
+      <tableStyleElement type="totalRow" dxfId="188"/>
+      <tableStyleElement type="firstRowStripe" dxfId="187"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="186"/>
+      <tableStyleElement type="firstHeaderCell" dxfId="185"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="184"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="183"/>
+      <tableStyleElement type="firstColumnSubheading" dxfId="182"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="181"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="180"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="179"/>
+      <tableStyleElement type="pageFieldValues" dxfId="178"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -10130,94 +9809,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TMR" displayName="TMR" ref="B2:L222" totalsRowShown="0" headerRowDxfId="146" dataDxfId="144" headerRowBorderDxfId="145" tableBorderDxfId="143" totalsRowBorderDxfId="142">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TMR" displayName="TMR" ref="B2:L222" totalsRowShown="0" headerRowDxfId="52" dataDxfId="50" headerRowBorderDxfId="51" tableBorderDxfId="49" totalsRowBorderDxfId="48">
   <autoFilter ref="B2:L222" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="CÓDIGO" dataDxfId="141"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="DESCRIPCIÓN" dataDxfId="140"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="ORIGEN" dataDxfId="139"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="CATEGORÍA" dataDxfId="138"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Tiempo de Vida" dataDxfId="137"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tottus" dataDxfId="136">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="CÓDIGO" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="DESCRIPCIÓN" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="ORIGEN" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="CATEGORÍA" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Tiempo de Vida" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tottus" dataDxfId="42">
       <calculatedColumnFormula>IF(F3&lt;=210,F3*0.6,IF(F3&lt;=365,120,IF(F3&lt;=3600,150)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Cencosud" dataDxfId="135"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Tambo" dataDxfId="134"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Oxxo" dataDxfId="133"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPSA / MAKRO" dataDxfId="132">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Cencosud" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Tambo" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Oxxo" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPSA / MAKRO" dataDxfId="38">
       <calculatedColumnFormula>ROUNDDOWN(F3/3,0)-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Canal Tradicional / Otros" dataDxfId="131"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Canal Tradicional / Otros" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Principal" displayName="Principal" ref="B18:BJ546" totalsRowShown="0" headerRowDxfId="210" dataDxfId="0" tableBorderDxfId="209" headerRowCellStyle="Normal 10 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Principal" displayName="Principal" ref="B18:BJ546" totalsRowShown="0" headerRowDxfId="177" dataDxfId="176" tableBorderDxfId="175" headerRowCellStyle="Normal 10 2">
   <autoFilter ref="B18:BJ546" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="61">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="RESPONSABLE DE PRODUCCIÓN" dataDxfId="60" totalsRowDxfId="208"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="GEOGRAFÍA" dataDxfId="59" totalsRowDxfId="207"/>
-    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="CATEGORÍA" dataDxfId="58" totalsRowDxfId="206"/>
-    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="MARCA" dataDxfId="57" totalsRowDxfId="205"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="CÓDIGO" dataDxfId="56" totalsRowDxfId="204"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="DESCRIPCIÓN" dataDxfId="203" totalsRowDxfId="202"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Plan de demanda" dataDxfId="55" totalsRowDxfId="201"/>
-    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="Plan Demanda (Kg)" dataDxfId="54" totalsRowDxfId="200"/>
-    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Salidas varias" dataDxfId="53" totalsRowDxfId="199"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Avance Vta." dataDxfId="52" totalsRowDxfId="198"/>
-    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Avance _x000a_Vta. (Kg)" dataDxfId="51" totalsRowDxfId="197" dataCellStyle="Porcentaje"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="%V Mes actual" dataDxfId="50" totalsRowDxfId="196" dataCellStyle="Porcentaje"/>
-    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="Error ABS_x000a_(KG)" dataDxfId="49" totalsRowDxfId="195" dataCellStyle="Porcentaje"/>
-    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Días consumidos por sobreventa en el mes pasado" dataDxfId="48" totalsRowDxfId="194" dataCellStyle="Porcentaje"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="%V Mes pasado" dataDxfId="47" totalsRowDxfId="193" dataCellStyle="Porcentaje"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="STOCK TOTAL" dataDxfId="46" totalsRowDxfId="192"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="STOCK POR FACTURAR" dataDxfId="45" totalsRowDxfId="191"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="CEDI FINAL" dataDxfId="44" totalsRowDxfId="190"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="PLANTA" dataDxfId="43" totalsRowDxfId="189"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="TRANSITO" dataDxfId="42" totalsRowDxfId="188"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="CALIDAD" dataDxfId="41" totalsRowDxfId="187"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="BLOQUEADO" dataDxfId="40" totalsRowDxfId="186"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Vta. Proy." dataDxfId="39" totalsRowDxfId="185"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Días De Inventario" dataDxfId="38" totalsRowDxfId="184"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Faltante" dataDxfId="37" totalsRowDxfId="183"/>
-    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="Valorizado Plan de Demanda" dataDxfId="36" totalsRowDxfId="182" dataCellStyle="Moneda"/>
-    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="Valorizado Stock" dataDxfId="35" totalsRowDxfId="181" dataCellStyle="Moneda"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="% Cob." dataDxfId="34" totalsRowDxfId="180" dataCellStyle="Porcentaje"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="1" dataDxfId="33" totalsRowDxfId="179"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="2" dataDxfId="32" totalsRowDxfId="178"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="3" dataDxfId="31" totalsRowDxfId="177"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="4" dataDxfId="30" totalsRowDxfId="176"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="5" dataDxfId="29" totalsRowDxfId="175"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="6" dataDxfId="28" totalsRowDxfId="174"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="7" dataDxfId="27" totalsRowDxfId="173"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="8" dataDxfId="26" totalsRowDxfId="172"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="9" dataDxfId="25" totalsRowDxfId="171"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="10" dataDxfId="24" totalsRowDxfId="170"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="11" dataDxfId="23" totalsRowDxfId="169"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="12" dataDxfId="22" totalsRowDxfId="168"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="13" dataDxfId="21" totalsRowDxfId="167"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="14" dataDxfId="20" totalsRowDxfId="166"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="15" dataDxfId="19" totalsRowDxfId="165"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="16" dataDxfId="18" totalsRowDxfId="164"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="17" dataDxfId="17" totalsRowDxfId="163"/>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="18" dataDxfId="16" totalsRowDxfId="162"/>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="19" dataDxfId="15" totalsRowDxfId="161"/>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="20" dataDxfId="14" totalsRowDxfId="160"/>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="21" dataDxfId="13" totalsRowDxfId="159"/>
-    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="22" dataDxfId="12" totalsRowDxfId="158"/>
-    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="23" dataDxfId="11" totalsRowDxfId="157"/>
-    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="24" dataDxfId="10" totalsRowDxfId="156"/>
-    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="25" dataDxfId="9" totalsRowDxfId="155"/>
-    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="26" dataDxfId="8" totalsRowDxfId="154"/>
-    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="27" dataDxfId="7" totalsRowDxfId="153"/>
-    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="28" dataDxfId="6" totalsRowDxfId="152"/>
-    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="29" dataDxfId="5" totalsRowDxfId="151"/>
-    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="30" dataDxfId="4" totalsRowDxfId="150"/>
-    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="31" dataDxfId="3" totalsRowDxfId="149"/>
-    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Fecha de _x000a_Ingreso según RAS" dataDxfId="2" totalsRowDxfId="148" dataCellStyle="Millares 10"/>
-    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="Causal / Observado" dataDxfId="1" totalsRowDxfId="147" dataCellStyle="Millares 10"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="RESPONSABLE DE PRODUCCIÓN" dataDxfId="174" totalsRowDxfId="173"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="GEOGRAFÍA" dataDxfId="172" totalsRowDxfId="171"/>
+    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="CATEGORÍA" dataDxfId="170" totalsRowDxfId="169"/>
+    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="MARCA" dataDxfId="168" totalsRowDxfId="167"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="CÓDIGO" dataDxfId="166" totalsRowDxfId="165"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="DESCRIPCIÓN" dataDxfId="164" totalsRowDxfId="163"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Plan de demanda" dataDxfId="162" totalsRowDxfId="161"/>
+    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="Plan Demanda (Kg)" dataDxfId="160" totalsRowDxfId="159"/>
+    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Salidas varias" dataDxfId="158" totalsRowDxfId="157"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Avance Vta." dataDxfId="156" totalsRowDxfId="155"/>
+    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Avance _x000a_Vta. (Kg)" dataDxfId="154" totalsRowDxfId="153" dataCellStyle="Porcentaje"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="%V Mes actual" dataDxfId="152" totalsRowDxfId="151" dataCellStyle="Porcentaje"/>
+    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="Error ABS_x000a_(KG)" dataDxfId="150" totalsRowDxfId="149" dataCellStyle="Porcentaje"/>
+    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Días consumidos por sobreventa en el mes pasado" dataDxfId="148" totalsRowDxfId="147" dataCellStyle="Porcentaje"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="%V Mes pasado" dataDxfId="146" totalsRowDxfId="145" dataCellStyle="Porcentaje"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="STOCK TOTAL" dataDxfId="144" totalsRowDxfId="143"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="STOCK POR FACTURAR" dataDxfId="142" totalsRowDxfId="141"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="CEDI FINAL" dataDxfId="140" totalsRowDxfId="139"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="PLANTA" dataDxfId="138" totalsRowDxfId="137"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="TRANSITO" dataDxfId="136" totalsRowDxfId="135"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="CALIDAD" dataDxfId="134" totalsRowDxfId="133"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="BLOQUEADO" dataDxfId="132" totalsRowDxfId="131"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Vta. Proy." dataDxfId="130" totalsRowDxfId="129"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Días De Inventario" dataDxfId="128" totalsRowDxfId="127"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Faltante" dataDxfId="126" totalsRowDxfId="125"/>
+    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="Valorizado Plan de Demanda" dataDxfId="124" totalsRowDxfId="123" dataCellStyle="Moneda"/>
+    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="Valorizado Stock" dataDxfId="122" totalsRowDxfId="121" dataCellStyle="Moneda"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="% Cob." dataDxfId="120" totalsRowDxfId="119" dataCellStyle="Porcentaje"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="1" dataDxfId="118" totalsRowDxfId="117"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="2" dataDxfId="116" totalsRowDxfId="115"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="3" dataDxfId="114" totalsRowDxfId="113"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="4" dataDxfId="112" totalsRowDxfId="111"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="5" dataDxfId="110" totalsRowDxfId="109"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="6" dataDxfId="108" totalsRowDxfId="107"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="7" dataDxfId="106" totalsRowDxfId="105"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="8" dataDxfId="104" totalsRowDxfId="103"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="9" dataDxfId="102" totalsRowDxfId="101"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="10" dataDxfId="100" totalsRowDxfId="99"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="11" dataDxfId="98" totalsRowDxfId="97"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="12" dataDxfId="96" totalsRowDxfId="95"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="13" dataDxfId="94" totalsRowDxfId="93"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="14" dataDxfId="92" totalsRowDxfId="91"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="15" dataDxfId="90" totalsRowDxfId="89"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="16" dataDxfId="88" totalsRowDxfId="87"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="17" dataDxfId="86" totalsRowDxfId="85"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="18" dataDxfId="84" totalsRowDxfId="83"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="19" dataDxfId="82" totalsRowDxfId="81"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="20" dataDxfId="80" totalsRowDxfId="79"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="21" dataDxfId="78" totalsRowDxfId="77"/>
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="22" dataDxfId="76" totalsRowDxfId="75"/>
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="23" dataDxfId="74" totalsRowDxfId="73"/>
+    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="24" dataDxfId="72" totalsRowDxfId="71"/>
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="25" dataDxfId="70" totalsRowDxfId="69"/>
+    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="26" dataDxfId="68" totalsRowDxfId="67"/>
+    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="27" dataDxfId="66" totalsRowDxfId="65"/>
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="28" dataDxfId="64" totalsRowDxfId="63"/>
+    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="29" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="30" dataDxfId="60" totalsRowDxfId="59"/>
+    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="31" dataDxfId="58" totalsRowDxfId="57"/>
+    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Fecha de _x000a_Ingreso según RAS" dataDxfId="56" totalsRowDxfId="55" dataCellStyle="Millares 10"/>
+    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="Causal / Observado" dataDxfId="54" totalsRowDxfId="53" dataCellStyle="Millares 10"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -18647,10 +18326,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="130" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B222">
-    <cfRule type="duplicateValues" dxfId="129" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" copies="0" r:id="rId1"/>
@@ -19838,10 +19517,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="128" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2">
-    <cfRule type="duplicateValues" dxfId="127" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" copies="0" r:id="rId1"/>
@@ -19907,25 +19586,25 @@
     </row>
     <row r="2" spans="1:59" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="118"/>
-      <c r="B2" s="196" t="s">
+      <c r="B2" s="198" t="s">
         <v>341</v>
       </c>
-      <c r="C2" s="197"/>
-      <c r="D2" s="197"/>
-      <c r="E2" s="197"/>
-      <c r="F2" s="197"/>
-      <c r="G2" s="200">
+      <c r="C2" s="199"/>
+      <c r="D2" s="199"/>
+      <c r="E2" s="199"/>
+      <c r="F2" s="199"/>
+      <c r="G2" s="202">
         <v>46122</v>
       </c>
     </row>
     <row r="3" spans="1:59" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="118"/>
-      <c r="B3" s="198"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="199"/>
-      <c r="F3" s="199"/>
-      <c r="G3" s="201"/>
+      <c r="B3" s="200"/>
+      <c r="C3" s="201"/>
+      <c r="D3" s="201"/>
+      <c r="E3" s="201"/>
+      <c r="F3" s="201"/>
+      <c r="G3" s="203"/>
     </row>
     <row r="4" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A4" s="118"/>
@@ -20173,55 +19852,55 @@
       <c r="M17" s="20"/>
       <c r="N17" s="94"/>
       <c r="O17" s="21"/>
-      <c r="Q17" s="202" t="s">
+      <c r="Q17" s="204" t="s">
         <v>342</v>
       </c>
-      <c r="R17" s="203"/>
-      <c r="S17" s="204"/>
-      <c r="T17" s="202" t="s">
+      <c r="R17" s="205"/>
+      <c r="S17" s="206"/>
+      <c r="T17" s="204" t="s">
         <v>497</v>
       </c>
-      <c r="U17" s="203"/>
-      <c r="V17" s="203"/>
-      <c r="W17" s="203"/>
+      <c r="U17" s="205"/>
+      <c r="V17" s="205"/>
+      <c r="W17" s="205"/>
       <c r="X17" s="28"/>
       <c r="Y17" s="28"/>
       <c r="Z17" s="26"/>
       <c r="AA17" s="26"/>
       <c r="AB17" s="26"/>
-      <c r="AC17" s="195" t="s">
+      <c r="AC17" s="197" t="s">
         <v>331</v>
       </c>
-      <c r="AD17" s="195"/>
-      <c r="AE17" s="195"/>
-      <c r="AF17" s="195"/>
-      <c r="AG17" s="195"/>
-      <c r="AH17" s="195"/>
-      <c r="AI17" s="195"/>
-      <c r="AJ17" s="195"/>
-      <c r="AK17" s="195"/>
-      <c r="AL17" s="195"/>
-      <c r="AM17" s="195"/>
-      <c r="AN17" s="195"/>
-      <c r="AO17" s="195"/>
-      <c r="AP17" s="195"/>
-      <c r="AQ17" s="195"/>
-      <c r="AR17" s="195"/>
-      <c r="AS17" s="195"/>
-      <c r="AT17" s="195"/>
-      <c r="AU17" s="195"/>
-      <c r="AV17" s="195"/>
-      <c r="AW17" s="195"/>
-      <c r="AX17" s="195"/>
-      <c r="AY17" s="195"/>
-      <c r="AZ17" s="195"/>
-      <c r="BA17" s="195"/>
-      <c r="BB17" s="195"/>
-      <c r="BC17" s="195"/>
-      <c r="BD17" s="195"/>
-      <c r="BE17" s="195"/>
-      <c r="BF17" s="195"/>
-      <c r="BG17" s="195"/>
+      <c r="AD17" s="197"/>
+      <c r="AE17" s="197"/>
+      <c r="AF17" s="197"/>
+      <c r="AG17" s="197"/>
+      <c r="AH17" s="197"/>
+      <c r="AI17" s="197"/>
+      <c r="AJ17" s="197"/>
+      <c r="AK17" s="197"/>
+      <c r="AL17" s="197"/>
+      <c r="AM17" s="197"/>
+      <c r="AN17" s="197"/>
+      <c r="AO17" s="197"/>
+      <c r="AP17" s="197"/>
+      <c r="AQ17" s="197"/>
+      <c r="AR17" s="197"/>
+      <c r="AS17" s="197"/>
+      <c r="AT17" s="197"/>
+      <c r="AU17" s="197"/>
+      <c r="AV17" s="197"/>
+      <c r="AW17" s="197"/>
+      <c r="AX17" s="197"/>
+      <c r="AY17" s="197"/>
+      <c r="AZ17" s="197"/>
+      <c r="BA17" s="197"/>
+      <c r="BB17" s="197"/>
+      <c r="BC17" s="197"/>
+      <c r="BD17" s="197"/>
+      <c r="BE17" s="197"/>
+      <c r="BF17" s="197"/>
+      <c r="BG17" s="197"/>
       <c r="BH17" s="7"/>
     </row>
     <row r="18" spans="1:62" ht="39" x14ac:dyDescent="0.35">
@@ -20654,7 +20333,9 @@
       <c r="BI20" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="BJ20" s="31"/>
+      <c r="BJ20" s="31" t="s">
+        <v>836</v>
+      </c>
     </row>
     <row r="21" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="118"/>
@@ -21872,8 +21553,8 @@
       <c r="BI30" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="BJ30" s="31" t="s">
-        <v>802</v>
+      <c r="BJ30" s="207" t="s">
+        <v>835</v>
       </c>
     </row>
     <row r="31" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -22487,7 +22168,7 @@
       <c r="BH35" s="71"/>
       <c r="BI35" s="126"/>
       <c r="BJ35" s="31" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="36" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -22733,7 +22414,7 @@
         <v>1</v>
       </c>
       <c r="BJ37" s="31" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="38" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -22870,13 +22551,13 @@
         <v>308</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F39" s="6">
         <v>1079783</v>
       </c>
-      <c r="G39" s="205" t="s">
-        <v>804</v>
+      <c r="G39" s="195" t="s">
+        <v>803</v>
       </c>
       <c r="H39" s="129">
         <v>1070</v>
@@ -23471,7 +23152,7 @@
         <v>1</v>
       </c>
       <c r="BJ43" s="31" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="44" spans="1:62" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -23595,7 +23276,7 @@
         <v>1</v>
       </c>
       <c r="BJ44" s="31" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="45" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -23841,7 +23522,7 @@
       <c r="BH46" s="71"/>
       <c r="BI46" s="2"/>
       <c r="BJ46" s="31" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="47" spans="1:62" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -24592,13 +24273,13 @@
         <v>308</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F53" s="6">
         <v>1079786</v>
       </c>
       <c r="G53" s="162" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H53" s="129">
         <v>500</v>
@@ -25067,7 +24748,7 @@
       <c r="BH56" s="71"/>
       <c r="BI56" s="2"/>
       <c r="BJ56" s="31" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="57" spans="1:62" ht="14" customHeight="1" x14ac:dyDescent="0.35">
@@ -25191,7 +24872,7 @@
         <v>1</v>
       </c>
       <c r="BJ57" s="31" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="58" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -25335,7 +25016,7 @@
       <c r="F59" s="61">
         <v>1074164</v>
       </c>
-      <c r="G59" s="206" t="s">
+      <c r="G59" s="196" t="s">
         <v>700</v>
       </c>
       <c r="H59" s="129">
@@ -26186,13 +25867,13 @@
         <v>308</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F66" s="6">
         <v>1079785</v>
       </c>
       <c r="G66" s="162" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H66" s="129">
         <v>500</v>
@@ -27153,7 +26834,7 @@
         <v>1</v>
       </c>
       <c r="BJ73" s="31" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="74" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -27402,7 +27083,7 @@
         <v>1</v>
       </c>
       <c r="BJ75" s="31" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="76" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -27774,7 +27455,7 @@
         <v>1</v>
       </c>
       <c r="BJ78" s="31" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="79" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -28388,7 +28069,7 @@
         <v>1</v>
       </c>
       <c r="BJ83" s="31" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="84" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -28403,13 +28084,13 @@
         <v>308</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F84" s="6">
         <v>1079784</v>
       </c>
       <c r="G84" s="162" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H84" s="129">
         <v>1000</v>
@@ -28630,7 +28311,7 @@
       <c r="BH85" s="71"/>
       <c r="BI85" s="126"/>
       <c r="BJ85" s="31" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="86" spans="1:62" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -28878,7 +28559,7 @@
         <v>1</v>
       </c>
       <c r="BJ87" s="31" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="88" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -29856,7 +29537,7 @@
       <c r="BH95" s="71"/>
       <c r="BI95" s="2"/>
       <c r="BJ95" s="31" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="96" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -30098,7 +29779,7 @@
       <c r="BH97" s="71"/>
       <c r="BI97" s="126"/>
       <c r="BJ97" s="31" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="98" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -30350,7 +30031,7 @@
         <v>1</v>
       </c>
       <c r="BJ99" s="31" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="100" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -31210,7 +30891,7 @@
       <c r="BH106" s="71"/>
       <c r="BI106" s="2"/>
       <c r="BJ106" s="31" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="107" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -31336,7 +31017,7 @@
         <v>1</v>
       </c>
       <c r="BJ107" s="31" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="108" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -32802,7 +32483,7 @@
         <v>1</v>
       </c>
       <c r="BJ119" s="31" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="120" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -32926,7 +32607,7 @@
         <v>1</v>
       </c>
       <c r="BJ120" s="31" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="121" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -33790,7 +33471,7 @@
       <c r="BH127" s="71"/>
       <c r="BI127" s="2"/>
       <c r="BJ127" s="31" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="128" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -34276,7 +33957,7 @@
         <v>1</v>
       </c>
       <c r="BJ131" s="31" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="132" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -35132,7 +34813,7 @@
         <v>1</v>
       </c>
       <c r="BJ138" s="31" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="139" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -36854,7 +36535,7 @@
         <v>1</v>
       </c>
       <c r="BJ152" s="31" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="153" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -37096,7 +36777,7 @@
       <c r="BH154" s="71"/>
       <c r="BI154" s="126"/>
       <c r="BJ154" s="31" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="155" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -38068,7 +37749,7 @@
       <c r="BH162" s="71"/>
       <c r="BI162" s="2"/>
       <c r="BJ162" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="163" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -38316,7 +37997,7 @@
         <v>1</v>
       </c>
       <c r="BJ164" s="31" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="165" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -84997,7 +84678,7 @@
         <v>1083416</v>
       </c>
       <c r="G546" s="194" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H546" s="176">
         <v>0</v>
@@ -85109,128 +84790,110 @@
   </mergeCells>
   <phoneticPr fontId="33" type="noConversion"/>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="126" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18">
-    <cfRule type="duplicateValues" dxfId="125" priority="400"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="400"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="duplicateValues" dxfId="30" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="duplicateValues" dxfId="29" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28:F34">
+    <cfRule type="duplicateValues" dxfId="28" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F59">
+    <cfRule type="duplicateValues" dxfId="27" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F60:F98 F261:F299 F118:F125 F100:F116 F216:F225 F127:F207 F482 F426:F472 F353:F388 F209:F214 F238:F251 F253:F259 F303:F314 F301 F485:F515 F474:F480 F390:F424 F227:F236 F35:F58 F26:F27 F20:F24 F316:F351">
+    <cfRule type="duplicateValues" dxfId="26" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F99">
+    <cfRule type="duplicateValues" dxfId="25" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F117">
+    <cfRule type="duplicateValues" dxfId="24" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F126">
+    <cfRule type="duplicateValues" dxfId="23" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F208">
+    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F215">
+    <cfRule type="duplicateValues" dxfId="21" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F226">
+    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F237">
+    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F252">
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F260">
+    <cfRule type="duplicateValues" dxfId="17" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F300">
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F302">
+    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F315">
+    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F352">
+    <cfRule type="duplicateValues" dxfId="13" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F389">
+    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F425">
+    <cfRule type="duplicateValues" dxfId="11" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F473">
+    <cfRule type="duplicateValues" dxfId="10" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F483">
+    <cfRule type="duplicateValues" dxfId="9" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F484">
+    <cfRule type="duplicateValues" dxfId="8" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F521">
+    <cfRule type="duplicateValues" dxfId="7" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F522">
+    <cfRule type="duplicateValues" dxfId="6" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F523:F524">
+    <cfRule type="duplicateValues" dxfId="5" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G45">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:O18">
-    <cfRule type="expression" dxfId="97" priority="306" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="306" stopIfTrue="1">
       <formula>"g4&gt;1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P18">
-    <cfRule type="expression" dxfId="96" priority="305" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="305" stopIfTrue="1">
       <formula>"g4&gt;1"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y508:Y514 Y19:Y479">
-    <cfRule type="cellIs" dxfId="93" priority="7" operator="between">
+  <conditionalFormatting sqref="Y19:Y514">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
       <formula>5</formula>
       <formula>10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>5</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y480">
-    <cfRule type="cellIs" dxfId="91" priority="4" operator="between">
-      <formula>5</formula>
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="5" operator="lessThan">
-      <formula>5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y481:Y507">
-    <cfRule type="cellIs" dxfId="89" priority="2" operator="between">
-      <formula>5</formula>
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="3" operator="lessThan">
-      <formula>5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G45">
-    <cfRule type="duplicateValues" dxfId="87" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F60:F98 F261:F299 F118:F125 F100:F116 F216:F225 F127:F207 F482 F426:F472 F353:F388 F209:F214 F238:F251 F253:F259 F303:F314 F301 F485:F515 F474:F480 F390:F424 F227:F236 F35:F58 F26:F27 F20:F24 F316:F351">
-    <cfRule type="duplicateValues" dxfId="86" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F315">
-    <cfRule type="duplicateValues" dxfId="85" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F226">
-    <cfRule type="duplicateValues" dxfId="84" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F389">
-    <cfRule type="duplicateValues" dxfId="83" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F473">
-    <cfRule type="duplicateValues" dxfId="82" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F483">
-    <cfRule type="duplicateValues" dxfId="81" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F484">
-    <cfRule type="duplicateValues" dxfId="80" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F300">
-    <cfRule type="duplicateValues" dxfId="79" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F302">
-    <cfRule type="duplicateValues" dxfId="78" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F252">
-    <cfRule type="duplicateValues" dxfId="77" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F237">
-    <cfRule type="duplicateValues" dxfId="76" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F208">
-    <cfRule type="duplicateValues" dxfId="75" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F352">
-    <cfRule type="duplicateValues" dxfId="74" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F425">
-    <cfRule type="duplicateValues" dxfId="73" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F521">
-    <cfRule type="duplicateValues" dxfId="72" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F28:F34">
-    <cfRule type="duplicateValues" dxfId="71" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
-    <cfRule type="duplicateValues" dxfId="70" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F523:F524">
-    <cfRule type="duplicateValues" dxfId="69" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F522">
-    <cfRule type="duplicateValues" dxfId="68" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F126">
-    <cfRule type="duplicateValues" dxfId="67" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F215">
-    <cfRule type="duplicateValues" dxfId="66" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F59">
-    <cfRule type="duplicateValues" dxfId="65" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F99">
-    <cfRule type="duplicateValues" dxfId="64" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F117">
-    <cfRule type="duplicateValues" dxfId="63" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F260">
-    <cfRule type="duplicateValues" dxfId="62" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="61" priority="36"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="18" orientation="portrait" horizontalDpi="300" r:id="rId1"/>
@@ -85243,25 +84906,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="9" id="{F609D9FD-1A46-4AC1-B563-A741C31CD9E5}">
-            <x14:iconSet custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>10</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>46</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3TrafficLights1" iconId="0"/>
-              <x14:cfIcon iconSet="3TrafficLights1" iconId="2"/>
-              <x14:cfIcon iconSet="3TrafficLights1" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>Y508:Y514 Y19:Y479</xm:sqref>
-        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="6" id="{0A451A67-8228-47B3-BC45-8A2F82FCB882}">
             <x14:iconSet custom="1">
@@ -85300,6 +84944,25 @@
           </x14:cfRule>
           <xm:sqref>Y481:Y507</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="9" id="{F609D9FD-1A46-4AC1-B563-A741C31CD9E5}">
+            <x14:iconSet custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>10</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>46</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3TrafficLights1" iconId="0"/>
+              <x14:cfIcon iconSet="3TrafficLights1" iconId="2"/>
+              <x14:cfIcon iconSet="3TrafficLights1" iconId="0"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>Y508:Y514 Y19:Y479</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/datos_stock.xlsx
+++ b/datos_stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fpjmojeda\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF552E6-107E-45EF-8833-E7CA2DCE164A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E421178B-7D04-43D2-A373-07AE62150EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12300" tabRatio="813" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5173" uniqueCount="805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5178" uniqueCount="809">
   <si>
     <t>GLINA. MONTBLANC ESTUCHE16ESTX7UN INT NG GEMA</t>
   </si>
@@ -2461,6 +2461,18 @@
 El 23/04 ingresa 99,000 und
 El 24/04 ingresa 49,632 und</t>
   </si>
+  <si>
+    <t>Ingresa el día 22/04/24 un total de 3,520 cajas</t>
+  </si>
+  <si>
+    <t>Se estima para los últimos días del mes de Abril</t>
+  </si>
+  <si>
+    <t>Producto bloqueado, se debe de vender la referencia de Ole Ole San Valentin</t>
+  </si>
+  <si>
+    <t>Debido a la falta de rotación el SKU se encuentra bloqueso por encontrarse menor a 3 meses de vida útil</t>
+  </si>
 </sst>
 </file>
 
@@ -4228,36 +4240,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="7" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="7" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="7" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="47" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4303,6 +4285,36 @@
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -4365,7 +4377,531 @@
     <cellStyle name="Título 3" xfId="13" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="26" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="209">
+  <dxfs count="143">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4378,17 +4914,183 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color auto="1"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -6709,336 +7411,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <border outline="0">
         <left style="dashed">
           <color indexed="64"/>
@@ -7050,6 +7422,30 @@
           <color indexed="64"/>
         </top>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -7084,1050 +7480,6 @@
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF002060"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -8431,34 +7783,34 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="PivotStyleMedium6 2" table="0" count="13" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="208"/>
-      <tableStyleElement type="headerRow" dxfId="207"/>
-      <tableStyleElement type="totalRow" dxfId="206"/>
-      <tableStyleElement type="firstRowStripe" dxfId="205"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="204"/>
-      <tableStyleElement type="firstHeaderCell" dxfId="203"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="202"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="201"/>
-      <tableStyleElement type="firstColumnSubheading" dxfId="200"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="199"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="198"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="197"/>
-      <tableStyleElement type="pageFieldValues" dxfId="196"/>
+      <tableStyleElement type="wholeTable" dxfId="142"/>
+      <tableStyleElement type="headerRow" dxfId="141"/>
+      <tableStyleElement type="totalRow" dxfId="140"/>
+      <tableStyleElement type="firstRowStripe" dxfId="139"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="138"/>
+      <tableStyleElement type="firstHeaderCell" dxfId="137"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="136"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="135"/>
+      <tableStyleElement type="firstColumnSubheading" dxfId="134"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="133"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="132"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="131"/>
+      <tableStyleElement type="pageFieldValues" dxfId="130"/>
     </tableStyle>
     <tableStyle name="PivotStyleMedium6 3" table="0" count="13" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" dxfId="195"/>
-      <tableStyleElement type="headerRow" dxfId="194"/>
-      <tableStyleElement type="totalRow" dxfId="193"/>
-      <tableStyleElement type="firstRowStripe" dxfId="192"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="191"/>
-      <tableStyleElement type="firstHeaderCell" dxfId="190"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="189"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="188"/>
-      <tableStyleElement type="firstColumnSubheading" dxfId="187"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="186"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="185"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="184"/>
-      <tableStyleElement type="pageFieldValues" dxfId="183"/>
+      <tableStyleElement type="wholeTable" dxfId="129"/>
+      <tableStyleElement type="headerRow" dxfId="128"/>
+      <tableStyleElement type="totalRow" dxfId="127"/>
+      <tableStyleElement type="firstRowStripe" dxfId="126"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="125"/>
+      <tableStyleElement type="firstHeaderCell" dxfId="124"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="123"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="122"/>
+      <tableStyleElement type="firstColumnSubheading" dxfId="121"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="120"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="119"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="118"/>
+      <tableStyleElement type="pageFieldValues" dxfId="117"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -8484,94 +7836,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TMR" displayName="TMR" ref="B2:L222" totalsRowShown="0" headerRowDxfId="182" dataDxfId="180" headerRowBorderDxfId="181" tableBorderDxfId="179" totalsRowBorderDxfId="178">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TMR" displayName="TMR" ref="B2:L222" totalsRowShown="0" headerRowDxfId="52" dataDxfId="50" headerRowBorderDxfId="51" tableBorderDxfId="49" totalsRowBorderDxfId="48">
   <autoFilter ref="B2:L222" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="CÓDIGO" dataDxfId="177"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="DESCRIPCIÓN" dataDxfId="176"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="ORIGEN" dataDxfId="175"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="CATEGORÍA" dataDxfId="174"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Tiempo de Vida" dataDxfId="173"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tottus" dataDxfId="172">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="CÓDIGO" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="DESCRIPCIÓN" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="ORIGEN" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="CATEGORÍA" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Tiempo de Vida" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tottus" dataDxfId="42">
       <calculatedColumnFormula>IF(F3&lt;=210,F3*0.6,IF(F3&lt;=365,120,IF(F3&lt;=3600,150)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Cencosud" dataDxfId="171"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Tambo" dataDxfId="170"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Oxxo" dataDxfId="169"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPSA / MAKRO" dataDxfId="168">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Cencosud" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Tambo" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Oxxo" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPSA / MAKRO" dataDxfId="38">
       <calculatedColumnFormula>ROUNDDOWN(F3/3,0)-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Canal Tradicional / Otros" dataDxfId="167"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Canal Tradicional / Otros" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Principal" displayName="Principal" ref="B18:BJ546" totalsRowShown="0" headerRowDxfId="96" dataDxfId="0" tableBorderDxfId="95" headerRowCellStyle="Normal 10 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Principal" displayName="Principal" ref="B18:BJ546" totalsRowShown="0" headerRowDxfId="116" dataDxfId="115" tableBorderDxfId="114" headerRowCellStyle="Normal 10 2">
   <autoFilter ref="B18:BJ546" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="61">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="RESPONSABLE DE PRODUCCIÓN" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="GEOGRAFÍA" dataDxfId="60"/>
-    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="CATEGORÍA" dataDxfId="59"/>
-    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="MARCA" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="CÓDIGO" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="DESCRIPCIÓN" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Plan de demanda" dataDxfId="55"/>
-    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="Plan Demanda (Kg)" dataDxfId="54"/>
-    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Salidas varias" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Avance Vta." dataDxfId="52"/>
-    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Avance _x000a_Vta. (Kg)" dataDxfId="51" dataCellStyle="Porcentaje"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="%V Mes actual" dataDxfId="50" dataCellStyle="Porcentaje"/>
-    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="Error ABS_x000a_(KG)" dataDxfId="49" dataCellStyle="Porcentaje"/>
-    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Días consumidos por sobreventa en el mes pasado" dataDxfId="48" dataCellStyle="Porcentaje"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="%V Mes pasado" dataDxfId="47" dataCellStyle="Porcentaje"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="STOCK TOTAL" dataDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="STOCK POR FACTURAR" dataDxfId="45"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="CEDI FINAL" dataDxfId="44"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="PLANTA" dataDxfId="43"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="TRANSITO" dataDxfId="42"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="CALIDAD" dataDxfId="41"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="BLOQUEADO" dataDxfId="40"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Vta. Proy." dataDxfId="39"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Días De Inventario" dataDxfId="38"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Faltante" dataDxfId="37"/>
-    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="Valorizado Plan de Demanda" dataDxfId="36" dataCellStyle="Moneda"/>
-    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="Valorizado Stock" dataDxfId="35" dataCellStyle="Moneda"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="% Cob." dataDxfId="34" dataCellStyle="Porcentaje"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="1" dataDxfId="33"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="2" dataDxfId="32"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="3" dataDxfId="31"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="4" dataDxfId="30"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="5" dataDxfId="29"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="6" dataDxfId="28"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="7" dataDxfId="27"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="8" dataDxfId="26"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="9" dataDxfId="25"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="10" dataDxfId="24"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="11" dataDxfId="23"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="12" dataDxfId="22"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="13" dataDxfId="21"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="14" dataDxfId="20"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="15" dataDxfId="19"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="16" dataDxfId="18"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="17" dataDxfId="17"/>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="18" dataDxfId="16"/>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="19" dataDxfId="15"/>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="20" dataDxfId="14"/>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="21" dataDxfId="13"/>
-    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="22" dataDxfId="12"/>
-    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="23" dataDxfId="11"/>
-    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="24" dataDxfId="10"/>
-    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="25" dataDxfId="9"/>
-    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="26" dataDxfId="8"/>
-    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="27" dataDxfId="7"/>
-    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="28" dataDxfId="6"/>
-    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="29" dataDxfId="5"/>
-    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="30" dataDxfId="4"/>
-    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="31" dataDxfId="3"/>
-    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Fecha de _x000a_Ingreso según RAS" dataDxfId="2" dataCellStyle="Millares 10"/>
-    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="Causal / Observado" dataDxfId="1" dataCellStyle="Millares 10"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="RESPONSABLE DE PRODUCCIÓN" dataDxfId="113"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="GEOGRAFÍA" dataDxfId="112"/>
+    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="CATEGORÍA" dataDxfId="111"/>
+    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="MARCA" dataDxfId="110"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="CÓDIGO" dataDxfId="109"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="DESCRIPCIÓN" dataDxfId="108"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Plan de demanda" dataDxfId="107"/>
+    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="Plan Demanda (Kg)" dataDxfId="106"/>
+    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Salidas varias" dataDxfId="105"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Avance Vta." dataDxfId="104"/>
+    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Avance _x000a_Vta. (Kg)" dataDxfId="103" dataCellStyle="Porcentaje"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="%V Mes actual" dataDxfId="102" dataCellStyle="Porcentaje"/>
+    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="Error ABS_x000a_(KG)" dataDxfId="101" dataCellStyle="Porcentaje"/>
+    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Días consumidos por sobreventa en el mes pasado" dataDxfId="100" dataCellStyle="Porcentaje"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="%V Mes pasado" dataDxfId="99" dataCellStyle="Porcentaje"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="STOCK TOTAL" dataDxfId="98"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="STOCK POR FACTURAR" dataDxfId="97"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="CEDI FINAL" dataDxfId="96"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="PLANTA" dataDxfId="95"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="TRANSITO" dataDxfId="94"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="CALIDAD" dataDxfId="93"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="BLOQUEADO" dataDxfId="92"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Vta. Proy." dataDxfId="91"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Días De Inventario" dataDxfId="90"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Faltante" dataDxfId="89"/>
+    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="Valorizado Plan de Demanda" dataDxfId="88" dataCellStyle="Moneda"/>
+    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="Valorizado Stock" dataDxfId="87" dataCellStyle="Moneda"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="% Cob." dataDxfId="86" dataCellStyle="Porcentaje"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="1" dataDxfId="85"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="2" dataDxfId="84"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="3" dataDxfId="83"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="4" dataDxfId="82"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="5" dataDxfId="81"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="6" dataDxfId="80"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="7" dataDxfId="79"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="8" dataDxfId="78"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="9" dataDxfId="77"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="10" dataDxfId="76"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="11" dataDxfId="75"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="12" dataDxfId="74"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="13" dataDxfId="73"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="14" dataDxfId="72"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="15" dataDxfId="71"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="16" dataDxfId="70"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="17" dataDxfId="69"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="18" dataDxfId="68"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="19" dataDxfId="67"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="20" dataDxfId="66"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="21" dataDxfId="65"/>
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="22" dataDxfId="64"/>
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="23" dataDxfId="63"/>
+    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="24" dataDxfId="62"/>
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="25" dataDxfId="61"/>
+    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="26" dataDxfId="60"/>
+    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="27" dataDxfId="59"/>
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="28" dataDxfId="58"/>
+    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="29" dataDxfId="57"/>
+    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="30" dataDxfId="56"/>
+    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="31" dataDxfId="55"/>
+    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Fecha de _x000a_Ingreso según RAS" dataDxfId="54" dataCellStyle="Millares 10"/>
+    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="Causal / Observado" dataDxfId="53" dataCellStyle="Millares 10"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17001,10 +16353,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="166" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B222">
-    <cfRule type="duplicateValues" dxfId="165" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" copies="0" r:id="rId1"/>
@@ -18192,10 +17544,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="164" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2">
-    <cfRule type="duplicateValues" dxfId="163" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" copies="0" r:id="rId1"/>
@@ -18261,25 +17613,25 @@
     </row>
     <row r="2" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="118"/>
-      <c r="B2" s="180" t="s">
+      <c r="B2" s="196" t="s">
         <v>341</v>
       </c>
-      <c r="C2" s="181"/>
-      <c r="D2" s="181"/>
-      <c r="E2" s="181"/>
-      <c r="F2" s="181"/>
-      <c r="G2" s="184">
+      <c r="C2" s="197"/>
+      <c r="D2" s="197"/>
+      <c r="E2" s="197"/>
+      <c r="F2" s="197"/>
+      <c r="G2" s="200">
         <v>46133</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="118"/>
-      <c r="B3" s="182"/>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="185"/>
+      <c r="B3" s="198"/>
+      <c r="C3" s="199"/>
+      <c r="D3" s="199"/>
+      <c r="E3" s="199"/>
+      <c r="F3" s="199"/>
+      <c r="G3" s="201"/>
     </row>
     <row r="4" spans="1:62" x14ac:dyDescent="0.35">
       <c r="A4" s="118"/>
@@ -18528,55 +17880,55 @@
       <c r="M17" s="20"/>
       <c r="N17" s="94"/>
       <c r="O17" s="21"/>
-      <c r="Q17" s="186" t="s">
+      <c r="Q17" s="202" t="s">
         <v>342</v>
       </c>
-      <c r="R17" s="187"/>
-      <c r="S17" s="188"/>
-      <c r="T17" s="186" t="s">
+      <c r="R17" s="203"/>
+      <c r="S17" s="204"/>
+      <c r="T17" s="202" t="s">
         <v>497</v>
       </c>
-      <c r="U17" s="187"/>
-      <c r="V17" s="187"/>
-      <c r="W17" s="187"/>
+      <c r="U17" s="203"/>
+      <c r="V17" s="203"/>
+      <c r="W17" s="203"/>
       <c r="X17" s="28"/>
       <c r="Y17" s="28"/>
       <c r="Z17" s="26"/>
       <c r="AA17" s="26"/>
       <c r="AB17" s="26"/>
-      <c r="AC17" s="179" t="s">
+      <c r="AC17" s="195" t="s">
         <v>331</v>
       </c>
-      <c r="AD17" s="179"/>
-      <c r="AE17" s="179"/>
-      <c r="AF17" s="179"/>
-      <c r="AG17" s="179"/>
-      <c r="AH17" s="179"/>
-      <c r="AI17" s="179"/>
-      <c r="AJ17" s="179"/>
-      <c r="AK17" s="179"/>
-      <c r="AL17" s="179"/>
-      <c r="AM17" s="179"/>
-      <c r="AN17" s="179"/>
-      <c r="AO17" s="179"/>
-      <c r="AP17" s="179"/>
-      <c r="AQ17" s="179"/>
-      <c r="AR17" s="179"/>
-      <c r="AS17" s="179"/>
-      <c r="AT17" s="179"/>
-      <c r="AU17" s="179"/>
-      <c r="AV17" s="179"/>
-      <c r="AW17" s="179"/>
-      <c r="AX17" s="179"/>
-      <c r="AY17" s="179"/>
-      <c r="AZ17" s="179"/>
-      <c r="BA17" s="179"/>
-      <c r="BB17" s="179"/>
-      <c r="BC17" s="179"/>
-      <c r="BD17" s="179"/>
-      <c r="BE17" s="179"/>
-      <c r="BF17" s="179"/>
-      <c r="BG17" s="179"/>
+      <c r="AD17" s="195"/>
+      <c r="AE17" s="195"/>
+      <c r="AF17" s="195"/>
+      <c r="AG17" s="195"/>
+      <c r="AH17" s="195"/>
+      <c r="AI17" s="195"/>
+      <c r="AJ17" s="195"/>
+      <c r="AK17" s="195"/>
+      <c r="AL17" s="195"/>
+      <c r="AM17" s="195"/>
+      <c r="AN17" s="195"/>
+      <c r="AO17" s="195"/>
+      <c r="AP17" s="195"/>
+      <c r="AQ17" s="195"/>
+      <c r="AR17" s="195"/>
+      <c r="AS17" s="195"/>
+      <c r="AT17" s="195"/>
+      <c r="AU17" s="195"/>
+      <c r="AV17" s="195"/>
+      <c r="AW17" s="195"/>
+      <c r="AX17" s="195"/>
+      <c r="AY17" s="195"/>
+      <c r="AZ17" s="195"/>
+      <c r="BA17" s="195"/>
+      <c r="BB17" s="195"/>
+      <c r="BC17" s="195"/>
+      <c r="BD17" s="195"/>
+      <c r="BE17" s="195"/>
+      <c r="BF17" s="195"/>
+      <c r="BG17" s="195"/>
       <c r="BH17" s="7"/>
     </row>
     <row r="18" spans="1:62" ht="39" x14ac:dyDescent="0.35">
@@ -18883,7 +18235,9 @@
       <c r="BG19" s="71"/>
       <c r="BH19" s="71"/>
       <c r="BI19" s="2"/>
-      <c r="BJ19" s="31"/>
+      <c r="BJ19" s="31" t="s">
+        <v>806</v>
+      </c>
     </row>
     <row r="20" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="118"/>
@@ -19373,7 +18727,9 @@
       <c r="BI23" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="BJ23" s="31"/>
+      <c r="BJ23" s="31" t="s">
+        <v>807</v>
+      </c>
     </row>
     <row r="24" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="118"/>
@@ -19617,7 +18973,9 @@
       <c r="BG25" s="71"/>
       <c r="BH25" s="71"/>
       <c r="BI25" s="2"/>
-      <c r="BJ25" s="31"/>
+      <c r="BJ25" s="31" t="s">
+        <v>805</v>
+      </c>
     </row>
     <row r="26" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="118"/>
@@ -19741,7 +19099,9 @@
       <c r="BI26" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="BJ26" s="31"/>
+      <c r="BJ26" s="31" t="s">
+        <v>805</v>
+      </c>
     </row>
     <row r="27" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="118"/>
@@ -20229,7 +19589,9 @@
       <c r="BI30" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="BJ30" s="31"/>
+      <c r="BJ30" s="31" t="s">
+        <v>808</v>
+      </c>
     </row>
     <row r="31" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="118"/>
@@ -48790,10 +48152,10 @@
       <c r="E264" s="116" t="s">
         <v>319</v>
       </c>
-      <c r="F264" s="189">
+      <c r="F264" s="179">
         <v>1072625</v>
       </c>
-      <c r="G264" s="190" t="s">
+      <c r="G264" s="180" t="s">
         <v>623</v>
       </c>
       <c r="H264" s="129">
@@ -49286,10 +48648,10 @@
       <c r="E268" s="116" t="s">
         <v>319</v>
       </c>
-      <c r="F268" s="191">
+      <c r="F268" s="181">
         <v>1067806</v>
       </c>
-      <c r="G268" s="192" t="s">
+      <c r="G268" s="182" t="s">
         <v>638</v>
       </c>
       <c r="H268" s="129">
@@ -49780,10 +49142,10 @@
       <c r="E272" s="116" t="s">
         <v>319</v>
       </c>
-      <c r="F272" s="189">
+      <c r="F272" s="179">
         <v>1072796</v>
       </c>
-      <c r="G272" s="190" t="s">
+      <c r="G272" s="180" t="s">
         <v>626</v>
       </c>
       <c r="H272" s="129">
@@ -50028,10 +49390,10 @@
       <c r="E274" s="116" t="s">
         <v>319</v>
       </c>
-      <c r="F274" s="189">
+      <c r="F274" s="179">
         <v>1067805</v>
       </c>
-      <c r="G274" s="190" t="s">
+      <c r="G274" s="180" t="s">
         <v>644</v>
       </c>
       <c r="H274" s="129">
@@ -50398,10 +49760,10 @@
       <c r="E277" s="116" t="s">
         <v>319</v>
       </c>
-      <c r="F277" s="193">
+      <c r="F277" s="183">
         <v>1072517</v>
       </c>
-      <c r="G277" s="194" t="s">
+      <c r="G277" s="184" t="s">
         <v>637</v>
       </c>
       <c r="H277" s="129">
@@ -52732,10 +52094,10 @@
       <c r="E296" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="F296" s="195">
+      <c r="F296" s="185">
         <v>1083041</v>
       </c>
-      <c r="G296" s="196" t="s">
+      <c r="G296" s="186" t="s">
         <v>784</v>
       </c>
       <c r="H296" s="129">
@@ -52853,10 +52215,10 @@
       <c r="E297" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="F297" s="195">
+      <c r="F297" s="185">
         <v>1082951</v>
       </c>
-      <c r="G297" s="196" t="s">
+      <c r="G297" s="186" t="s">
         <v>783</v>
       </c>
       <c r="H297" s="129">
@@ -55298,7 +54660,7 @@
       <c r="F317" s="6">
         <v>1083381</v>
       </c>
-      <c r="G317" s="197" t="s">
+      <c r="G317" s="187" t="s">
         <v>790</v>
       </c>
       <c r="H317" s="129">
@@ -61903,10 +61265,10 @@
       <c r="E371" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="F371" s="195">
+      <c r="F371" s="185">
         <v>1083253</v>
       </c>
-      <c r="G371" s="196" t="s">
+      <c r="G371" s="186" t="s">
         <v>780</v>
       </c>
       <c r="H371" s="129">
@@ -64602,7 +63964,7 @@
       <c r="F393" s="6">
         <v>1083108</v>
       </c>
-      <c r="G393" s="198" t="s">
+      <c r="G393" s="188" t="s">
         <v>778</v>
       </c>
       <c r="H393" s="129">
@@ -64723,7 +64085,7 @@
       <c r="F394" s="6">
         <v>1083107</v>
       </c>
-      <c r="G394" s="198" t="s">
+      <c r="G394" s="188" t="s">
         <v>777</v>
       </c>
       <c r="H394" s="129">
@@ -70946,7 +70308,7 @@
       <c r="F445" s="154">
         <v>1083117</v>
       </c>
-      <c r="G445" s="199" t="s">
+      <c r="G445" s="189" t="s">
         <v>779</v>
       </c>
       <c r="H445" s="129">
@@ -80955,10 +80317,10 @@
       <c r="E527" s="173" t="s">
         <v>317</v>
       </c>
-      <c r="F527" s="200">
+      <c r="F527" s="190">
         <v>1053203</v>
       </c>
-      <c r="G527" s="201" t="s">
+      <c r="G527" s="191" t="s">
         <v>499</v>
       </c>
       <c r="H527" s="129">
@@ -83286,10 +82648,10 @@
       <c r="E546" s="174" t="s">
         <v>315</v>
       </c>
-      <c r="F546" s="202">
+      <c r="F546" s="192">
         <v>1075202</v>
       </c>
-      <c r="G546" s="203" t="s">
+      <c r="G546" s="193" t="s">
         <v>641</v>
       </c>
       <c r="H546" s="168">
@@ -83389,7 +82751,7 @@
       <c r="BF546" s="72"/>
       <c r="BG546" s="72"/>
       <c r="BH546" s="72"/>
-      <c r="BI546" s="204"/>
+      <c r="BI546" s="194"/>
       <c r="BJ546" s="176"/>
     </row>
   </sheetData>
@@ -83402,128 +82764,110 @@
   </mergeCells>
   <phoneticPr fontId="33" type="noConversion"/>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="162" priority="460"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="460"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18">
-    <cfRule type="duplicateValues" dxfId="161" priority="688"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="688"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="duplicateValues" dxfId="30" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="duplicateValues" dxfId="29" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28:F34">
+    <cfRule type="duplicateValues" dxfId="28" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F59">
+    <cfRule type="duplicateValues" dxfId="27" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F60:F98 F261:F299 F118:F125 F100:F116 F216:F225 F127:F207 F482 F426:F472 F353:F388 F209:F214 F238:F251 F253:F259 F303:F314 F301 F485:F515 F474:F480 F390:F424 F227:F236 F35:F58 F26:F27 F20:F24 F316:F351">
+    <cfRule type="duplicateValues" dxfId="26" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F99">
+    <cfRule type="duplicateValues" dxfId="25" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F117">
+    <cfRule type="duplicateValues" dxfId="24" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F126">
+    <cfRule type="duplicateValues" dxfId="23" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F208">
+    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F215">
+    <cfRule type="duplicateValues" dxfId="21" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F226">
+    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F237">
+    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F252">
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F260">
+    <cfRule type="duplicateValues" dxfId="17" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F300">
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F302">
+    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F315">
+    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F352">
+    <cfRule type="duplicateValues" dxfId="13" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F389">
+    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F425">
+    <cfRule type="duplicateValues" dxfId="11" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F473">
+    <cfRule type="duplicateValues" dxfId="10" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F483">
+    <cfRule type="duplicateValues" dxfId="9" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F484">
+    <cfRule type="duplicateValues" dxfId="8" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F521">
+    <cfRule type="duplicateValues" dxfId="7" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F522">
+    <cfRule type="duplicateValues" dxfId="6" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F523:F524">
+    <cfRule type="duplicateValues" dxfId="5" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G45">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:O18">
-    <cfRule type="expression" dxfId="133" priority="594" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="594" stopIfTrue="1">
       <formula>"g4&gt;1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P18">
-    <cfRule type="expression" dxfId="132" priority="593" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="593" stopIfTrue="1">
       <formula>"g4&gt;1"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y508:Y514 Y19:Y479">
-    <cfRule type="cellIs" dxfId="94" priority="7" operator="between">
+  <conditionalFormatting sqref="Y19:Y514">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
       <formula>5</formula>
       <formula>10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>5</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y480">
-    <cfRule type="cellIs" dxfId="92" priority="4" operator="between">
-      <formula>5</formula>
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="5" operator="lessThan">
-      <formula>5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y481:Y507">
-    <cfRule type="cellIs" dxfId="90" priority="2" operator="between">
-      <formula>5</formula>
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="3" operator="lessThan">
-      <formula>5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G45">
-    <cfRule type="duplicateValues" dxfId="88" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F60:F98 F261:F299 F118:F125 F100:F116 F216:F225 F127:F207 F482 F426:F472 F353:F388 F209:F214 F238:F251 F253:F259 F303:F314 F301 F485:F515 F474:F480 F390:F424 F227:F236 F35:F58 F26:F27 F20:F24 F316:F351">
-    <cfRule type="duplicateValues" dxfId="87" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F315">
-    <cfRule type="duplicateValues" dxfId="86" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F226">
-    <cfRule type="duplicateValues" dxfId="85" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F389">
-    <cfRule type="duplicateValues" dxfId="84" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F473">
-    <cfRule type="duplicateValues" dxfId="83" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F483">
-    <cfRule type="duplicateValues" dxfId="82" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F484">
-    <cfRule type="duplicateValues" dxfId="81" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F300">
-    <cfRule type="duplicateValues" dxfId="80" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F302">
-    <cfRule type="duplicateValues" dxfId="79" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F252">
-    <cfRule type="duplicateValues" dxfId="78" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F237">
-    <cfRule type="duplicateValues" dxfId="77" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F208">
-    <cfRule type="duplicateValues" dxfId="76" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F352">
-    <cfRule type="duplicateValues" dxfId="75" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F425">
-    <cfRule type="duplicateValues" dxfId="74" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F521">
-    <cfRule type="duplicateValues" dxfId="73" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F28:F34">
-    <cfRule type="duplicateValues" dxfId="72" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
-    <cfRule type="duplicateValues" dxfId="71" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F523:F524">
-    <cfRule type="duplicateValues" dxfId="70" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F522">
-    <cfRule type="duplicateValues" dxfId="69" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F126">
-    <cfRule type="duplicateValues" dxfId="68" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F215">
-    <cfRule type="duplicateValues" dxfId="67" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F59">
-    <cfRule type="duplicateValues" dxfId="66" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F99">
-    <cfRule type="duplicateValues" dxfId="65" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F117">
-    <cfRule type="duplicateValues" dxfId="64" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F260">
-    <cfRule type="duplicateValues" dxfId="63" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="62" priority="36"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="18" orientation="portrait" horizontalDpi="300" r:id="rId1"/>
@@ -83536,25 +82880,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="9" id="{43602F9F-517A-402D-B554-7FEA1AC504F9}">
-            <x14:iconSet custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>10</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>46</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3TrafficLights1" iconId="0"/>
-              <x14:cfIcon iconSet="3TrafficLights1" iconId="2"/>
-              <x14:cfIcon iconSet="3TrafficLights1" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>Y508:Y514 Y19:Y479</xm:sqref>
-        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="6" id="{B0563D42-B442-4058-A0C6-491823322407}">
             <x14:iconSet custom="1">
@@ -83593,6 +82918,25 @@
           </x14:cfRule>
           <xm:sqref>Y481:Y507</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="9" id="{43602F9F-517A-402D-B554-7FEA1AC504F9}">
+            <x14:iconSet custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>10</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>46</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3TrafficLights1" iconId="0"/>
+              <x14:cfIcon iconSet="3TrafficLights1" iconId="2"/>
+              <x14:cfIcon iconSet="3TrafficLights1" iconId="0"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>Y508:Y514 Y19:Y479</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/datos_stock.xlsx
+++ b/datos_stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fpjmojeda\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F794119B-FA29-4A02-AF29-7EA7C1768D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B3A2ED-FD7E-472D-B792-6330CDC3E1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12300" tabRatio="813" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2457,9 +2457,6 @@
     <t>Cocoa Winters RTS Cjx13ux90g</t>
   </si>
   <si>
-    <t>Ingresa el día 22/04/24 un total de 3,520 cajas</t>
-  </si>
-  <si>
     <t>Se estima para los últimos días del mes de Abril</t>
   </si>
   <si>
@@ -2474,6 +2471,10 @@
   </si>
   <si>
     <t>Ingreso estimado en la 2da quincena de Mayo</t>
+  </si>
+  <si>
+    <t>Ingresa el día 22/04/24 un total de 3,520 cajas
+Ingresa el día 24/04/24 un total de 2,464 cajas</t>
   </si>
 </sst>
 </file>
@@ -4285,6 +4286,15 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4314,15 +4324,6 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="7" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -4385,7 +4386,721 @@
     <cellStyle name="Título 3" xfId="13" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="26" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="176">
+  <dxfs count="143">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -6705,1050 +7420,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF002060"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
       <border outline="0">
         <left style="dashed">
           <color indexed="64"/>
@@ -8121,34 +7792,34 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="PivotStyleMedium6 2" table="0" count="13" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="175"/>
-      <tableStyleElement type="headerRow" dxfId="174"/>
-      <tableStyleElement type="totalRow" dxfId="173"/>
-      <tableStyleElement type="firstRowStripe" dxfId="172"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="171"/>
-      <tableStyleElement type="firstHeaderCell" dxfId="170"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="169"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="168"/>
-      <tableStyleElement type="firstColumnSubheading" dxfId="167"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="166"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="165"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="164"/>
-      <tableStyleElement type="pageFieldValues" dxfId="163"/>
+      <tableStyleElement type="wholeTable" dxfId="142"/>
+      <tableStyleElement type="headerRow" dxfId="141"/>
+      <tableStyleElement type="totalRow" dxfId="140"/>
+      <tableStyleElement type="firstRowStripe" dxfId="139"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="138"/>
+      <tableStyleElement type="firstHeaderCell" dxfId="137"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="136"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="135"/>
+      <tableStyleElement type="firstColumnSubheading" dxfId="134"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="133"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="132"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="131"/>
+      <tableStyleElement type="pageFieldValues" dxfId="130"/>
     </tableStyle>
     <tableStyle name="PivotStyleMedium6 3" table="0" count="13" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" dxfId="162"/>
-      <tableStyleElement type="headerRow" dxfId="161"/>
-      <tableStyleElement type="totalRow" dxfId="160"/>
-      <tableStyleElement type="firstRowStripe" dxfId="159"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="158"/>
-      <tableStyleElement type="firstHeaderCell" dxfId="157"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="156"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="155"/>
-      <tableStyleElement type="firstColumnSubheading" dxfId="154"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="153"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="152"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="151"/>
-      <tableStyleElement type="pageFieldValues" dxfId="150"/>
+      <tableStyleElement type="wholeTable" dxfId="129"/>
+      <tableStyleElement type="headerRow" dxfId="128"/>
+      <tableStyleElement type="totalRow" dxfId="127"/>
+      <tableStyleElement type="firstRowStripe" dxfId="126"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="125"/>
+      <tableStyleElement type="firstHeaderCell" dxfId="124"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="123"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="122"/>
+      <tableStyleElement type="firstColumnSubheading" dxfId="121"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="120"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="119"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="118"/>
+      <tableStyleElement type="pageFieldValues" dxfId="117"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -8174,94 +7845,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TMR" displayName="TMR" ref="B2:L222" totalsRowShown="0" headerRowDxfId="146" dataDxfId="144" headerRowBorderDxfId="145" tableBorderDxfId="143" totalsRowBorderDxfId="142">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TMR" displayName="TMR" ref="B2:L222" totalsRowShown="0" headerRowDxfId="52" dataDxfId="50" headerRowBorderDxfId="51" tableBorderDxfId="49" totalsRowBorderDxfId="48">
   <autoFilter ref="B2:L222" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="CÓDIGO" dataDxfId="141"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="DESCRIPCIÓN" dataDxfId="140"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="ORIGEN" dataDxfId="139"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="CATEGORÍA" dataDxfId="138"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Tiempo de Vida" dataDxfId="137"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tottus" dataDxfId="136">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="CÓDIGO" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="DESCRIPCIÓN" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="ORIGEN" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="CATEGORÍA" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Tiempo de Vida" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tottus" dataDxfId="42">
       <calculatedColumnFormula>IF(F3&lt;=210,F3*0.6,IF(F3&lt;=365,120,IF(F3&lt;=3600,150)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Cencosud" dataDxfId="135"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Tambo" dataDxfId="134"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Oxxo" dataDxfId="133"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPSA / MAKRO" dataDxfId="132">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Cencosud" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Tambo" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Oxxo" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPSA / MAKRO" dataDxfId="38">
       <calculatedColumnFormula>ROUNDDOWN(F3/3,0)-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Canal Tradicional / Otros" dataDxfId="131"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Canal Tradicional / Otros" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Principal" displayName="Principal" ref="B18:BJ546" totalsRowShown="0" headerRowDxfId="149" dataDxfId="148" tableBorderDxfId="147" headerRowCellStyle="Normal 10 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Principal" displayName="Principal" ref="B18:BJ546" totalsRowShown="0" headerRowDxfId="116" dataDxfId="115" tableBorderDxfId="114" headerRowCellStyle="Normal 10 2">
   <autoFilter ref="B18:BJ546" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="61">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="RESPONSABLE DE PRODUCCIÓN" dataDxfId="60"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="GEOGRAFÍA" dataDxfId="59"/>
-    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="CATEGORÍA" dataDxfId="58"/>
-    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="MARCA" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="CÓDIGO" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="DESCRIPCIÓN" dataDxfId="55"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Plan de demanda" dataDxfId="54"/>
-    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="Plan Demanda (Kg)" dataDxfId="53"/>
-    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Salidas varias" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Avance Vta." dataDxfId="51"/>
-    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Avance _x000a_Vta. (Kg)" dataDxfId="50" dataCellStyle="Porcentaje"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="%V Mes actual" dataDxfId="49" dataCellStyle="Porcentaje"/>
-    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="Error ABS_x000a_(KG)" dataDxfId="48" dataCellStyle="Porcentaje"/>
-    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Días consumidos por sobreventa en el mes pasado" dataDxfId="47" dataCellStyle="Porcentaje"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="%V Mes pasado" dataDxfId="46" dataCellStyle="Porcentaje"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="STOCK TOTAL" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="STOCK POR FACTURAR" dataDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="CEDI FINAL" dataDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="PLANTA" dataDxfId="42"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="TRANSITO" dataDxfId="41"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="CALIDAD" dataDxfId="40"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="BLOQUEADO" dataDxfId="39"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Vta. Proy." dataDxfId="38"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Días De Inventario" dataDxfId="37"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Faltante" dataDxfId="36"/>
-    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="Valorizado Plan de Demanda" dataDxfId="35" dataCellStyle="Moneda"/>
-    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="Valorizado Stock" dataDxfId="34" dataCellStyle="Moneda"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="% Cob." dataDxfId="33" dataCellStyle="Porcentaje"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="1" dataDxfId="32"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="2" dataDxfId="31"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="3" dataDxfId="30"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="4" dataDxfId="29"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="5" dataDxfId="28"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="6" dataDxfId="27"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="7" dataDxfId="26"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="8" dataDxfId="25"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="9" dataDxfId="24"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="10" dataDxfId="23"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="11" dataDxfId="22"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="12" dataDxfId="21"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="13" dataDxfId="20"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="14" dataDxfId="19"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="15" dataDxfId="18"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="16" dataDxfId="17"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="17" dataDxfId="16"/>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="18" dataDxfId="15"/>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="19" dataDxfId="14"/>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="20" dataDxfId="13"/>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="21" dataDxfId="12"/>
-    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="22" dataDxfId="11"/>
-    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="23" dataDxfId="10"/>
-    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="24" dataDxfId="9"/>
-    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="25" dataDxfId="8"/>
-    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="26" dataDxfId="7"/>
-    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="27" dataDxfId="6"/>
-    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="28" dataDxfId="5"/>
-    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="29" dataDxfId="4"/>
-    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="30" dataDxfId="3"/>
-    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="31" dataDxfId="2"/>
-    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Fecha de _x000a_Ingreso según RAS" dataDxfId="1" dataCellStyle="Millares 10"/>
-    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="Causal / Observado" dataDxfId="0" dataCellStyle="Millares 10"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="RESPONSABLE DE PRODUCCIÓN" dataDxfId="113"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="GEOGRAFÍA" dataDxfId="112"/>
+    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="CATEGORÍA" dataDxfId="111"/>
+    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="MARCA" dataDxfId="110"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="CÓDIGO" dataDxfId="109"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="DESCRIPCIÓN" dataDxfId="108"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Plan de demanda" dataDxfId="107"/>
+    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="Plan Demanda (Kg)" dataDxfId="106"/>
+    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Salidas varias" dataDxfId="105"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Avance Vta." dataDxfId="104"/>
+    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Avance _x000a_Vta. (Kg)" dataDxfId="103" dataCellStyle="Porcentaje"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="%V Mes actual" dataDxfId="102" dataCellStyle="Porcentaje"/>
+    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="Error ABS_x000a_(KG)" dataDxfId="101" dataCellStyle="Porcentaje"/>
+    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Días consumidos por sobreventa en el mes pasado" dataDxfId="100" dataCellStyle="Porcentaje"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="%V Mes pasado" dataDxfId="99" dataCellStyle="Porcentaje"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="STOCK TOTAL" dataDxfId="98"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="STOCK POR FACTURAR" dataDxfId="97"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="CEDI FINAL" dataDxfId="96"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="PLANTA" dataDxfId="95"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="TRANSITO" dataDxfId="94"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="CALIDAD" dataDxfId="93"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="BLOQUEADO" dataDxfId="92"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Vta. Proy." dataDxfId="91"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Días De Inventario" dataDxfId="90"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Faltante" dataDxfId="89"/>
+    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="Valorizado Plan de Demanda" dataDxfId="88" dataCellStyle="Moneda"/>
+    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="Valorizado Stock" dataDxfId="87" dataCellStyle="Moneda"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="% Cob." dataDxfId="86" dataCellStyle="Porcentaje"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="1" dataDxfId="85"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="2" dataDxfId="84"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="3" dataDxfId="83"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="4" dataDxfId="82"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="5" dataDxfId="81"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="6" dataDxfId="80"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="7" dataDxfId="79"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="8" dataDxfId="78"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="9" dataDxfId="77"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="10" dataDxfId="76"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="11" dataDxfId="75"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="12" dataDxfId="74"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="13" dataDxfId="73"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="14" dataDxfId="72"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="15" dataDxfId="71"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="16" dataDxfId="70"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="17" dataDxfId="69"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="18" dataDxfId="68"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="19" dataDxfId="67"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="20" dataDxfId="66"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="21" dataDxfId="65"/>
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="22" dataDxfId="64"/>
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="23" dataDxfId="63"/>
+    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="24" dataDxfId="62"/>
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="25" dataDxfId="61"/>
+    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="26" dataDxfId="60"/>
+    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="27" dataDxfId="59"/>
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="28" dataDxfId="58"/>
+    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="29" dataDxfId="57"/>
+    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="30" dataDxfId="56"/>
+    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="31" dataDxfId="55"/>
+    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Fecha de _x000a_Ingreso según RAS" dataDxfId="54" dataCellStyle="Millares 10"/>
+    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="Causal / Observado" dataDxfId="53" dataCellStyle="Millares 10"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16691,10 +16362,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="130" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B222">
-    <cfRule type="duplicateValues" dxfId="129" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" copies="0" r:id="rId1"/>
@@ -17882,10 +17553,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="128" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2">
-    <cfRule type="duplicateValues" dxfId="127" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" copies="0" r:id="rId1"/>
@@ -17951,25 +17622,25 @@
     </row>
     <row r="2" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="118"/>
-      <c r="B2" s="195" t="s">
+      <c r="B2" s="198" t="s">
         <v>341</v>
       </c>
-      <c r="C2" s="196"/>
-      <c r="D2" s="196"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="199">
+      <c r="C2" s="199"/>
+      <c r="D2" s="199"/>
+      <c r="E2" s="199"/>
+      <c r="F2" s="199"/>
+      <c r="G2" s="202">
         <v>46133</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="118"/>
-      <c r="B3" s="197"/>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="200"/>
+      <c r="B3" s="200"/>
+      <c r="C3" s="201"/>
+      <c r="D3" s="201"/>
+      <c r="E3" s="201"/>
+      <c r="F3" s="201"/>
+      <c r="G3" s="203"/>
     </row>
     <row r="4" spans="1:62" x14ac:dyDescent="0.35">
       <c r="A4" s="118"/>
@@ -18218,55 +17889,55 @@
       <c r="M17" s="20"/>
       <c r="N17" s="94"/>
       <c r="O17" s="21"/>
-      <c r="Q17" s="201" t="s">
+      <c r="Q17" s="204" t="s">
         <v>342</v>
       </c>
-      <c r="R17" s="202"/>
-      <c r="S17" s="203"/>
-      <c r="T17" s="201" t="s">
+      <c r="R17" s="205"/>
+      <c r="S17" s="206"/>
+      <c r="T17" s="204" t="s">
         <v>497</v>
       </c>
-      <c r="U17" s="202"/>
-      <c r="V17" s="202"/>
-      <c r="W17" s="202"/>
+      <c r="U17" s="205"/>
+      <c r="V17" s="205"/>
+      <c r="W17" s="205"/>
       <c r="X17" s="28"/>
       <c r="Y17" s="28"/>
       <c r="Z17" s="26"/>
       <c r="AA17" s="26"/>
       <c r="AB17" s="26"/>
-      <c r="AC17" s="194" t="s">
+      <c r="AC17" s="197" t="s">
         <v>331</v>
       </c>
-      <c r="AD17" s="194"/>
-      <c r="AE17" s="194"/>
-      <c r="AF17" s="194"/>
-      <c r="AG17" s="194"/>
-      <c r="AH17" s="194"/>
-      <c r="AI17" s="194"/>
-      <c r="AJ17" s="194"/>
-      <c r="AK17" s="194"/>
-      <c r="AL17" s="194"/>
-      <c r="AM17" s="194"/>
-      <c r="AN17" s="194"/>
-      <c r="AO17" s="194"/>
-      <c r="AP17" s="194"/>
-      <c r="AQ17" s="194"/>
-      <c r="AR17" s="194"/>
-      <c r="AS17" s="194"/>
-      <c r="AT17" s="194"/>
-      <c r="AU17" s="194"/>
-      <c r="AV17" s="194"/>
-      <c r="AW17" s="194"/>
-      <c r="AX17" s="194"/>
-      <c r="AY17" s="194"/>
-      <c r="AZ17" s="194"/>
-      <c r="BA17" s="194"/>
-      <c r="BB17" s="194"/>
-      <c r="BC17" s="194"/>
-      <c r="BD17" s="194"/>
-      <c r="BE17" s="194"/>
-      <c r="BF17" s="194"/>
-      <c r="BG17" s="194"/>
+      <c r="AD17" s="197"/>
+      <c r="AE17" s="197"/>
+      <c r="AF17" s="197"/>
+      <c r="AG17" s="197"/>
+      <c r="AH17" s="197"/>
+      <c r="AI17" s="197"/>
+      <c r="AJ17" s="197"/>
+      <c r="AK17" s="197"/>
+      <c r="AL17" s="197"/>
+      <c r="AM17" s="197"/>
+      <c r="AN17" s="197"/>
+      <c r="AO17" s="197"/>
+      <c r="AP17" s="197"/>
+      <c r="AQ17" s="197"/>
+      <c r="AR17" s="197"/>
+      <c r="AS17" s="197"/>
+      <c r="AT17" s="197"/>
+      <c r="AU17" s="197"/>
+      <c r="AV17" s="197"/>
+      <c r="AW17" s="197"/>
+      <c r="AX17" s="197"/>
+      <c r="AY17" s="197"/>
+      <c r="AZ17" s="197"/>
+      <c r="BA17" s="197"/>
+      <c r="BB17" s="197"/>
+      <c r="BC17" s="197"/>
+      <c r="BD17" s="197"/>
+      <c r="BE17" s="197"/>
+      <c r="BF17" s="197"/>
+      <c r="BG17" s="197"/>
       <c r="BH17" s="7"/>
     </row>
     <row r="18" spans="1:62" ht="39" x14ac:dyDescent="0.35">
@@ -18574,7 +18245,7 @@
       <c r="BH19" s="71"/>
       <c r="BI19" s="2"/>
       <c r="BJ19" s="31" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="20" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -19185,8 +18856,8 @@
       <c r="BG24" s="71"/>
       <c r="BH24" s="71"/>
       <c r="BI24" s="2"/>
-      <c r="BJ24" s="31" t="s">
-        <v>804</v>
+      <c r="BJ24" s="195" t="s">
+        <v>809</v>
       </c>
     </row>
     <row r="25" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -19311,8 +18982,8 @@
       <c r="BI25" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="BJ25" s="31" t="s">
-        <v>804</v>
+      <c r="BJ25" s="195" t="s">
+        <v>809</v>
       </c>
     </row>
     <row r="26" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -20284,7 +19955,7 @@
         <v>1</v>
       </c>
       <c r="BJ33" s="177" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="34" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -20653,8 +20324,8 @@
       <c r="BI36" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="BJ36" s="205" t="s">
-        <v>808</v>
+      <c r="BJ36" s="195" t="s">
+        <v>807</v>
       </c>
     </row>
     <row r="37" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -20904,7 +20575,7 @@
         <v>1</v>
       </c>
       <c r="BJ38" s="31" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="39" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -23248,7 +22919,7 @@
       <c r="F58" s="133">
         <v>1076009</v>
       </c>
-      <c r="G58" s="204" t="s">
+      <c r="G58" s="194" t="s">
         <v>655</v>
       </c>
       <c r="H58" s="129">
@@ -57671,7 +57342,7 @@
         <v>1</v>
       </c>
       <c r="BJ338" s="31" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="339" spans="2:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -83095,7 +82766,7 @@
       <c r="BJ546" s="176"/>
     </row>
     <row r="549" spans="2:62" x14ac:dyDescent="0.35">
-      <c r="H549" s="206"/>
+      <c r="H549" s="196"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -83107,128 +82778,110 @@
   </mergeCells>
   <phoneticPr fontId="33" type="noConversion"/>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="126" priority="496"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="496"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18">
-    <cfRule type="duplicateValues" dxfId="125" priority="724"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="724"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="duplicateValues" dxfId="30" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="duplicateValues" dxfId="29" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28:F34">
+    <cfRule type="duplicateValues" dxfId="28" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F59">
+    <cfRule type="duplicateValues" dxfId="27" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F60:F98 F261:F299 F118:F125 F100:F116 F216:F225 F127:F207 F482 F426:F472 F353:F388 F209:F214 F238:F251 F253:F259 F303:F314 F301 F485:F515 F474:F480 F390:F424 F227:F236 F35:F58 F26:F27 F20:F24 F316:F351">
+    <cfRule type="duplicateValues" dxfId="26" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F99">
+    <cfRule type="duplicateValues" dxfId="25" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F117">
+    <cfRule type="duplicateValues" dxfId="24" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F126">
+    <cfRule type="duplicateValues" dxfId="23" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F208">
+    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F215">
+    <cfRule type="duplicateValues" dxfId="21" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F226">
+    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F237">
+    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F252">
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F260">
+    <cfRule type="duplicateValues" dxfId="17" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F300">
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F302">
+    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F315">
+    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F352">
+    <cfRule type="duplicateValues" dxfId="13" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F389">
+    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F425">
+    <cfRule type="duplicateValues" dxfId="11" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F473">
+    <cfRule type="duplicateValues" dxfId="10" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F483">
+    <cfRule type="duplicateValues" dxfId="9" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F484">
+    <cfRule type="duplicateValues" dxfId="8" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F521">
+    <cfRule type="duplicateValues" dxfId="7" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F522">
+    <cfRule type="duplicateValues" dxfId="6" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F523:F524">
+    <cfRule type="duplicateValues" dxfId="5" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G45">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:O18">
-    <cfRule type="expression" dxfId="97" priority="630" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="630" stopIfTrue="1">
       <formula>"g4&gt;1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P18">
-    <cfRule type="expression" dxfId="96" priority="629" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="629" stopIfTrue="1">
       <formula>"g4&gt;1"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y508:Y514 Y19:Y479">
-    <cfRule type="cellIs" dxfId="93" priority="7" operator="between">
+  <conditionalFormatting sqref="Y19:Y514">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
       <formula>5</formula>
       <formula>10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>5</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y480">
-    <cfRule type="cellIs" dxfId="91" priority="4" operator="between">
-      <formula>5</formula>
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="5" operator="lessThan">
-      <formula>5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y481:Y507">
-    <cfRule type="cellIs" dxfId="89" priority="2" operator="between">
-      <formula>5</formula>
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="3" operator="lessThan">
-      <formula>5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G45">
-    <cfRule type="duplicateValues" dxfId="87" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F60:F98 F261:F299 F118:F125 F100:F116 F216:F225 F127:F207 F482 F426:F472 F353:F388 F209:F214 F238:F251 F253:F259 F303:F314 F301 F485:F515 F474:F480 F390:F424 F227:F236 F35:F58 F26:F27 F20:F24 F316:F351">
-    <cfRule type="duplicateValues" dxfId="86" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F315">
-    <cfRule type="duplicateValues" dxfId="85" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F226">
-    <cfRule type="duplicateValues" dxfId="84" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F389">
-    <cfRule type="duplicateValues" dxfId="83" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F473">
-    <cfRule type="duplicateValues" dxfId="82" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F483">
-    <cfRule type="duplicateValues" dxfId="81" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F484">
-    <cfRule type="duplicateValues" dxfId="80" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F300">
-    <cfRule type="duplicateValues" dxfId="79" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F302">
-    <cfRule type="duplicateValues" dxfId="78" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F252">
-    <cfRule type="duplicateValues" dxfId="77" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F237">
-    <cfRule type="duplicateValues" dxfId="76" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F208">
-    <cfRule type="duplicateValues" dxfId="75" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F352">
-    <cfRule type="duplicateValues" dxfId="74" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F425">
-    <cfRule type="duplicateValues" dxfId="73" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F521">
-    <cfRule type="duplicateValues" dxfId="72" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F28:F34">
-    <cfRule type="duplicateValues" dxfId="71" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
-    <cfRule type="duplicateValues" dxfId="70" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F523:F524">
-    <cfRule type="duplicateValues" dxfId="69" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F522">
-    <cfRule type="duplicateValues" dxfId="68" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F126">
-    <cfRule type="duplicateValues" dxfId="67" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F215">
-    <cfRule type="duplicateValues" dxfId="66" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F59">
-    <cfRule type="duplicateValues" dxfId="65" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F99">
-    <cfRule type="duplicateValues" dxfId="64" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F117">
-    <cfRule type="duplicateValues" dxfId="63" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F260">
-    <cfRule type="duplicateValues" dxfId="62" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="61" priority="36"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="18" orientation="portrait" horizontalDpi="300" r:id="rId1"/>
@@ -83241,25 +82894,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="9" id="{6136961E-F6EF-4F9C-80ED-958EA14FC7F2}">
-            <x14:iconSet custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>10</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>46</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3TrafficLights1" iconId="0"/>
-              <x14:cfIcon iconSet="3TrafficLights1" iconId="2"/>
-              <x14:cfIcon iconSet="3TrafficLights1" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>Y508:Y514 Y19:Y479</xm:sqref>
-        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="6" id="{13BEF9CA-572B-444D-883D-57892FC911CB}">
             <x14:iconSet custom="1">
@@ -83298,6 +82932,25 @@
           </x14:cfRule>
           <xm:sqref>Y481:Y507</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="9" id="{6136961E-F6EF-4F9C-80ED-958EA14FC7F2}">
+            <x14:iconSet custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>10</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>46</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3TrafficLights1" iconId="0"/>
+              <x14:cfIcon iconSet="3TrafficLights1" iconId="2"/>
+              <x14:cfIcon iconSet="3TrafficLights1" iconId="0"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>Y508:Y514 Y19:Y479</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/datos_stock.xlsx
+++ b/datos_stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fpjmojeda\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2BF6F6-9C52-4002-81C5-2CE5948DC5D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADC01D3-651A-41E2-B152-9E57A4A3B2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12300" tabRatio="813" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4419,6 +4419,15 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4448,15 +4457,6 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="7" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="67">
@@ -4528,7 +4528,531 @@
     <cellStyle name="Título 3" xfId="13" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="26" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="172">
+  <dxfs count="143">
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4541,17 +5065,183 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color auto="1"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -6778,817 +7468,16 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
+      <border outline="0">
+        <left style="dashed">
           <color indexed="64"/>
         </left>
-        <right/>
-        <top style="thin">
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -7603,196 +7492,17 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="1"/>
+        <color auto="1"/>
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF002060"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -8130,34 +7840,34 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="PivotStyleMedium6 2" table="0" count="13" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="171"/>
-      <tableStyleElement type="headerRow" dxfId="170"/>
-      <tableStyleElement type="totalRow" dxfId="169"/>
-      <tableStyleElement type="firstRowStripe" dxfId="168"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="167"/>
-      <tableStyleElement type="firstHeaderCell" dxfId="166"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="165"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="164"/>
-      <tableStyleElement type="firstColumnSubheading" dxfId="163"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="162"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="161"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="160"/>
-      <tableStyleElement type="pageFieldValues" dxfId="159"/>
+      <tableStyleElement type="wholeTable" dxfId="142"/>
+      <tableStyleElement type="headerRow" dxfId="141"/>
+      <tableStyleElement type="totalRow" dxfId="140"/>
+      <tableStyleElement type="firstRowStripe" dxfId="139"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="138"/>
+      <tableStyleElement type="firstHeaderCell" dxfId="137"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="136"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="135"/>
+      <tableStyleElement type="firstColumnSubheading" dxfId="134"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="133"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="132"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="131"/>
+      <tableStyleElement type="pageFieldValues" dxfId="130"/>
     </tableStyle>
     <tableStyle name="PivotStyleMedium6 3" table="0" count="13" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" dxfId="158"/>
-      <tableStyleElement type="headerRow" dxfId="157"/>
-      <tableStyleElement type="totalRow" dxfId="156"/>
-      <tableStyleElement type="firstRowStripe" dxfId="155"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="154"/>
-      <tableStyleElement type="firstHeaderCell" dxfId="153"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="152"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="151"/>
-      <tableStyleElement type="firstColumnSubheading" dxfId="150"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="149"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="148"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="147"/>
-      <tableStyleElement type="pageFieldValues" dxfId="146"/>
+      <tableStyleElement type="wholeTable" dxfId="129"/>
+      <tableStyleElement type="headerRow" dxfId="128"/>
+      <tableStyleElement type="totalRow" dxfId="127"/>
+      <tableStyleElement type="firstRowStripe" dxfId="126"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="125"/>
+      <tableStyleElement type="firstHeaderCell" dxfId="124"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="123"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="122"/>
+      <tableStyleElement type="firstColumnSubheading" dxfId="121"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="120"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="119"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="118"/>
+      <tableStyleElement type="pageFieldValues" dxfId="117"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -8183,94 +7893,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TMR" displayName="TMR" ref="B2:L222" totalsRowShown="0" headerRowDxfId="143" dataDxfId="141" headerRowBorderDxfId="142" tableBorderDxfId="140" totalsRowBorderDxfId="139">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TMR" displayName="TMR" ref="B2:L222" totalsRowShown="0" headerRowDxfId="52" dataDxfId="50" headerRowBorderDxfId="51" tableBorderDxfId="49" totalsRowBorderDxfId="48">
   <autoFilter ref="B2:L222" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="CÓDIGO" dataDxfId="138"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="DESCRIPCIÓN" dataDxfId="137"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="ORIGEN" dataDxfId="136"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="CATEGORÍA" dataDxfId="135"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Tiempo de Vida" dataDxfId="134"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tottus" dataDxfId="133">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="CÓDIGO" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="DESCRIPCIÓN" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="ORIGEN" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="CATEGORÍA" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Tiempo de Vida" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tottus" dataDxfId="42">
       <calculatedColumnFormula>IF(F3&lt;=210,F3*0.6,IF(F3&lt;=365,120,IF(F3&lt;=3600,150)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Cencosud" dataDxfId="132"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Tambo" dataDxfId="131"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Oxxo" dataDxfId="130"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPSA / MAKRO" dataDxfId="129">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Cencosud" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Tambo" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Oxxo" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPSA / MAKRO" dataDxfId="38">
       <calculatedColumnFormula>ROUNDDOWN(F3/3,0)-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Canal Tradicional / Otros" dataDxfId="128"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Canal Tradicional / Otros" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Principal" displayName="Principal" ref="B18:BJ547" totalsRowShown="0" headerRowDxfId="145" dataDxfId="0" tableBorderDxfId="144" headerRowCellStyle="Normal 10 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Principal" displayName="Principal" ref="B18:BJ547" totalsRowShown="0" headerRowDxfId="116" dataDxfId="115" tableBorderDxfId="114" headerRowCellStyle="Normal 10 2">
   <autoFilter ref="B18:BJ547" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="61">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="RESPONSABLE DE PRODUCCIÓN" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="GEOGRAFÍA" dataDxfId="60"/>
-    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="CATEGORÍA" dataDxfId="59"/>
-    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="MARCA" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="CÓDIGO" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="DESCRIPCIÓN" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Plan de demanda" dataDxfId="55"/>
-    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="Plan Demanda (Kg)" dataDxfId="54"/>
-    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Salidas varias" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Avance Vta." dataDxfId="52"/>
-    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Avance _x000a_Vta. (Kg)" dataDxfId="51" dataCellStyle="Porcentaje"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="%V Mes actual" dataDxfId="50" dataCellStyle="Porcentaje"/>
-    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="Error ABS_x000a_(KG)" dataDxfId="49" dataCellStyle="Porcentaje"/>
-    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Días consumidos por sobreventa en el mes pasado" dataDxfId="48" dataCellStyle="Porcentaje"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="%V Mes pasado" dataDxfId="47" dataCellStyle="Porcentaje"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="STOCK TOTAL" dataDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="STOCK POR FACTURAR" dataDxfId="45"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="CEDI FINAL" dataDxfId="44"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="PLANTA" dataDxfId="43"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="TRANSITO" dataDxfId="42"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="CALIDAD" dataDxfId="41"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="BLOQUEADO" dataDxfId="40"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Vta. Proy." dataDxfId="39"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Días De Inventario" dataDxfId="38"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Faltante" dataDxfId="37"/>
-    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="Valorizado Plan de Demanda" dataDxfId="36" dataCellStyle="Moneda"/>
-    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="Valorizado Stock" dataDxfId="35" dataCellStyle="Moneda"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="% Cob." dataDxfId="34" dataCellStyle="Porcentaje"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="1" dataDxfId="33"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="2" dataDxfId="32"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="3" dataDxfId="31"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="4" dataDxfId="30"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="5" dataDxfId="29"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="6" dataDxfId="28"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="7" dataDxfId="27"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="8" dataDxfId="26"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="9" dataDxfId="25"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="10" dataDxfId="24"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="11" dataDxfId="23"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="12" dataDxfId="22"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="13" dataDxfId="21"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="14" dataDxfId="20"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="15" dataDxfId="19"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="16" dataDxfId="18"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="17" dataDxfId="17"/>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="18" dataDxfId="16"/>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="19" dataDxfId="15"/>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="20" dataDxfId="14"/>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="21" dataDxfId="13"/>
-    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="22" dataDxfId="12"/>
-    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="23" dataDxfId="11"/>
-    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="24" dataDxfId="10"/>
-    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="25" dataDxfId="9"/>
-    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="26" dataDxfId="8"/>
-    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="27" dataDxfId="7"/>
-    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="28" dataDxfId="6"/>
-    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="29" dataDxfId="5"/>
-    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="30" dataDxfId="4"/>
-    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="31" dataDxfId="3"/>
-    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Fecha de _x000a_Ingreso según RAS" dataDxfId="2" dataCellStyle="Millares 10"/>
-    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="Causal / Observado" dataDxfId="1" dataCellStyle="Millares 10"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="RESPONSABLE DE PRODUCCIÓN" dataDxfId="113"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="GEOGRAFÍA" dataDxfId="112"/>
+    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="CATEGORÍA" dataDxfId="111"/>
+    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="MARCA" dataDxfId="110"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="CÓDIGO" dataDxfId="109"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="DESCRIPCIÓN" dataDxfId="108"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Plan de demanda" dataDxfId="107"/>
+    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="Plan Demanda (Kg)" dataDxfId="106"/>
+    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Salidas varias" dataDxfId="105"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Avance Vta." dataDxfId="104"/>
+    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Avance _x000a_Vta. (Kg)" dataDxfId="103" dataCellStyle="Porcentaje"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="%V Mes actual" dataDxfId="102" dataCellStyle="Porcentaje"/>
+    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="Error ABS_x000a_(KG)" dataDxfId="101" dataCellStyle="Porcentaje"/>
+    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Días consumidos por sobreventa en el mes pasado" dataDxfId="100" dataCellStyle="Porcentaje"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="%V Mes pasado" dataDxfId="99" dataCellStyle="Porcentaje"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="STOCK TOTAL" dataDxfId="98"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="STOCK POR FACTURAR" dataDxfId="97"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="CEDI FINAL" dataDxfId="96"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="PLANTA" dataDxfId="95"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="TRANSITO" dataDxfId="94"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="CALIDAD" dataDxfId="93"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="BLOQUEADO" dataDxfId="92"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Vta. Proy." dataDxfId="91"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Días De Inventario" dataDxfId="90"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Faltante" dataDxfId="89"/>
+    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="Valorizado Plan de Demanda" dataDxfId="88" dataCellStyle="Moneda"/>
+    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="Valorizado Stock" dataDxfId="87" dataCellStyle="Moneda"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="% Cob." dataDxfId="86" dataCellStyle="Porcentaje"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="1" dataDxfId="85"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="2" dataDxfId="84"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="3" dataDxfId="83"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="4" dataDxfId="82"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="5" dataDxfId="81"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="6" dataDxfId="80"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="7" dataDxfId="79"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="8" dataDxfId="78"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="9" dataDxfId="77"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="10" dataDxfId="76"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="11" dataDxfId="75"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="12" dataDxfId="74"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="13" dataDxfId="73"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="14" dataDxfId="72"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="15" dataDxfId="71"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="16" dataDxfId="70"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="17" dataDxfId="69"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="18" dataDxfId="68"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="19" dataDxfId="67"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="20" dataDxfId="66"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="21" dataDxfId="65"/>
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="22" dataDxfId="64"/>
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="23" dataDxfId="63"/>
+    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="24" dataDxfId="62"/>
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="25" dataDxfId="61"/>
+    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="26" dataDxfId="60"/>
+    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="27" dataDxfId="59"/>
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="28" dataDxfId="58"/>
+    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="29" dataDxfId="57"/>
+    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="30" dataDxfId="56"/>
+    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="31" dataDxfId="55"/>
+    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Fecha de _x000a_Ingreso según RAS" dataDxfId="54" dataCellStyle="Millares 10"/>
+    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="Causal / Observado" dataDxfId="53" dataCellStyle="Millares 10"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16700,10 +16410,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="127" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B222">
-    <cfRule type="duplicateValues" dxfId="126" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" copies="0" r:id="rId1"/>
@@ -17891,10 +17601,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="125" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2">
-    <cfRule type="duplicateValues" dxfId="124" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" copies="0" r:id="rId1"/>
@@ -17960,25 +17670,25 @@
     </row>
     <row r="2" spans="1:62" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="110"/>
-      <c r="B2" s="190" t="s">
+      <c r="B2" s="193" t="s">
         <v>341</v>
       </c>
-      <c r="C2" s="191"/>
-      <c r="D2" s="191"/>
-      <c r="E2" s="191"/>
-      <c r="F2" s="191"/>
-      <c r="G2" s="194">
-        <v>46153</v>
+      <c r="C2" s="194"/>
+      <c r="D2" s="194"/>
+      <c r="E2" s="194"/>
+      <c r="F2" s="194"/>
+      <c r="G2" s="197">
+        <v>46154</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="110"/>
-      <c r="B3" s="192"/>
-      <c r="C3" s="193"/>
-      <c r="D3" s="193"/>
-      <c r="E3" s="193"/>
-      <c r="F3" s="193"/>
-      <c r="G3" s="195"/>
+      <c r="B3" s="195"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="196"/>
+      <c r="F3" s="196"/>
+      <c r="G3" s="198"/>
     </row>
     <row r="4" spans="1:62" x14ac:dyDescent="0.35">
       <c r="A4" s="110"/>
@@ -18227,55 +17937,55 @@
       <c r="M17" s="18"/>
       <c r="N17" s="91"/>
       <c r="O17" s="19"/>
-      <c r="Q17" s="196" t="s">
+      <c r="Q17" s="199" t="s">
         <v>342</v>
       </c>
-      <c r="R17" s="197"/>
-      <c r="S17" s="198"/>
-      <c r="T17" s="196" t="s">
+      <c r="R17" s="200"/>
+      <c r="S17" s="201"/>
+      <c r="T17" s="199" t="s">
         <v>497</v>
       </c>
-      <c r="U17" s="197"/>
-      <c r="V17" s="197"/>
-      <c r="W17" s="197"/>
+      <c r="U17" s="200"/>
+      <c r="V17" s="200"/>
+      <c r="W17" s="200"/>
       <c r="X17" s="26"/>
       <c r="Y17" s="26"/>
       <c r="Z17" s="24"/>
       <c r="AA17" s="24"/>
       <c r="AB17" s="24"/>
-      <c r="AC17" s="189" t="s">
+      <c r="AC17" s="192" t="s">
         <v>331</v>
       </c>
-      <c r="AD17" s="189"/>
-      <c r="AE17" s="189"/>
-      <c r="AF17" s="189"/>
-      <c r="AG17" s="189"/>
-      <c r="AH17" s="189"/>
-      <c r="AI17" s="189"/>
-      <c r="AJ17" s="189"/>
-      <c r="AK17" s="189"/>
-      <c r="AL17" s="189"/>
-      <c r="AM17" s="189"/>
-      <c r="AN17" s="189"/>
-      <c r="AO17" s="189"/>
-      <c r="AP17" s="189"/>
-      <c r="AQ17" s="189"/>
-      <c r="AR17" s="189"/>
-      <c r="AS17" s="189"/>
-      <c r="AT17" s="189"/>
-      <c r="AU17" s="189"/>
-      <c r="AV17" s="189"/>
-      <c r="AW17" s="189"/>
-      <c r="AX17" s="189"/>
-      <c r="AY17" s="189"/>
-      <c r="AZ17" s="189"/>
-      <c r="BA17" s="189"/>
-      <c r="BB17" s="189"/>
-      <c r="BC17" s="189"/>
-      <c r="BD17" s="189"/>
-      <c r="BE17" s="189"/>
-      <c r="BF17" s="189"/>
-      <c r="BG17" s="189"/>
+      <c r="AD17" s="192"/>
+      <c r="AE17" s="192"/>
+      <c r="AF17" s="192"/>
+      <c r="AG17" s="192"/>
+      <c r="AH17" s="192"/>
+      <c r="AI17" s="192"/>
+      <c r="AJ17" s="192"/>
+      <c r="AK17" s="192"/>
+      <c r="AL17" s="192"/>
+      <c r="AM17" s="192"/>
+      <c r="AN17" s="192"/>
+      <c r="AO17" s="192"/>
+      <c r="AP17" s="192"/>
+      <c r="AQ17" s="192"/>
+      <c r="AR17" s="192"/>
+      <c r="AS17" s="192"/>
+      <c r="AT17" s="192"/>
+      <c r="AU17" s="192"/>
+      <c r="AV17" s="192"/>
+      <c r="AW17" s="192"/>
+      <c r="AX17" s="192"/>
+      <c r="AY17" s="192"/>
+      <c r="AZ17" s="192"/>
+      <c r="BA17" s="192"/>
+      <c r="BB17" s="192"/>
+      <c r="BC17" s="192"/>
+      <c r="BD17" s="192"/>
+      <c r="BE17" s="192"/>
+      <c r="BF17" s="192"/>
+      <c r="BG17" s="192"/>
       <c r="BH17" s="7"/>
     </row>
     <row r="18" spans="1:62" ht="39" x14ac:dyDescent="0.35">
@@ -20955,7 +20665,7 @@
       <c r="F39" s="139">
         <v>1080749</v>
       </c>
-      <c r="G39" s="199" t="s">
+      <c r="G39" s="189" t="s">
         <v>769</v>
       </c>
       <c r="H39" s="143">
@@ -81836,7 +81546,7 @@
       <c r="BF546" s="69"/>
       <c r="BG546" s="69"/>
       <c r="BH546" s="69"/>
-      <c r="BI546" s="200"/>
+      <c r="BI546" s="190"/>
       <c r="BJ546" s="28"/>
     </row>
     <row r="547" spans="2:62" x14ac:dyDescent="0.3">
@@ -81858,7 +81568,7 @@
       <c r="G547" s="186" t="s">
         <v>641</v>
       </c>
-      <c r="H547" s="201"/>
+      <c r="H547" s="191"/>
       <c r="I547" s="143">
         <v>0</v>
       </c>
@@ -81965,109 +81675,109 @@
   </mergeCells>
   <phoneticPr fontId="33" type="noConversion"/>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="123" priority="876"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="876"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18">
-    <cfRule type="duplicateValues" dxfId="122" priority="1104"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="1104"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="duplicateValues" dxfId="30" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="duplicateValues" dxfId="29" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28:F34">
+    <cfRule type="duplicateValues" dxfId="28" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F59">
+    <cfRule type="duplicateValues" dxfId="27" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F60:F98 F261:F299 F118:F125 F100:F116 F216:F225 F127:F207 F482 F426:F472 F353:F388 F209:F214 F238:F251 F253:F259 F303:F314 F301 F485:F516 F474:F480 F390:F424 F227:F236 F35:F58 F26:F27 F20:F24 F316:F351">
+    <cfRule type="duplicateValues" dxfId="26" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F99">
+    <cfRule type="duplicateValues" dxfId="25" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F117">
+    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F126">
+    <cfRule type="duplicateValues" dxfId="23" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F208">
+    <cfRule type="duplicateValues" dxfId="22" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F215">
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F226">
+    <cfRule type="duplicateValues" dxfId="20" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F237">
+    <cfRule type="duplicateValues" dxfId="19" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F252">
+    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F260">
+    <cfRule type="duplicateValues" dxfId="17" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F300">
+    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F302">
+    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F315">
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F352">
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F389">
+    <cfRule type="duplicateValues" dxfId="12" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F425">
+    <cfRule type="duplicateValues" dxfId="11" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F473">
+    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F483">
+    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F484">
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F522">
+    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F523">
+    <cfRule type="duplicateValues" dxfId="6" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F524:F525">
+    <cfRule type="duplicateValues" dxfId="5" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G45">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:O18">
-    <cfRule type="expression" dxfId="94" priority="1010" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="1010" stopIfTrue="1">
       <formula>"g4&gt;1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P18">
-    <cfRule type="expression" dxfId="93" priority="1009" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="1009" stopIfTrue="1">
       <formula>"g4&gt;1"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="90" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
-    <cfRule type="duplicateValues" dxfId="89" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F28:F34">
-    <cfRule type="duplicateValues" dxfId="88" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F59">
-    <cfRule type="duplicateValues" dxfId="87" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F60:F98 F261:F299 F118:F125 F100:F116 F216:F225 F127:F207 F482 F426:F472 F353:F388 F209:F214 F238:F251 F253:F259 F303:F314 F301 F485:F516 F474:F480 F390:F424 F227:F236 F35:F58 F26:F27 F20:F24 F316:F351">
-    <cfRule type="duplicateValues" dxfId="86" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F99">
-    <cfRule type="duplicateValues" dxfId="85" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F117">
-    <cfRule type="duplicateValues" dxfId="84" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F126">
-    <cfRule type="duplicateValues" dxfId="83" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F208">
-    <cfRule type="duplicateValues" dxfId="82" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F215">
-    <cfRule type="duplicateValues" dxfId="81" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F226">
-    <cfRule type="duplicateValues" dxfId="80" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F237">
-    <cfRule type="duplicateValues" dxfId="79" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F252">
-    <cfRule type="duplicateValues" dxfId="78" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F260">
-    <cfRule type="duplicateValues" dxfId="77" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F300">
-    <cfRule type="duplicateValues" dxfId="76" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F302">
-    <cfRule type="duplicateValues" dxfId="75" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F315">
-    <cfRule type="duplicateValues" dxfId="74" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F352">
-    <cfRule type="duplicateValues" dxfId="73" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F389">
-    <cfRule type="duplicateValues" dxfId="72" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F425">
-    <cfRule type="duplicateValues" dxfId="71" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F473">
-    <cfRule type="duplicateValues" dxfId="70" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F483">
-    <cfRule type="duplicateValues" dxfId="69" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F484">
-    <cfRule type="duplicateValues" dxfId="68" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F522">
-    <cfRule type="duplicateValues" dxfId="67" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F523">
-    <cfRule type="duplicateValues" dxfId="66" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F524:F525">
-    <cfRule type="duplicateValues" dxfId="65" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G45">
-    <cfRule type="duplicateValues" dxfId="64" priority="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="Y19:Y514">
-    <cfRule type="cellIs" dxfId="63" priority="28" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="29" operator="lessThan">
+      <formula>5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="28" operator="between">
       <formula>5</formula>
       <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="29" operator="lessThan">
-      <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
